--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -11,7 +11,7 @@
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4699,37 +4699,37 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>GE-01</t>
+          <t>UI-01</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>禁止直收触发器件</t>
+          <t>历史记录查询</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P0（设计红线）</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>4.3.1.2</t>
+          <t>关联 DR-02/FA-11</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>设计检查 + 尝试将探测器/手报直接接入</t>
+          <t>进入查询→历史记录；翻页浏览；断电重启后再查</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
+          <t>事件按时间序列出（火警/故障/操作各类），内容与黑匣子一致；断电重启后记录仍在</t>
         </is>
       </c>
       <c r="I94" s="2" t="n"/>
@@ -4744,37 +4744,37 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>GE-02</t>
+          <t>UI-02</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>启动控制全流程</t>
+          <t>控制器信息</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 ↔ 5.3.1</t>
+          <t>第 8 章标志</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间</t>
+          <t>查看型号/软件版本/容量/地址</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>① 发出启动声光并记录时间（声可消，再有启动信号可再启动）；② 启动声光警报器；③ 进入延时：延时光指示+显示延时时间和保护区域+关闭防火门窗/防火阀+停通风空调；④ 延时结束发启动喷洒控制信号+光指示+启动喷洒光警报器；⑤ 喷洒阶段发出相应声光保持至复位并记录时间</t>
+          <t>与铭牌、说明书声明一致（软件版本号须与标志一致）</t>
         </is>
       </c>
       <c r="I95" s="2" t="n"/>
@@ -4789,37 +4789,37 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>GE-03</t>
+          <t>UI-03</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>延时设置与手动中止</t>
+          <t>设备总览</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.3 ↔ 5.3.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>调整延时值；延时期间执行手动停止</t>
+          <t>列出点表全部设备</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>延时 0～30 s 可调；延时期间能手动停止后续动作</t>
+          <t>设备数与点表一致；在线/报警/故障/屏蔽状态实时准确</t>
         </is>
       </c>
       <c r="I96" s="2" t="n"/>
@@ -4834,37 +4834,37 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>GE-04</t>
+          <t>UI-04</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>手/自动与优先级</t>
+          <t>单点查询</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4 ↔ 5.3.1</t>
+          <t>关联 FA-12</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
+          <t>选任一部位查看详情</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>有控制状态指示，状态不受复位影响；自动下手动插入优先；手动停止后再有启动信号仍按预置逻辑工作</t>
+          <t>类型/状态/注释准确；若支持阈值调节则显示当前设定值（设置界面外可查）</t>
         </is>
       </c>
       <c r="I97" s="2" t="n"/>
@@ -4879,37 +4879,37 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>GE-05</t>
+          <t>UI-05</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>声信号优先级</t>
+          <t>级联从机</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>△形态</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.5 ↔ 5.3.1</t>
+          <t>5.4.8</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>使喷洒声、启动声、故障声两两同时存在</t>
+          <t>组网信息显示</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
+          <t>独立型形态下应显示"无从机/未组网"；做组网时随 6.10 用例组补充</t>
         </is>
       </c>
       <c r="I98" s="2" t="n"/>
@@ -4924,37 +4924,37 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>GE-06</t>
+          <t>UI-06</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>接收联动信号</t>
+          <t>检查信息</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.6</t>
+          <t>关联 CK-01</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>消防联动控制器下发联动信号</t>
+          <t>菜单入口进入检查功能</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>正确接收并按逻辑执行</t>
+          <t>四总数（设计/正常/故障/屏蔽）正确；入口不受操作级别限制（5.4.9.1 豁免同样适用于菜单路径）</t>
         </is>
       </c>
       <c r="I99" s="2" t="n"/>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GE-07</t>
+          <t>UI-07</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>分区警报器与分区指示</t>
+          <t>节点设备监控</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>逐区启动/停止声光警报器</t>
+          <t>实时监视页面开着，使某设备状态变化（报警/故障/恢复）</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>可分区启动和停止保护区域声光警报器；每个保护区域有独立工作状态指示灯</t>
+          <t>页面刷新及时反映，且监视页面开着不影响报警声光与联动（任何界面停留都不阻断报警，FA-13 语义）</t>
         </is>
       </c>
       <c r="I100" s="2" t="n"/>
@@ -5014,37 +5014,37 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>GE-08</t>
+          <t>UI-08</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>向联动控制器上报</t>
+          <t>通讯成功率</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9 ↔ 5.3.1</t>
+          <t>企标特色·关联 FT-11</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>触发各阶段，在联动控制器（或模拟器）端核对</t>
+          <t>查看总线通信统计；用线间并电阻制造误码</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>能发送：启动控制信号、延时信号、启动喷洒控制信号、气体喷洒信号、故障信号、选择阀和瓶头阀动作信息</t>
+          <t>正常时成功率稳定；制造干扰后数值可观察地下降（该页是判断 d) 类隐患的运维工具）</t>
         </is>
       </c>
       <c r="I101" s="2" t="n"/>
@@ -5059,37 +5059,37 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>GE-09</t>
+          <t>UI-09</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>复位与状态重建</t>
+          <t>机内设备监控</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.11 ↔ 5.3.1</t>
+          <t>关联 PW-07</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>启动保持状态下手动复位，计时</t>
+          <t>查看主/备电电压、备电电量、充电状态</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>设复位按键；复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
+          <t>与万用表实测一致（容差内）；备电分段电压可见</t>
         </is>
       </c>
       <c r="I102" s="2" t="n"/>
@@ -5104,17 +5104,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>GE-10</t>
+          <t>UI-10</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>计时精度</t>
+          <t>启停控制</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12 ↔ 5.3.1</t>
+          <t>表 1 第 8 项</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>连续运行 24 h 比对</t>
+          <t>Ⅰ 级态尝试菜单启停某设备；Ⅱ 级登录后再操作</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>日计时误差 ≤30 s；打印含月日时分，不能仅用打印机记录</t>
+          <t>Ⅰ 级被拦；Ⅱ 级可启停，动作与黑匣子记录一致</t>
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
@@ -5149,17 +5149,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>GE-11</t>
+          <t>UI-11</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>输出特性</t>
+          <t>屏蔽控制</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.10 ↔ 5.3.1</t>
+          <t>关联 SH-01</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>测输出接点电压/电流/容量</t>
+          <t>菜单路径执行屏蔽/解除</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>满足制造商规定</t>
+          <t>权限、每次 1 只、报警/故障中不可屏——SH-01 全部判据经菜单路径同样成立</t>
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
@@ -5194,37 +5194,37 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>GE-12</t>
+          <t>UI-12</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>故障报警（部位/类型）</t>
+          <t>用户登陆</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
+          <t>关联 OP-01/02</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
+          <t>正确/错误密码各试；登录后放置超时</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>≤100 s 故障声光（声可消可再启动，光保持至排除）；a)/b) 指示部位；c)/d)/e) 指示类型；故障指示灯点亮</t>
+          <t>正确密码升级并显示当前级别（屏上"一级"图标变化）；错误拒绝；超时自动回落 Ⅰ 级</t>
         </is>
       </c>
       <c r="I105" s="2" t="n"/>
@@ -5239,17 +5239,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>GE-13</t>
+          <t>UI-13</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>阶段×故障双向互检</t>
+          <t>密码设置</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>关联 OP-03</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
+          <t>Ⅲ 级改各级密码；Ⅱ 级尝试改 Ⅲ 级密码</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>① 各阶段中故障均正常显示且不打断当前流程；② 故障先存在时，流程照常推进且故障指示灯全程保持</t>
+          <t>Ⅲ 可改；Ⅱ 改 Ⅲ 被拦（密钥单向性）；修改事件进黑匣子</t>
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
@@ -5284,37 +5284,37 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>GE-14</t>
+          <t>UI-14</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>故障复位复显与清空</t>
+          <t>基础设置·时钟</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
+          <t>关联 FA-11</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
+          <t>调整时钟</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>① 尚存故障 ≤100 s 重新显示；② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
+          <t>生效；黑匣子记录"调整时钟"事件（代码 131）；调后日误差仍 ≤6 s</t>
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
@@ -5329,37 +5329,37 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>GE-15</t>
+          <t>UI-15</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>自检不动作输出</t>
+          <t>联网设置</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.1 ↔ 5.3.3</t>
+          <t>关联 CM-01</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
+          <t>配置 CRT 通信参数</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>自检期间受控设备与输出接点均不动作；超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
+          <t>参数生效可重连；以太网口防外网侵入措施在位</t>
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
@@ -5374,37 +5374,37 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>GE-16</t>
+          <t>UI-16</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>面板自检</t>
+          <t>节点设置（点表编辑）</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.2 ↔ 5.3.3</t>
+          <t>关联 WD-03</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>手动检查音响、指示灯、显示器</t>
+          <t>Ⅲ 级编辑部位注释/类型/确认方式；编辑中途使真火警发生</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>全部可手动检查</t>
+          <t>编辑缓冲与运行配置分离、确认后原子生效；编辑过程中报警照常（输入不阻断报警）</t>
         </is>
       </c>
       <c r="I109" s="2" t="n"/>
@@ -5419,37 +5419,37 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>GE-17</t>
+          <t>UI-17</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>主备电转换</t>
+          <t>操作模式设置</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>LC-03 红线</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>断主电/恢复主电</t>
+          <t>先确认该菜单含义</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>自动转换、状态指示、主电过流保护、转换不误动作</t>
+          <t>若含手/自动切换：不合规——5.4.2.2 强制自复位钥匙开关，菜单软切换不满足；若仅为显示/声音模式设置则按 P1 正常测</t>
         </is>
       </c>
       <c r="I110" s="2" t="n"/>
@@ -5464,37 +5464,37 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>GE-18</t>
+          <t>UI-18</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>备电容量</t>
+          <t>点位注册</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
+          <t>注册新总线设备；故意注册重复地址</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>全程正常工作</t>
+          <t>正常注册入表；重复地址被检出拒绝</t>
         </is>
       </c>
       <c r="I111" s="2" t="n"/>
@@ -5509,37 +5509,37 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>GE-19</t>
+          <t>UI-19</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>电压容限</t>
+          <t>配置导入</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.2 ↔ 5.3.4</t>
+          <t>关联 WD-03</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
+          <t>导入合法配置；导入中断电；导入损坏文件</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>全范围正常工作</t>
+          <t>导入前校验（版本/CRC）；原子生效——中断/损坏则完整回滚到旧配置，绝无半套配置；导入事件进黑匣子</t>
         </is>
       </c>
       <c r="I112" s="2" t="n"/>
@@ -5554,17 +5554,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>GE-20</t>
+          <t>UI-20</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>现场数据断电保存</t>
+          <t>联动编程</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.2.4 b)</t>
+          <t>关联联动逻辑</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>断电 14 d 后上电检查现场设置数据</t>
+          <t>Ⅲ 级编辑与/或逻辑；未按确认前触发火警</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
+          <t>未确认的编辑不生效（旧逻辑照常联动）；确认后新逻辑生效并记录</t>
         </is>
       </c>
       <c r="I113" s="2" t="n"/>
@@ -5599,37 +5599,37 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>GE-21</t>
+          <t>UI-21</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>数据输入防意外执行</t>
+          <t>调试助手 / 直控调试</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.1.3</t>
+          <t>关联 OP-05 / 表 1 第 19 项</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>各状态下输入数据</t>
+          <t>进入调试功能收发信号</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>不引起程序意外执行</t>
+          <t>调试态边界：可收火警/故障、不启动真实联动输出、状态可区分；⚠权限审查：表 1"进入调试状态"属 Ⅳ 级（不能经本机），屏上标注"调试：调试员"的权限设计需与认证口径核对</t>
         </is>
       </c>
       <c r="I114" s="2" t="n"/>
@@ -5644,17 +5644,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>EX-01</t>
+          <t>UI-22</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>外观与包装</t>
+          <t>联网注册</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>完整包装、产品标志、合格标志、说明书；无腐蚀/脱漆/划伤/毛刺；紧固无松动</t>
+          <t>关联 CM 组</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>向 CRT/上级注册</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>注册流程完成，对端可见本机</t>
         </is>
       </c>
       <c r="I115" s="2" t="n"/>
@@ -5689,37 +5689,37 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>EX-02</t>
+          <t>UI-23</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>供电与接地</t>
+          <t>固件升级</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>主电 AC 220 V/50 Hz；保护接地；部件供电优先 DC 24 V；电源线独立接线端子</t>
+          <t>表 1 第 17 项</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>审查升级路径设计</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
+          <t>⚠"修改软硬件"属 Ⅳ 级、不能通过控制器本身进行——菜单入口必须强制依赖外部专用手段（专用上位机/签名固件+专用工具），裸菜单升级不合规；升级前后版本进黑匣子；升级失败可回滚</t>
         </is>
       </c>
       <c r="I116" s="2" t="n"/>
@@ -5734,17 +5734,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>EX-03</t>
+          <t>UI-24</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>按键与面板（报警控制器）</t>
+          <t>记录导出</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5754,17 +5754,17 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm；指示灯/按键按标准图 1/图 2 顺序排列；中文标注；按键有提示音</t>
+          <t>关联 DR-04</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>经 USB 导出运行记录</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.5/5.3.8</t>
+          <t>附录 B 口径：专用工具+授权、B/C 型母口 Device 模式；导出不影响记录本体；导出行为进黑匣子</t>
         </is>
       </c>
       <c r="I117" s="2" t="n"/>
@@ -5779,17 +5779,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>EX-04</t>
+          <t>UI-25</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>指示灯颜色</t>
+          <t>恢复出厂设置</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止（GB 4717 5.3.2.1）。气灭控制器：红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电（GB 16806 4.1.3.2.1）</t>
+          <t>B.1.1.3</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>高权限+二次确认执行；恢复后检查记录</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>清运行配置；不得清除运行记录/黑匣子（防删除是附录 B 硬要求——恢复出厂也不许抹历史）；恢复操作本身进黑匣子；恢复后设备按说明书声明状态启动</t>
         </is>
       </c>
       <c r="I118" s="2" t="n"/>
@@ -5824,37 +5824,37 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>EX-05</t>
+          <t>GE-01</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>指示灯可见性与闪动参数</t>
+          <t>禁止直收触发器件</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0（设计红线）</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：100～500 lx、22.5°，0.8 m/3 m（GB 4717 5.3.2.2）。气灭控制器：5～500 lx、22.5°、3 m；闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz；一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮（GB 16806 4.1.3.2）</t>
+          <t>4.3.1.2</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>设计检查 + 尝试将探测器/手报直接接入</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
@@ -5869,37 +5869,37 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>EX-06</t>
+          <t>GE-02</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>外壳防护与燃烧（报警控制器）</t>
+          <t>启动控制全流程</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>≥IP30；非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
+          <t>4.3.2.2 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.8/5.3.1.9</t>
+          <t>① 发出启动声光并记录时间（声可消，再有启动信号可再启动）；② 启动声光警报器；③ 进入延时：延时光指示+显示延时时间和保护区域+关闭防火门窗/防火阀+停通风空调；④ 延时结束发启动喷洒控制信号+光指示+启动喷洒光警报器；⑤ 喷洒阶段发出相应声光保持至复位并记录时间</t>
         </is>
       </c>
       <c r="I120" s="2" t="n"/>
@@ -5914,37 +5914,37 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>EX-07</t>
+          <t>GE-03</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>音响器件</t>
+          <t>延时设置与手动中止</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：1 m 处 65～105 dB(A)、接线防脱耐 50 N（GB 4717 5.3.4）。气灭控制器：1 m 处 &gt;65 且 &lt;115 dB(A)（GB 16806 4.1.3.4.1）。两者：85% 额定电压下正常发声</t>
+          <t>4.3.2.3 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>调整延时值；延时期间执行手动停止</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>延时 0～30 s 可调；延时期间能手动停止后续动作</t>
         </is>
       </c>
       <c r="I121" s="2" t="n"/>
@@ -5959,37 +5959,37 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>EX-08</t>
+          <t>GE-04</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>过负荷/熔断器</t>
+          <t>手/自动与优先级</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）；参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
+          <t>4.3.2.4 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+          <t>有控制状态指示，状态不受复位影响；自动下手动插入优先；手动停止后再有启动信号仍按预置逻辑工作</t>
         </is>
       </c>
       <c r="I122" s="2" t="n"/>
@@ -6004,17 +6004,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>EX-09</t>
+          <t>GE-05</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>端子与导线</t>
+          <t>声信号优先级</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>端子编号清晰；电池正极红线、负极黑/蓝线；（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
+          <t>4.3.2.5 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>使喷洒声、启动声、故障声两两同时存在</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
+          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
         </is>
       </c>
       <c r="I123" s="2" t="n"/>
@@ -6049,37 +6049,37 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>EX-10</t>
+          <t>GE-06</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>元件温升（气灭控制器）</t>
+          <t>接收联动信号</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>主要元件温升 ≤60℃；变压器等表面 ≤90℃（25±3℃）；电池周围 ≤45℃</t>
+          <t>4.3.2.6</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>消防联动控制器下发联动信号</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>正确接收并按逻辑执行</t>
         </is>
       </c>
       <c r="I124" s="2" t="n"/>
@@ -6094,17 +6094,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>GE-07</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>软件资料</t>
+          <t>分区警报器与分区指示</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6114,17 +6114,17 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号；程序存于不易丢失存储器；软件防非专门人员改动</t>
+          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>逐区启动/停止声光警报器</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>可分区启动和停止保护区域声光警报器；每个保护区域有独立工作状态指示灯</t>
         </is>
       </c>
       <c r="I125" s="2" t="n"/>
@@ -6139,37 +6139,37 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>GE-08</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>产品标志</t>
+          <t>向联动控制器上报</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
+          <t>4.3.2.9 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>触发各阶段，在联动控制器（或模拟器）端核对</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 8；GB 16806 7</t>
+          <t>能发送：启动控制信号、延时信号、启动喷洒控制信号、气体喷洒信号、故障信号、选择阀和瓶头阀动作信息</t>
         </is>
       </c>
       <c r="I126" s="2" t="n"/>
@@ -6184,37 +6184,37 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>TT-01</t>
+          <t>GE-09</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>绝缘电阻</t>
+          <t>复位与状态重建</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.2.11 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
+          <t>启动保持状态下手动复位，计时</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
+          <t>设复位按键；复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
         </is>
       </c>
       <c r="I127" s="2" t="n"/>
@@ -6229,37 +6229,37 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>TT-02</t>
+          <t>GE-10</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>泄漏电流</t>
+          <t>计时精度</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.2.12 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>同左（5.14）</t>
+          <t>连续运行 24 h 比对</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
+          <t>日计时误差 ≤30 s；打印含月日时分，不能仅用打印机记录</t>
         </is>
       </c>
       <c r="I128" s="2" t="n"/>
@@ -6274,37 +6274,37 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>TT-03</t>
+          <t>GE-11</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>电气强度</t>
+          <t>输出特性</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.2.10 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.15，不做</t>
+          <t>测输出接点电压/电流/容量</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
+          <t>满足制造商规定</t>
         </is>
       </c>
       <c r="I129" s="2" t="n"/>
@@ -6319,37 +6319,37 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>TT-04</t>
+          <t>GE-12</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>射频电磁场辐射</t>
+          <t>故障报警（部位/类型）</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.16）</t>
+          <t>分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
+          <t>≤100 s 故障声光（声可消可再启动，光保持至排除）；a)/b) 指示部位；c)/d)/e) 指示类型；故障指示灯点亮</t>
         </is>
       </c>
       <c r="I130" s="2" t="n"/>
@@ -6364,37 +6364,37 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>TT-05</t>
+          <t>GE-13</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>射频传导骚扰</t>
+          <t>阶段×故障双向互检</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>140 dBμV、0.15～100 MHz（5.17）</t>
+          <t>双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：140 dBμV、0.15～80 MHz（6.20）</t>
+          <t>① 各阶段中故障均正常显示且不打断当前流程；② 故障先存在时，流程照常推进且故障指示灯全程保持</t>
         </is>
       </c>
       <c r="I131" s="2" t="n"/>
@@ -6409,37 +6409,37 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>TT-06</t>
+          <t>GE-14</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>静电放电</t>
+          <t>故障复位复显与清空</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.18）</t>
+          <t>① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
+          <t>① 尚存故障 ≤100 s 重新显示；② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
@@ -6454,37 +6454,37 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>TT-07</t>
+          <t>GE-15</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>电快速瞬变</t>
+          <t>自检不动作输出</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.4.1 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
+          <t>自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
+          <t>自检期间受控设备与输出接点均不动作；超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
@@ -6499,37 +6499,37 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>TT-08</t>
+          <t>GE-16</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>浪涌</t>
+          <t>面板自检</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.4.2 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
+          <t>手动检查音响、指示灯、显示器</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
+          <t>全部可手动检查</t>
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
@@ -6544,37 +6544,37 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>TT-09</t>
+          <t>GE-17</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>电源瞬变</t>
+          <t>主备电转换</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>通 9 s/断 1 s×500 次（5.21）</t>
+          <t>断主电/恢复主电</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
+          <t>自动转换、状态指示、主电过流保护、转换不误动作</t>
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
@@ -6589,17 +6589,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>TT-10</t>
+          <t>GE-18</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>电压暂降</t>
+          <t>备电容量</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>40%/20 ms×10；0 V/10 ms×10（5.22）</t>
+          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40%/200 ms×10；0 V/20 ms×10（6.25）</t>
+          <t>全程正常工作</t>
         </is>
       </c>
       <c r="I136" s="2" t="n"/>
@@ -6634,37 +6634,37 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>TT-11</t>
+          <t>GE-19</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>低温（运行）</t>
+          <t>电压容限</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.3.5.2 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>0℃±3℃、16 h（5.23）</t>
+          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
+          <t>全范围正常工作</t>
         </is>
       </c>
       <c r="I137" s="2" t="n"/>
@@ -6679,37 +6679,37 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>TT-12</t>
+          <t>GE-20</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>恒定湿热（运行）</t>
+          <t>现场数据断电保存</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.1.5.2.4 b)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、90%～95%RH、4 d（5.24）</t>
+          <t>断电 14 d 后上电检查现场设置数据</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、4 d（6.27）</t>
+          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
         </is>
       </c>
       <c r="I138" s="2" t="n"/>
@@ -6724,37 +6724,37 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>TT-13</t>
+          <t>GE-21</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>恒定湿热（耐久）</t>
+          <t>数据输入防意外执行</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>4.1.5.1.3</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.25，不做</t>
+          <t>各状态下输入数据</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
+          <t>不引起程序意外执行</t>
         </is>
       </c>
       <c r="I139" s="2" t="n"/>
@@ -6769,37 +6769,37 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>TT-14</t>
+          <t>EX-01</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>振动（运行）</t>
+          <t>外观与包装</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>完整包装、产品标志、合格标志、说明书；无腐蚀/脱漆/划伤/毛刺；紧固无松动</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="I140" s="2" t="n"/>
@@ -6814,37 +6814,37 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>TT-15</t>
+          <t>EX-02</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>碰撞</t>
+          <t>供电与接地</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>主电 AC 220 V/50 Hz；保护接地；部件供电优先 DC 24 V；电源线独立接线端子</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.28）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：0.5 J±0.04 J×3 次/易损部件（6.30）</t>
+          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
         </is>
       </c>
       <c r="I141" s="2" t="n"/>
@@ -6859,37 +6859,37 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>TT-16</t>
+          <t>EX-03</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>外壳燃烧（非金属外壳）</t>
+          <t>按键与面板（报警控制器）</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm；指示灯/按键按标准图 1/图 2 顺序排列；中文标注；按键有提示音</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+          <t>GB 4717 5.3.1.5/5.3.8</t>
         </is>
       </c>
       <c r="I142" s="2" t="n"/>
@@ -6904,37 +6904,37 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>TT-17</t>
+          <t>EX-04</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>备用电池全项</t>
+          <t>指示灯颜色</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>报警控制器：红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止（GB 4717 5.3.2.1）。气灭控制器：红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电（GB 16806 4.1.3.2.1）</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：—（按整机备电试验 PW-04）</t>
+          <t>两标准分列</t>
         </is>
       </c>
       <c r="I143" s="2" t="n"/>
@@ -6943,9 +6943,1134 @@
       <c r="L143" s="2" t="n"/>
       <c r="M143" s="2" t="n"/>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>EX-05</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>指示灯可见性与闪动参数</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>报警控制器：100～500 lx、22.5°，0.8 m/3 m（GB 4717 5.3.2.2）。气灭控制器：5～500 lx、22.5°、3 m；闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz；一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮（GB 16806 4.1.3.2）</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>两标准分列</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>EX-06</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>外壳防护与燃烧（报警控制器）</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>≥IP30；非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>GB 4717 5.3.1.8/5.3.1.9</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
+      <c r="L145" s="2" t="n"/>
+      <c r="M145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>EX-07</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>音响器件</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>报警控制器：1 m 处 65～105 dB(A)、接线防脱耐 50 N（GB 4717 5.3.4）。气灭控制器：1 m 处 &gt;65 且 &lt;115 dB(A)（GB 16806 4.1.3.4.1）。两者：85% 额定电压下正常发声</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>两标准分列</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>EX-08</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>过负荷/熔断器</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）；参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n"/>
+      <c r="J147" s="2" t="n"/>
+      <c r="K147" s="2" t="n"/>
+      <c r="L147" s="2" t="n"/>
+      <c r="M147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>EX-09</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>端子与导线</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>端子编号清晰；电池正极红线、负极黑/蓝线；（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
+      <c r="K148" s="2" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>EX-10</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>元件温升（气灭控制器）</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>主要元件温升 ≤60℃；变压器等表面 ≤90℃（25±3℃）；电池周围 ≤45℃</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 4.1.3.10</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="n"/>
+      <c r="K149" s="2" t="n"/>
+      <c r="L149" s="2" t="n"/>
+      <c r="M149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>EX-11</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>软件资料</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号；程序存于不易丢失存储器；软件防非专门人员改动</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>EX-12</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>产品标志</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>GB 4717 8；GB 16806 7</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n"/>
+      <c r="J151" s="2" t="n"/>
+      <c r="K151" s="2" t="n"/>
+      <c r="L151" s="2" t="n"/>
+      <c r="M151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>TT-01</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>绝缘电阻</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>TT-02</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>泄漏电流</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>同左（5.14）</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n"/>
+      <c r="J153" s="2" t="n"/>
+      <c r="K153" s="2" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>TT-03</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>电气强度</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>表 4 未列 5.15，不做</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
+      <c r="K154" s="2" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>TT-04</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>射频电磁场辐射</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>同参数（5.16）</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n"/>
+      <c r="J155" s="2" t="n"/>
+      <c r="K155" s="2" t="n"/>
+      <c r="L155" s="2" t="n"/>
+      <c r="M155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>TT-05</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>射频传导骚扰</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>140 dBμV、0.15～100 MHz（5.17）</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：140 dBμV、0.15～80 MHz（6.20）</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
+      <c r="K156" s="2" t="n"/>
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>TT-06</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>静电放电</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>同参数（5.18）</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="n"/>
+      <c r="L157" s="2" t="n"/>
+      <c r="M157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>TT-07</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>电快速瞬变</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>TT-08</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>浪涌</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n"/>
+      <c r="J159" s="2" t="n"/>
+      <c r="K159" s="2" t="n"/>
+      <c r="L159" s="2" t="n"/>
+      <c r="M159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>TT-09</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>电源瞬变</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>通 9 s/断 1 s×500 次（5.21）</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="n"/>
+      <c r="K160" s="2" t="n"/>
+      <c r="L160" s="2" t="n"/>
+      <c r="M160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>TT-10</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>电压暂降</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>40%/20 ms×10；0 V/10 ms×10（5.22）</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40%/200 ms×10；0 V/20 ms×10（6.25）</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n"/>
+      <c r="J161" s="2" t="n"/>
+      <c r="K161" s="2" t="n"/>
+      <c r="L161" s="2" t="n"/>
+      <c r="M161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>TT-11</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>低温（运行）</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>0℃±3℃、16 h（5.23）</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="n"/>
+      <c r="K162" s="2" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>TT-12</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>恒定湿热（运行）</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>40℃±2℃、90%～95%RH、4 d（5.24）</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40℃±2℃、93%±3%RH、4 d（6.27）</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n"/>
+      <c r="J163" s="2" t="n"/>
+      <c r="K163" s="2" t="n"/>
+      <c r="L163" s="2" t="n"/>
+      <c r="M163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>TT-13</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>恒定湿热（耐久）</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>表 4 未列 5.25，不做</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n"/>
+      <c r="J164" s="2" t="n"/>
+      <c r="K164" s="2" t="n"/>
+      <c r="L164" s="2" t="n"/>
+      <c r="M164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>TT-14</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>振动（运行）</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="n"/>
+      <c r="K165" s="2" t="n"/>
+      <c r="L165" s="2" t="n"/>
+      <c r="M165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>TT-15</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>碰撞</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>同参数（5.28）</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：0.5 J±0.04 J×3 次/易损部件（6.30）</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
+      <c r="L166" s="2" t="n"/>
+      <c r="M166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>TT-16</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>外壳燃烧（非金属外壳）</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="n"/>
+      <c r="K167" s="2" t="n"/>
+      <c r="L167" s="2" t="n"/>
+      <c r="M167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>TT-17</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>备用电池全项</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：—（按整机备电试验 PW-04）</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M143"/>
-  <conditionalFormatting sqref="J2:J143">
+  <autoFilter ref="A1:M168"/>
+  <conditionalFormatting sqref="J2:J168">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"通过"</formula>
     </cfRule>
@@ -6954,7 +8079,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J143" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6994,7 +8119,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -7004,7 +8129,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTA(测试执行表!J2:J143)-COUNTIF(测试执行表!J2:J143,"待测")</f>
+        <f>COUNTA(测试执行表!J2:J168)-COUNTIF(测试执行表!J2:J168,"待测")</f>
         <v/>
       </c>
     </row>
@@ -7015,7 +8140,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!J2:J143,"通过")</f>
+        <f>COUNTIF(测试执行表!J2:J168,"通过")</f>
         <v/>
       </c>
     </row>
@@ -7026,7 +8151,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!J2:J143,"不通过")</f>
+        <f>COUNTIF(测试执行表!J2:J168,"不通过")</f>
         <v/>
       </c>
     </row>
@@ -7037,7 +8162,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!J2:J143,"不适用")</f>
+        <f>COUNTIF(测试执行表!J2:J168,"不适用")</f>
         <v/>
       </c>
     </row>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -11,7 +11,7 @@
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3169,37 +3169,37 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PW-01</t>
+          <t>CK-04</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>主备电自动转换</t>
+          <t>检查页·设备类型分行</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5.4.11.1 ↔ 6.13.1</t>
+          <t>5.4.9.1</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>切断主电→观察；恢复主电→观察</t>
+          <t>进入检查页查看行结构</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>自动转备电、自动转回主电；转换不发火警；主备电状态指示正确；主备电均有过流保护</t>
+          <t>按类型分行：烟感/温感/手报/消火栓/声光/显示盘/模块/其他 + 总计行；总计＝各行之和</t>
         </is>
       </c>
       <c r="I60" s="2" t="n"/>
@@ -3214,37 +3214,37 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PW-02</t>
+          <t>CK-05</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>电压容限</t>
+          <t>检查页·设计数量列</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>5.4.11.4</t>
+          <t>5.4.9.1 a)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>输入 187 V / 220 V / 242 V（(50±1) Hz）分别做基本功能试验</t>
+          <t>与点表工程配置比对</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>全范围正常工作</t>
+          <t>各行设计数量与点表一致（实机：总计 4＝烟感1+声光1+模块1+其他1）</t>
         </is>
       </c>
       <c r="I61" s="2" t="n"/>
@@ -3259,37 +3259,37 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PW-03</t>
+          <t>CK-06</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>主电容量</t>
+          <t>检查页·正常数量列</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>5.4.11.2 ↔ 6.13.2</t>
+          <t>5.4.9.1 b)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>一个回路接真实负载（回路线 1 000 m、1.0 mm² 铜绞线）；≤10 部位全报警 / &gt;10 部位时 20%（10～30 个）报警；连续 4 h</t>
+          <t>与实际在线设备比对</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4 h 正常工作</t>
+          <t>正常数量＝当前实际在线数（实机：3）</t>
         </is>
       </c>
       <c r="I62" s="2" t="n"/>
@@ -3304,37 +3304,37 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PW-04</t>
+          <t>CK-07</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>备电容量</t>
+          <t>检查页·故障数量列</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>5.4.11.3 ↔ 6.13.3</t>
+          <t>5.4.9.1 c)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>备电放至终止电压→充电 24 h→断主电监视 8 h→1/15 部位（10～30 个）报警工作 30 min</t>
+          <t>与故障表交叉比对</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>全程正常工作</t>
+          <t>故障数量与故障信息页一致（实机：1＝输入模块断路；存储单元/打印机属机内设备不计入点表口径，正确）</t>
         </is>
       </c>
       <c r="I63" s="2" t="n"/>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PW-05</t>
+          <t>CK-08</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>直流输出稳定度</t>
+          <t>检查页·屏蔽数量列</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5.4.11.4 ↔ 6.13.2.3</t>
+          <t>5.4.9.1 d)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>220/187/242 V 下测输出直流电压；等效负载阶跃测负载稳定度</t>
+          <t>无屏蔽时查看该列</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>电压稳定度、负载稳定度均 ≤5%</t>
+          <t>无屏蔽时应显式显示 0（不许留空白——空白无法区分"0"与"没读到数据"）</t>
         </is>
       </c>
       <c r="I64" s="2" t="n"/>
@@ -3394,17 +3394,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>PW-06</t>
+          <t>CK-09</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>总线末端压降</t>
+          <t>检查键联动进入检查页</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6.13.2.4</t>
+          <t>5.4.9.1</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>回路接 1 000 m、1.0 mm² 铜绞线，末端接 10 只探测器；187/220/242 V 下使末端 10 只全部报警</t>
+          <t>按面板检查键</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>末端探测器正常报警、确认灯及信号收发正常</t>
+          <t>直接进入本页（菜单"检查信息"入口与物理键到达同一页面）</t>
         </is>
       </c>
       <c r="I65" s="2" t="n"/>
@@ -3439,17 +3439,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>PW-07</t>
+          <t>CK-10</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>备电显示与分段保护</t>
+          <t>检查开启灯</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3459,17 +3459,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>5.3.7.4</t>
+          <t>5.4.9.1</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>检查备电电压/电量显示；使某段电压降至 &lt;90% 额定</t>
+          <t>进入/退出检查状态各一次</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>显示备电电压和电量；串接电池组额定 ≤12 V 时分段保护并显示每段电压（每段 ≤13 V）；任一段 &lt;90% 额定→故障声光并指示部位</t>
+          <t>进入点亮"开启"灯，退出熄灭</t>
         </is>
       </c>
       <c r="I66" s="2" t="n"/>
@@ -3484,37 +3484,37 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PW-08</t>
+          <t>CK-11</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>检查功能</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>备电电池选型检查</t>
+          <t>检查权限豁免</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P0（设计检查）</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>5.3.7.3</t>
+          <t>5.4.9.1</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>核对电池化学体系</t>
+          <t>Ⅰ 级（未登录）状态按检查键</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>禁用钴酸锂、三元锂及其他含钴锂电池</t>
+          <t>不受操作级别限制，Ⅰ 级即可进入</t>
         </is>
       </c>
       <c r="I67" s="2" t="n"/>
@@ -3529,17 +3529,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>WD-01</t>
+          <t>PW-01</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>看门狗</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>看门狗系统故障</t>
+          <t>主备电自动转换</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>5.4.12.1 ↔ 6.14.2</t>
+          <t>5.4.11.1 ↔ 6.13.1</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>操作"模拟 MCU 不能正常运行装置"使主程序停摆，计时</t>
+          <t>切断主电→观察；恢复主电→观察</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>≤100 s 发出系统故障信号、点亮单独的系统故障灯、进入异常状态（不发火警、不启动输出、不上传 CRT）</t>
+          <t>自动转备电、自动转回主电；转换不发火警；主备电状态指示正确；主备电均有过流保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="n"/>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>WD-02</t>
+          <t>PW-02</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>看门狗</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>存储器出错检测</t>
+          <t>电压容限</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3594,17 +3594,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>5.4.12.1 ↔ 6.14.3</t>
+          <t>5.4.11.4</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>使程序区/指定数据区内容出错</t>
+          <t>输入 187 V / 220 V / 242 V（(50±1) Hz）分别做基本功能试验</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>同 WD-01 判定</t>
+          <t>全范围正常工作</t>
         </is>
       </c>
       <c r="I69" s="2" t="n"/>
@@ -3619,37 +3619,37 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>WD-03</t>
+          <t>PW-03</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>看门狗</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>数据输入防意外执行</t>
+          <t>主电容量</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>5.4.12.2 ↔ 6.14.4</t>
+          <t>5.4.11.2 ↔ 6.13.2</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>各状态下手动/程序输入数据</t>
+          <t>一个回路接真实负载（回路线 1 000 m、1.0 mm² 铜绞线）；≤10 部位全报警 / &gt;10 部位时 20%（10～30 个）报警；连续 4 h</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>不引起程序意外执行</t>
+          <t>4 h 正常工作</t>
         </is>
       </c>
       <c r="I70" s="2" t="n"/>
@@ -3664,37 +3664,37 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>WD-04</t>
+          <t>PW-04</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>看门狗</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>探测器确认灯</t>
+          <t>备电容量</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>5.4.12.3 ↔ 6.14.5</t>
+          <t>5.4.11.3 ↔ 6.13.3</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>使探测器报警观察确认灯</t>
+          <t>备电放至终止电压→充电 24 h→断主电监视 8 h→1/15 部位（10～30 个）报警工作 30 min</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>发火警同时启动确认灯；常亮且与监视状态有明显区别</t>
+          <t>全程正常工作</t>
         </is>
       </c>
       <c r="I71" s="2" t="n"/>
@@ -3709,37 +3709,37 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CM-01</t>
+          <t>PW-05</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>接口形态</t>
+          <t>直流输出稳定度</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>5.4.10.1</t>
+          <t>5.4.11.4 ↔ 6.13.2.3</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>检查物理接口</t>
+          <t>220/187/242 V 下测输出直流电压；等效负载阶跃测负载稳定度</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>RS485 / CAN / 以太网至少一种；有防脱落措施；以太网需有防外网侵入措施</t>
+          <t>电压稳定度、负载稳定度均 ≤5%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n"/>
@@ -3754,37 +3754,37 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CM-02</t>
+          <t>PW-06</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>五类信息上报</t>
+          <t>总线末端压降</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5.4.10.2 ↔ 6.12.3～6.12.7</t>
+          <t>6.13.2.4</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>分别触发火警、监管、联动（启动/反馈）、屏蔽、故障（含 5.4.3.3 a～c 与 5.4.3.4 a～c 各类）并在 CRT 端抓包比对</t>
+          <t>回路接 1 000 m、1.0 mm² 铜绞线，末端接 10 只探测器；187/220/242 V 下使末端 10 只全部报警</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>上报信息含类别、名称、部位、位置、时间、工作状态（含故障恢复状态）；内容与本机状态一致</t>
+          <t>末端探测器正常报警、确认灯及信号收发正常</t>
         </is>
       </c>
       <c r="I73" s="2" t="n"/>
@@ -3799,37 +3799,37 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CM-03</t>
+          <t>PW-07</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>授时接收</t>
+          <t>备电显示与分段保护</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5.4.10.3</t>
+          <t>5.3.7.4</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>CRT 端下发授时</t>
+          <t>检查备电电压/电量显示；使某段电压降至 &lt;90% 额定</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>控制器接收授时并校准时钟</t>
+          <t>显示备电电压和电量；串接电池组额定 ≤12 V 时分段保护并显示每段电压（每段 ≤13 V）；任一段 &lt;90% 额定→故障声光并指示部位</t>
         </is>
       </c>
       <c r="I74" s="2" t="n"/>
@@ -3844,37 +3844,37 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CM-04</t>
+          <t>PW-08</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>电源</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>协议一致性</t>
+          <t>备电电池选型检查</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P0（设计检查）</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>5.4.10.4 / 附录 C</t>
+          <t>5.3.7.3</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>抓包核对帧结构</t>
+          <t>核对电池化学体系</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>符合附录 C（见 11.2）</t>
+          <t>禁用钴酸锂、三元锂及其他含钴锂电池</t>
         </is>
       </c>
       <c r="I75" s="2" t="n"/>
@@ -3889,37 +3889,37 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CM-10</t>
+          <t>WD-01</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>看门狗</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>帧格式</t>
+          <t>看门狗系统故障</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>C.4.1 / C.6</t>
+          <t>5.4.12.1 ↔ 6.14.2</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>抓包核对</t>
+          <t>操作"模拟 MCU 不能正常运行装置"使主程序停摆，计时</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>串行链路：起止符 0x7E、1起始+8数据+1停止无校验、波特率优先 4800/9600/19200；CRC16 多项式 0xA001 低字节在前；CAN：2.0B 29 bit ID、波特率优先 5/10/20/50/100 Kbit/s</t>
+          <t>≤100 s 发出系统故障信号、点亮单独的系统故障灯、进入异常状态（不发火警、不启动输出、不上传 CRT）</t>
         </is>
       </c>
       <c r="I76" s="2" t="n"/>
@@ -3934,37 +3934,37 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CM-11</t>
+          <t>WD-02</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>看门狗</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>地址与容量</t>
+          <t>存储器出错检测</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>C.3.2.2 / C.7.2.2</t>
+          <t>5.4.12.1 ↔ 6.14.3</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>配置地址边界值</t>
+          <t>使程序区/指定数据区内容出错</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>主控节点地址=1；消防电气控制装置 2～63；0=广播；总数 ≤62</t>
+          <t>同 WD-01 判定</t>
         </is>
       </c>
       <c r="I77" s="2" t="n"/>
@@ -3979,37 +3979,37 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CM-12</t>
+          <t>WD-03</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>看门狗</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>应答重发</t>
+          <t>数据输入防意外执行</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>C.3.3</t>
+          <t>5.4.12.2 ↔ 6.14.4</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>屏蔽应答，观察重发</t>
+          <t>各状态下手动/程序输入数据</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1 s 未应答重发，≤3 次</t>
+          <t>不引起程序意外执行</t>
         </is>
       </c>
       <c r="I78" s="2" t="n"/>
@@ -4024,17 +4024,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CM-13</t>
+          <t>WD-04</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>看门狗</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>建链流程</t>
+          <t>探测器确认灯</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>C.6</t>
+          <t>5.4.12.3 ↔ 6.14.5</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>冷启动/断线重连抓包</t>
+          <t>使探测器报警观察确认灯</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>主机发功能码 44（查协议版本）→应答→发 41（查当前事件）→记录；中断重连同流程</t>
+          <t>发火警同时启动确认灯；常亮且与监视状态有明显区别</t>
         </is>
       </c>
       <c r="I79" s="2" t="n"/>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CM-14</t>
+          <t>CM-01</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4079,27 +4079,27 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>状态应答码</t>
+          <t>接口形态</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>C.4.2.5</t>
+          <t>5.4.10.1</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>构造 CRC 错、无效请求、地址不存在等异常帧</t>
+          <t>检查物理接口</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>应答码正确（1=CRC 错、2=无效服务、6=地址不存在、7=参数错误等）</t>
+          <t>RS485 / CAN / 以太网至少一种；有防脱落措施；以太网需有防外网侵入措施</t>
         </is>
       </c>
       <c r="I80" s="2" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CM-15</t>
+          <t>CM-02</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4124,27 +4124,27 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>事件/类型代码表与装置状态显示</t>
+          <t>五类信息上报</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>表 C.16/C.17/C.18；6.4.13</t>
+          <t>5.4.10.2 ↔ 6.12.3～6.12.7</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>对照抓包中设备类型、事件类型、状态位；将连接的消防电气控制装置分别置于手动/自动状态</t>
+          <t>分别触发火警、监管、联动（启动/反馈）、屏蔽、故障（含 5.4.3.3 a～c 与 5.4.3.4 a～c 各类）并在 CRT 端抓包比对</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>与代码表一致（如 2=首火警、3=火警、19=启动、26=反馈、122=复位；状态 bit0=手/自动等）；电气控制装置的手/自动状态在本机正确显示（6.4.13）</t>
+          <t>上报信息含类别、名称、部位、位置、时间、工作状态（含故障恢复状态）；内容与本机状态一致</t>
         </is>
       </c>
       <c r="I81" s="2" t="n"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CM-16</t>
+          <t>CM-03</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4169,27 +4169,27 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>通信线独立性</t>
+          <t>授时接收</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>P0（设计检查）</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>5.3.1.6</t>
+          <t>5.4.10.3</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>检查布线设计</t>
+          <t>CRT 端下发授时</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>FECbus 独立通信线路，不与报警总线/联动总线共用</t>
+          <t>控制器接收授时并校准时钟</t>
         </is>
       </c>
       <c r="I82" s="2" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CM-17</t>
+          <t>CM-04</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4214,27 +4214,27 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>通信线冗余</t>
+          <t>协议一致性</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>C.3.2.3</t>
+          <t>5.4.10.4 / 附录 C</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>通信线任一点断路/短路</t>
+          <t>抓包核对帧结构</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>控制器与消防电气控制装置仍能正常通信</t>
+          <t>符合附录 C（见 11.2）</t>
         </is>
       </c>
       <c r="I83" s="2" t="n"/>
@@ -4249,37 +4249,37 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>DR-01</t>
+          <t>CM-10</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>存储单元(黑匣子)</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>结构与防护</t>
+          <t>帧格式</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>5.3.9</t>
+          <t>C.4.1 / C.6</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>检查结构；防护试验</t>
+          <t>抓包核对</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>独立可拆卸、金属外壳、≥IP54</t>
+          <t>串行链路：起止符 0x7E、1起始+8数据+1停止无校验、波特率优先 4800/9600/19200；CRC16 多项式 0xA001 低字节在前；CAN：2.0B 29 bit ID、波特率优先 5/10/20/50/100 Kbit/s</t>
         </is>
       </c>
       <c r="I84" s="2" t="n"/>
@@ -4294,17 +4294,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>DR-02</t>
+          <t>CM-11</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>存储单元(黑匣子)</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>全事件记录</t>
+          <t>地址与容量</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4314,17 +4314,17 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>B.1.1 ↔ B.2.2～B.2.5</t>
+          <t>C.3.2.2 / C.7.2.2</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>依次执行：报警+复位→开关机/复位/检查/调时→屏蔽→各类故障</t>
+          <t>配置地址边界值</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>全部事件被记录，每条含年月日时分秒；按时间序可导出；防篡改/防删除</t>
+          <t>主控节点地址=1；消防电气控制装置 2～63；0=广播；总数 ≤62</t>
         </is>
       </c>
       <c r="I85" s="2" t="n"/>
@@ -4339,17 +4339,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>DR-03</t>
+          <t>CM-12</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>存储单元(黑匣子)</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>容量与保存期</t>
+          <t>应答重发</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4359,17 +4359,17 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>B.1.2</t>
+          <t>C.3.3</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>灌满容量后继续写入；断电 14 d</t>
+          <t>屏蔽应答，观察重发</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>火警记录 ≥触发器件数×100、运行状态 ≥(触发器件+联动设备)×200；≥30 d 运行信息；超容量保持最新；首火警/火警/故障独立记录不被覆盖；断电数据保持 ≥14 d</t>
+          <t>1 s 未应答重发，≤3 次</t>
         </is>
       </c>
       <c r="I86" s="2" t="n"/>
@@ -4384,17 +4384,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>DR-04</t>
+          <t>CM-13</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>存储单元(黑匣子)</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>导出协议</t>
+          <t>建链流程</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4404,17 +4404,17 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>B.1.3 / 表 B.1～B.4</t>
+          <t>C.6</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>用专用工具经 USB 导出</t>
+          <t>冷启动/断线重连抓包</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>USB B 或 C 母口、USB 2.0 Device 模式；帧起止符 0x40、CRC16 0xA001、工具地址 0x7E、类型 0x7F、版本号 2；导出格式=存储格式；需授权</t>
+          <t>主机发功能码 44（查协议版本）→应答→发 41（查当前事件）→记录；中断重连同流程</t>
         </is>
       </c>
       <c r="I87" s="2" t="n"/>
@@ -4429,37 +4429,37 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>DR-05</t>
+          <t>CM-14</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>存储单元(黑匣子)</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>反压耐受</t>
+          <t>状态应答码</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>B.1.4.3 ↔ B.2.7</t>
+          <t>C.4.2.5</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>施加 120% 标称电压反向 1 min 后复测</t>
+          <t>构造 CRC 错、无效请求、地址不存在等异常帧</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>记录、存储、导出功能正常</t>
+          <t>应答码正确（1=CRC 错、2=无效服务、6=地址不存在、7=参数错误等）</t>
         </is>
       </c>
       <c r="I88" s="2" t="n"/>
@@ -4474,17 +4474,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>OP-01</t>
+          <t>CM-15</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>操作级别</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ 级边界</t>
+          <t>事件/类型代码表与装置状态显示</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4494,17 +4494,17 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>5.4.13 表1 / 5.4.14</t>
+          <t>表 C.16/C.17/C.18；6.4.13</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>不登录状态下逐项尝试全部操作</t>
+          <t>对照抓包中设备类型、事件类型、状态位；将连接的消防电气控制装置分别置于手动/自动状态</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>仅查询/消音/检查/信息确认/联动启动可用（O 项按产品定义）；复位、手动启动、屏蔽、手自动转换等全部拒绝</t>
+          <t>与代码表一致（如 2=首火警、3=火警、19=启动、26=反馈、122=复位；状态 bit0=手/自动等）；电气控制装置的手/自动状态在本机正确显示（6.4.13）</t>
         </is>
       </c>
       <c r="I89" s="2" t="n"/>
@@ -4519,37 +4519,37 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>OP-02</t>
+          <t>CM-16</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>操作级别</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ 级边界</t>
+          <t>通信线独立性</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0（设计检查）</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>5.4.13 表1 / 5.4.14</t>
+          <t>5.3.1.6</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Ⅱ 级钥匙/密码登录逐项尝试</t>
+          <t>检查布线设计</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>复位、手动直接启动输出、自检、调时、主备电操作、手自动转换可用；输入/更改数据、分区编程、延时设置拒绝</t>
+          <t>FECbus 独立通信线路，不与报警总线/联动总线共用</t>
         </is>
       </c>
       <c r="I90" s="2" t="n"/>
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>OP-03</t>
+          <t>CM-17</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>操作级别</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 级边界与密钥单向性</t>
+          <t>通信线冗余</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4584,17 +4584,17 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>5.4.13 表1 / 5.4.14</t>
+          <t>C.3.2.3</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 级登录逐项尝试；用 Ⅱ 级密钥尝试进 Ⅲ 级</t>
+          <t>通信线任一点断路/短路</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>编程/延时设置/数据修改可用；软硬件修改、数据导出回放、调试状态拒绝；Ⅲ 级钥匙可进 Ⅱ 级，Ⅱ 级钥匙不能进 Ⅲ 级</t>
+          <t>控制器与消防电气控制装置仍能正常通信</t>
         </is>
       </c>
       <c r="I91" s="2" t="n"/>
@@ -4609,37 +4609,37 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>OP-04</t>
+          <t>DR-01</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>操作级别</t>
+          <t>存储单元(黑匣子)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Ⅳ 级隔离</t>
+          <t>结构与防护</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>5.4.13 表1 / 5.4.14</t>
+          <t>5.3.9</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>尝试从控制器本机修改软硬件/导出数据/进调试</t>
+          <t>检查结构；防护试验</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Ⅳ 级操作不能通过控制器本身进行</t>
+          <t>独立可拆卸、金属外壳、≥IP54</t>
         </is>
       </c>
       <c r="I92" s="2" t="n"/>
@@ -4654,17 +4654,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>OP-05</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>操作级别</t>
+          <t>存储单元(黑匣子)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>调试功能</t>
+          <t>全事件记录</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>5.4.13 表1 / 5.4.14</t>
+          <t>B.1.1 ↔ B.2.2～B.2.5</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>5.4.14：接入调试设备，触发火警与故障</t>
+          <t>依次执行：报警+复位→开关机/复位/检查/调时→屏蔽→各类故障</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>进入调试状态；可收火警/故障信息但不启动联动控制输出；调试态与正常态可区分，传出信息有区别标识</t>
+          <t>全部事件被记录，每条含年月日时分秒；按时间序可导出；防篡改/防删除</t>
         </is>
       </c>
       <c r="I93" s="2" t="n"/>
@@ -4699,17 +4699,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>UI-01</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>存储单元(黑匣子)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>历史记录查询</t>
+          <t>容量与保存期</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>关联 DR-02/FA-11</t>
+          <t>B.1.2</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>进入查询→历史记录；翻页浏览；断电重启后再查</t>
+          <t>灌满容量后继续写入；断电 14 d</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>事件按时间序列出（火警/故障/操作各类），内容与黑匣子一致；断电重启后记录仍在</t>
+          <t>火警记录 ≥触发器件数×100、运行状态 ≥(触发器件+联动设备)×200；≥30 d 运行信息；超容量保持最新；首火警/火警/故障独立记录不被覆盖；断电数据保持 ≥14 d</t>
         </is>
       </c>
       <c r="I94" s="2" t="n"/>
@@ -4744,17 +4744,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>UI-02</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>存储单元(黑匣子)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>控制器信息</t>
+          <t>导出协议</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4764,17 +4764,17 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>第 8 章标志</t>
+          <t>B.1.3 / 表 B.1～B.4</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>查看型号/软件版本/容量/地址</t>
+          <t>用专用工具经 USB 导出</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>与铭牌、说明书声明一致（软件版本号须与标志一致）</t>
+          <t>USB B 或 C 母口、USB 2.0 Device 模式；帧起止符 0x40、CRC16 0xA001、工具地址 0x7E、类型 0x7F、版本号 2；导出格式=存储格式；需授权</t>
         </is>
       </c>
       <c r="I95" s="2" t="n"/>
@@ -4789,37 +4789,37 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>UI-03</t>
+          <t>DR-05</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>存储单元(黑匣子)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>设备总览</t>
+          <t>反压耐受</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B.1.4.3 ↔ B.2.7</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>列出点表全部设备</t>
+          <t>施加 120% 标称电压反向 1 min 后复测</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>设备数与点表一致；在线/报警/故障/屏蔽状态实时准确</t>
+          <t>记录、存储、导出功能正常</t>
         </is>
       </c>
       <c r="I96" s="2" t="n"/>
@@ -4834,17 +4834,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>UI-04</t>
+          <t>OP-01</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>操作级别</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>单点查询</t>
+          <t>Ⅰ 级边界</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4854,17 +4854,17 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>关联 FA-12</t>
+          <t>5.4.13 表1 / 5.4.14</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>选任一部位查看详情</t>
+          <t>不登录状态下逐项尝试全部操作</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>类型/状态/注释准确；若支持阈值调节则显示当前设定值（设置界面外可查）</t>
+          <t>仅查询/消音/检查/信息确认/联动启动可用（O 项按产品定义）；复位、手动启动、屏蔽、手自动转换等全部拒绝</t>
         </is>
       </c>
       <c r="I97" s="2" t="n"/>
@@ -4879,37 +4879,37 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>UI-05</t>
+          <t>OP-02</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>操作级别</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>级联从机</t>
+          <t>Ⅱ 级边界</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>△形态</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>5.4.8</t>
+          <t>5.4.13 表1 / 5.4.14</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>组网信息显示</t>
+          <t>Ⅱ 级钥匙/密码登录逐项尝试</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>独立型形态下应显示"无从机/未组网"；做组网时随 6.10 用例组补充</t>
+          <t>复位、手动直接启动输出、自检、调时、主备电操作、手自动转换可用；输入/更改数据、分区编程、延时设置拒绝</t>
         </is>
       </c>
       <c r="I98" s="2" t="n"/>
@@ -4924,17 +4924,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>UI-06</t>
+          <t>OP-03</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>操作级别</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>检查信息</t>
+          <t>Ⅲ 级边界与密钥单向性</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4944,17 +4944,17 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>关联 CK-01</t>
+          <t>5.4.13 表1 / 5.4.14</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>菜单入口进入检查功能</t>
+          <t>Ⅲ 级登录逐项尝试；用 Ⅱ 级密钥尝试进 Ⅲ 级</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>四总数（设计/正常/故障/屏蔽）正确；入口不受操作级别限制（5.4.9.1 豁免同样适用于菜单路径）</t>
+          <t>编程/延时设置/数据修改可用；软硬件修改、数据导出回放、调试状态拒绝；Ⅲ 级钥匙可进 Ⅱ 级，Ⅱ 级钥匙不能进 Ⅲ 级</t>
         </is>
       </c>
       <c r="I99" s="2" t="n"/>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>UI-07</t>
+          <t>OP-04</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>操作级别</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>节点设备监控</t>
+          <t>Ⅳ 级隔离</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.4.13 表1 / 5.4.14</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>实时监视页面开着，使某设备状态变化（报警/故障/恢复）</t>
+          <t>尝试从控制器本机修改软硬件/导出数据/进调试</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>页面刷新及时反映，且监视页面开着不影响报警声光与联动（任何界面停留都不阻断报警，FA-13 语义）</t>
+          <t>Ⅳ 级操作不能通过控制器本身进行</t>
         </is>
       </c>
       <c r="I100" s="2" t="n"/>
@@ -5014,17 +5014,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>UI-08</t>
+          <t>OP-05</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>人机菜单(产品级)</t>
+          <t>操作级别</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>通讯成功率</t>
+          <t>调试功能</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>企标特色·关联 FT-11</t>
+          <t>5.4.13 表1 / 5.4.14</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>查看总线通信统计；用线间并电阻制造误码</t>
+          <t>5.4.14：接入调试设备，触发火警与故障</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>正常时成功率稳定；制造干扰后数值可观察地下降（该页是判断 d) 类隐患的运维工具）</t>
+          <t>进入调试状态；可收火警/故障信息但不启动联动控制输出；调试态与正常态可区分，传出信息有区别标识</t>
         </is>
       </c>
       <c r="I101" s="2" t="n"/>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>UI-09</t>
+          <t>UI-01</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>机内设备监控</t>
+          <t>历史记录查询</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5079,17 +5079,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>关联 PW-07</t>
+          <t>关联 DR-02/FA-11</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>查看主/备电电压、备电电量、充电状态</t>
+          <t>进入查询→历史记录；翻页浏览；断电重启后再查</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>与万用表实测一致（容差内）；备电分段电压可见</t>
+          <t>事件按时间序列出（火警/故障/操作各类），内容与黑匣子一致；断电重启后记录仍在</t>
         </is>
       </c>
       <c r="I102" s="2" t="n"/>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>UI-10</t>
+          <t>UI-02</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>启停控制</t>
+          <t>控制器信息</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>表 1 第 8 项</t>
+          <t>第 8 章标志</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ 级态尝试菜单启停某设备；Ⅱ 级登录后再操作</t>
+          <t>查看型号/软件版本/容量/地址</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Ⅰ 级被拦；Ⅱ 级可启停，动作与黑匣子记录一致</t>
+          <t>与铭牌、说明书声明一致（软件版本号须与标志一致）</t>
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>UI-11</t>
+          <t>UI-03</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>屏蔽控制</t>
+          <t>设备总览</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>关联 SH-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>菜单路径执行屏蔽/解除</t>
+          <t>列出点表全部设备</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>权限、每次 1 只、报警/故障中不可屏——SH-01 全部判据经菜单路径同样成立</t>
+          <t>设备数与点表一致；在线/报警/故障/屏蔽状态实时准确</t>
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>UI-12</t>
+          <t>UI-04</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>用户登陆</t>
+          <t>单点查询</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>关联 OP-01/02</t>
+          <t>关联 FA-12</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>正确/错误密码各试；登录后放置超时</t>
+          <t>选任一部位查看详情</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>正确密码升级并显示当前级别（屏上"一级"图标变化）；错误拒绝；超时自动回落 Ⅰ 级</t>
+          <t>类型/状态/注释准确；若支持阈值调节则显示当前设定值（设置界面外可查）</t>
         </is>
       </c>
       <c r="I105" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>UI-13</t>
+          <t>UI-05</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5249,27 +5249,27 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>密码设置</t>
+          <t>级联从机</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>△形态</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>关联 OP-03</t>
+          <t>5.4.8</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 级改各级密码；Ⅱ 级尝试改 Ⅲ 级密码</t>
+          <t>组网信息显示</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 可改；Ⅱ 改 Ⅲ 被拦（密钥单向性）；修改事件进黑匣子</t>
+          <t>独立型形态下应显示"无从机/未组网"；做组网时随 6.10 用例组补充</t>
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>UI-14</t>
+          <t>UI-06</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>基础设置·时钟</t>
+          <t>检查信息</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>关联 FA-11</t>
+          <t>关联 CK-01</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>调整时钟</t>
+          <t>菜单入口进入检查功能</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>生效；黑匣子记录"调整时钟"事件（代码 131）；调后日误差仍 ≤6 s</t>
+          <t>四总数（设计/正常/故障/屏蔽）正确；入口不受操作级别限制（5.4.9.1 豁免同样适用于菜单路径）</t>
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>UI-15</t>
+          <t>UI-07</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>联网设置</t>
+          <t>节点设备监控</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5349,17 +5349,17 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>关联 CM-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>配置 CRT 通信参数</t>
+          <t>实时监视页面开着，使某设备状态变化（报警/故障/恢复）</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>参数生效可重连；以太网口防外网侵入措施在位</t>
+          <t>页面刷新及时反映，且监视页面开着不影响报警声光与联动（任何界面停留都不阻断报警，FA-13 语义）</t>
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>UI-16</t>
+          <t>UI-08</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>节点设置（点表编辑）</t>
+          <t>通讯成功率</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5394,17 +5394,17 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>关联 WD-03</t>
+          <t>企标特色·关联 FT-11</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 级编辑部位注释/类型/确认方式；编辑中途使真火警发生</t>
+          <t>查看总线通信统计；用线间并电阻制造误码</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>编辑缓冲与运行配置分离、确认后原子生效；编辑过程中报警照常（输入不阻断报警）</t>
+          <t>正常时成功率稳定；制造干扰后数值可观察地下降（该页是判断 d) 类隐患的运维工具）</t>
         </is>
       </c>
       <c r="I109" s="2" t="n"/>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>UI-17</t>
+          <t>UI-09</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5429,27 +5429,27 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>操作模式设置</t>
+          <t>机内设备监控</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>⚠审查</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>LC-03 红线</t>
+          <t>关联 PW-07</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>先确认该菜单含义</t>
+          <t>查看主/备电电压、备电电量、充电状态</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>若含手/自动切换：不合规——5.4.2.2 强制自复位钥匙开关，菜单软切换不满足；若仅为显示/声音模式设置则按 P1 正常测</t>
+          <t>与万用表实测一致（容差内）；备电分段电压可见</t>
         </is>
       </c>
       <c r="I110" s="2" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>UI-18</t>
+          <t>UI-10</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>点位注册</t>
+          <t>启停控制</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5484,17 +5484,17 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>表 1 第 8 项</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>注册新总线设备；故意注册重复地址</t>
+          <t>Ⅰ 级态尝试菜单启停某设备；Ⅱ 级登录后再操作</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>正常注册入表；重复地址被检出拒绝</t>
+          <t>Ⅰ 级被拦；Ⅱ 级可启停，动作与黑匣子记录一致</t>
         </is>
       </c>
       <c r="I111" s="2" t="n"/>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>UI-19</t>
+          <t>UI-11</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>配置导入</t>
+          <t>屏蔽控制</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5529,17 +5529,17 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>关联 WD-03</t>
+          <t>关联 SH-01</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>导入合法配置；导入中断电；导入损坏文件</t>
+          <t>菜单路径执行屏蔽/解除</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>导入前校验（版本/CRC）；原子生效——中断/损坏则完整回滚到旧配置，绝无半套配置；导入事件进黑匣子</t>
+          <t>权限、每次 1 只、报警/故障中不可屏——SH-01 全部判据经菜单路径同样成立</t>
         </is>
       </c>
       <c r="I112" s="2" t="n"/>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>UI-20</t>
+          <t>UI-12</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>联动编程</t>
+          <t>用户登陆</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>关联联动逻辑</t>
+          <t>关联 OP-01/02</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Ⅲ 级编辑与/或逻辑；未按确认前触发火警</t>
+          <t>正确/错误密码各试；登录后放置超时</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>未确认的编辑不生效（旧逻辑照常联动）；确认后新逻辑生效并记录</t>
+          <t>正确密码升级并显示当前级别（屏上"一级"图标变化）；错误拒绝；超时自动回落 Ⅰ 级</t>
         </is>
       </c>
       <c r="I113" s="2" t="n"/>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>UI-21</t>
+          <t>UI-13</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5609,27 +5609,27 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>调试助手 / 直控调试</t>
+          <t>密码设置</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>⚠审查</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>关联 OP-05 / 表 1 第 19 项</t>
+          <t>关联 OP-03</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>进入调试功能收发信号</t>
+          <t>Ⅲ 级改各级密码；Ⅱ 级尝试改 Ⅲ 级密码</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>调试态边界：可收火警/故障、不启动真实联动输出、状态可区分；⚠权限审查：表 1"进入调试状态"属 Ⅳ 级（不能经本机），屏上标注"调试：调试员"的权限设计需与认证口径核对</t>
+          <t>Ⅲ 可改；Ⅱ 改 Ⅲ 被拦（密钥单向性）；修改事件进黑匣子</t>
         </is>
       </c>
       <c r="I114" s="2" t="n"/>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>UI-22</t>
+          <t>UI-14</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>联网注册</t>
+          <t>基础设置·时钟</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>关联 CM 组</t>
+          <t>关联 FA-11</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>向 CRT/上级注册</t>
+          <t>调整时钟</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>注册流程完成，对端可见本机</t>
+          <t>生效；黑匣子记录"调整时钟"事件（代码 131）；调后日误差仍 ≤6 s</t>
         </is>
       </c>
       <c r="I115" s="2" t="n"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>UI-23</t>
+          <t>UI-15</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5699,27 +5699,27 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>固件升级</t>
+          <t>联网设置</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>⚠审查</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>表 1 第 17 项</t>
+          <t>关联 CM-01</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>审查升级路径设计</t>
+          <t>配置 CRT 通信参数</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>⚠"修改软硬件"属 Ⅳ 级、不能通过控制器本身进行——菜单入口必须强制依赖外部专用手段（专用上位机/签名固件+专用工具），裸菜单升级不合规；升级前后版本进黑匣子；升级失败可回滚</t>
+          <t>参数生效可重连；以太网口防外网侵入措施在位</t>
         </is>
       </c>
       <c r="I116" s="2" t="n"/>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>UI-24</t>
+          <t>UI-16</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>记录导出</t>
+          <t>节点设置（点表编辑）</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5754,17 +5754,17 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>关联 DR-04</t>
+          <t>关联 WD-03</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>经 USB 导出运行记录</t>
+          <t>Ⅲ 级编辑部位注释/类型/确认方式；编辑中途使真火警发生</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>附录 B 口径：专用工具+授权、B/C 型母口 Device 模式；导出不影响记录本体；导出行为进黑匣子</t>
+          <t>编辑缓冲与运行配置分离、确认后原子生效；编辑过程中报警照常（输入不阻断报警）</t>
         </is>
       </c>
       <c r="I117" s="2" t="n"/>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>UI-25</t>
+          <t>UI-17</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5789,27 +5789,27 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>恢复出厂设置</t>
+          <t>操作模式设置</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>B.1.1.3</t>
+          <t>LC-03 红线</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>高权限+二次确认执行；恢复后检查记录</t>
+          <t>先确认该菜单含义</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>清运行配置；不得清除运行记录/黑匣子（防删除是附录 B 硬要求——恢复出厂也不许抹历史）；恢复操作本身进黑匣子；恢复后设备按说明书声明状态启动</t>
+          <t>若含手/自动切换：不合规——5.4.2.2 强制自复位钥匙开关，菜单软切换不满足；若仅为显示/声音模式设置则按 P1 正常测</t>
         </is>
       </c>
       <c r="I118" s="2" t="n"/>
@@ -5824,37 +5824,37 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>GE-01</t>
+          <t>UI-18</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>禁止直收触发器件</t>
+          <t>点位注册</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P0（设计红线）</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>4.3.1.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>设计检查 + 尝试将探测器/手报直接接入</t>
+          <t>注册新总线设备；故意注册重复地址</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
+          <t>正常注册入表；重复地址被检出拒绝</t>
         </is>
       </c>
       <c r="I119" s="2" t="n"/>
@@ -5869,37 +5869,37 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>GE-02</t>
+          <t>UI-19</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>启动控制全流程</t>
+          <t>配置导入</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 ↔ 5.3.1</t>
+          <t>关联 WD-03</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间</t>
+          <t>导入合法配置；导入中断电；导入损坏文件</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>① 发出启动声光并记录时间（声可消，再有启动信号可再启动）；② 启动声光警报器；③ 进入延时：延时光指示+显示延时时间和保护区域+关闭防火门窗/防火阀+停通风空调；④ 延时结束发启动喷洒控制信号+光指示+启动喷洒光警报器；⑤ 喷洒阶段发出相应声光保持至复位并记录时间</t>
+          <t>导入前校验（版本/CRC）；原子生效——中断/损坏则完整回滚到旧配置，绝无半套配置；导入事件进黑匣子</t>
         </is>
       </c>
       <c r="I120" s="2" t="n"/>
@@ -5914,37 +5914,37 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>GE-03</t>
+          <t>UI-20</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>延时设置与手动中止</t>
+          <t>联动编程</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.3 ↔ 5.3.1</t>
+          <t>关联联动逻辑</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>调整延时值；延时期间执行手动停止</t>
+          <t>Ⅲ 级编辑与/或逻辑；未按确认前触发火警</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>延时 0～30 s 可调；延时期间能手动停止后续动作</t>
+          <t>未确认的编辑不生效（旧逻辑照常联动）；确认后新逻辑生效并记录</t>
         </is>
       </c>
       <c r="I121" s="2" t="n"/>
@@ -5959,37 +5959,37 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>GE-04</t>
+          <t>UI-21</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>手/自动与优先级</t>
+          <t>调试助手 / 直控调试</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4 ↔ 5.3.1</t>
+          <t>关联 OP-05 / 表 1 第 19 项</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
+          <t>进入调试功能收发信号</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>有控制状态指示，状态不受复位影响；自动下手动插入优先；手动停止后再有启动信号仍按预置逻辑工作</t>
+          <t>调试态边界：可收火警/故障、不启动真实联动输出、状态可区分；⚠权限审查：表 1"进入调试状态"属 Ⅳ 级（不能经本机），屏上标注"调试：调试员"的权限设计需与认证口径核对</t>
         </is>
       </c>
       <c r="I122" s="2" t="n"/>
@@ -6004,17 +6004,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>GE-05</t>
+          <t>UI-22</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>声信号优先级</t>
+          <t>联网注册</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.5 ↔ 5.3.1</t>
+          <t>关联 CM 组</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>使喷洒声、启动声、故障声两两同时存在</t>
+          <t>向 CRT/上级注册</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
+          <t>注册流程完成，对端可见本机</t>
         </is>
       </c>
       <c r="I123" s="2" t="n"/>
@@ -6049,37 +6049,37 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>GE-06</t>
+          <t>UI-23</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>接收联动信号</t>
+          <t>固件升级</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>⚠审查</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.6</t>
+          <t>表 1 第 17 项</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>消防联动控制器下发联动信号</t>
+          <t>审查升级路径设计</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>正确接收并按逻辑执行</t>
+          <t>⚠"修改软硬件"属 Ⅳ 级、不能通过控制器本身进行——菜单入口必须强制依赖外部专用手段（专用上位机/签名固件+专用工具），裸菜单升级不合规；升级前后版本进黑匣子；升级失败可回滚</t>
         </is>
       </c>
       <c r="I124" s="2" t="n"/>
@@ -6094,17 +6094,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>GE-07</t>
+          <t>UI-24</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>分区警报器与分区指示</t>
+          <t>记录导出</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6114,17 +6114,17 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
+          <t>关联 DR-04</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>逐区启动/停止声光警报器</t>
+          <t>经 USB 导出运行记录</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>可分区启动和停止保护区域声光警报器；每个保护区域有独立工作状态指示灯</t>
+          <t>附录 B 口径：专用工具+授权、B/C 型母口 Device 模式；导出不影响记录本体；导出行为进黑匣子</t>
         </is>
       </c>
       <c r="I125" s="2" t="n"/>
@@ -6139,37 +6139,37 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>GE-08</t>
+          <t>UI-25</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>向联动控制器上报</t>
+          <t>恢复出厂设置</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9 ↔ 5.3.1</t>
+          <t>B.1.1.3</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>触发各阶段，在联动控制器（或模拟器）端核对</t>
+          <t>高权限+二次确认执行；恢复后检查记录</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>能发送：启动控制信号、延时信号、启动喷洒控制信号、气体喷洒信号、故障信号、选择阀和瓶头阀动作信息</t>
+          <t>清运行配置；不得清除运行记录/黑匣子（防删除是附录 B 硬要求——恢复出厂也不许抹历史）；恢复操作本身进黑匣子；恢复后设备按说明书声明状态启动</t>
         </is>
       </c>
       <c r="I126" s="2" t="n"/>
@@ -6184,37 +6184,37 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>GE-09</t>
+          <t>UI-26</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>复位与状态重建</t>
+          <t>检查页右上角返回按钮</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.11 ↔ 5.3.1</t>
+          <t>导航约定</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>启动保持状态下手动复位，计时</t>
+          <t>在检查页点击右上角按钮</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>设复位按键；复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
+          <t>应为返回图标并返回上级页面（主页）；不应是菜单按钮/跳转信息显示页</t>
         </is>
       </c>
       <c r="I127" s="2" t="n"/>
@@ -6229,17 +6229,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>GE-10</t>
+          <t>UI-27</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>计时精度</t>
+          <t>信息显示页右上角返回按钮</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6249,17 +6249,17 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12 ↔ 5.3.1</t>
+          <t>导航约定</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>连续运行 24 h 比对</t>
+          <t>在信息显示页点击右上角按钮</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>日计时误差 ≤30 s；打印含月日时分，不能仅用打印机记录</t>
+          <t>应为返回图标并返回上级页面；导航通则：各二级页面右上角统一为返回上级</t>
         </is>
       </c>
       <c r="I128" s="2" t="n"/>
@@ -6274,17 +6274,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>GE-11</t>
+          <t>UI-28</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>输出特性</t>
+          <t>信息显示时间格式</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.10 ↔ 5.3.1</t>
+          <t>5.4.1.11</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>测输出接点电压/电流/容量</t>
+          <t>查看事件列表时间列</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>满足制造商规定</t>
+          <t>须含年月日时分秒（实机当前"01月02日 00:20:58"缺年份，不满足）；同时时钟应校准（UI-14）</t>
         </is>
       </c>
       <c r="I129" s="2" t="n"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>GE-12</t>
+          <t>GE-01</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6329,27 +6329,27 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>故障报警（部位/类型）</t>
+          <t>禁止直收触发器件</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P0（设计红线）</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
+          <t>4.3.1.2</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
+          <t>设计检查 + 尝试将探测器/手报直接接入</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>≤100 s 故障声光（声可消可再启动，光保持至排除）；a)/b) 指示部位；c)/d)/e) 指示类型；故障指示灯点亮</t>
+          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
         </is>
       </c>
       <c r="I130" s="2" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>GE-13</t>
+          <t>GE-02</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6374,27 +6374,27 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>阶段×故障双向互检</t>
+          <t>启动控制全流程</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.2.2 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
+          <t>分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>① 各阶段中故障均正常显示且不打断当前流程；② 故障先存在时，流程照常推进且故障指示灯全程保持</t>
+          <t>① 发出启动声光并记录时间（声可消，再有启动信号可再启动）；② 启动声光警报器；③ 进入延时：延时光指示+显示延时时间和保护区域+关闭防火门窗/防火阀+停通风空调；④ 延时结束发启动喷洒控制信号+光指示+启动喷洒光警报器；⑤ 喷洒阶段发出相应声光保持至复位并记录时间</t>
         </is>
       </c>
       <c r="I131" s="2" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>GE-14</t>
+          <t>GE-03</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>故障复位复显与清空</t>
+          <t>延时设置与手动中止</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
+          <t>4.3.2.3 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
+          <t>调整延时值；延时期间执行手动停止</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>① 尚存故障 ≤100 s 重新显示；② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
+          <t>延时 0～30 s 可调；延时期间能手动停止后续动作</t>
         </is>
       </c>
       <c r="I132" s="2" t="n"/>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>GE-15</t>
+          <t>GE-04</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>自检不动作输出</t>
+          <t>手/自动与优先级</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6474,17 +6474,17 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.1 ↔ 5.3.3</t>
+          <t>4.3.2.4 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
+          <t>切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>自检期间受控设备与输出接点均不动作；超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
+          <t>有控制状态指示，状态不受复位影响；自动下手动插入优先；手动停止后再有启动信号仍按预置逻辑工作</t>
         </is>
       </c>
       <c r="I133" s="2" t="n"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>GE-16</t>
+          <t>GE-05</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6509,27 +6509,27 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>面板自检</t>
+          <t>声信号优先级</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.2 ↔ 5.3.3</t>
+          <t>4.3.2.5 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>手动检查音响、指示灯、显示器</t>
+          <t>使喷洒声、启动声、故障声两两同时存在</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>全部可手动检查</t>
+          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
         </is>
       </c>
       <c r="I134" s="2" t="n"/>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>GE-17</t>
+          <t>GE-06</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>主备电转换</t>
+          <t>接收联动信号</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6564,17 +6564,17 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>4.3.2.6</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>断主电/恢复主电</t>
+          <t>消防联动控制器下发联动信号</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>自动转换、状态指示、主电过流保护、转换不误动作</t>
+          <t>正确接收并按逻辑执行</t>
         </is>
       </c>
       <c r="I135" s="2" t="n"/>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>GE-18</t>
+          <t>GE-07</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6599,27 +6599,27 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>备电容量</t>
+          <t>分区警报器与分区指示</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
+          <t>逐区启动/停止声光警报器</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>全程正常工作</t>
+          <t>可分区启动和停止保护区域声光警报器；每个保护区域有独立工作状态指示灯</t>
         </is>
       </c>
       <c r="I136" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>GE-19</t>
+          <t>GE-08</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>电压容限</t>
+          <t>向联动控制器上报</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.2 ↔ 5.3.4</t>
+          <t>4.3.2.9 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
+          <t>触发各阶段，在联动控制器（或模拟器）端核对</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>全范围正常工作</t>
+          <t>能发送：启动控制信号、延时信号、启动喷洒控制信号、气体喷洒信号、故障信号、选择阀和瓶头阀动作信息</t>
         </is>
       </c>
       <c r="I137" s="2" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>GE-20</t>
+          <t>GE-09</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6689,27 +6689,27 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>现场数据断电保存</t>
+          <t>复位与状态重建</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.2.4 b)</t>
+          <t>4.3.2.11 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>断电 14 d 后上电检查现场设置数据</t>
+          <t>启动保持状态下手动复位，计时</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
+          <t>设复位按键；复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
         </is>
       </c>
       <c r="I138" s="2" t="n"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>GE-21</t>
+          <t>GE-10</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>数据输入防意外执行</t>
+          <t>计时精度</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6744,17 +6744,17 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.1.3</t>
+          <t>4.3.2.12 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>各状态下输入数据</t>
+          <t>连续运行 24 h 比对</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>不引起程序意外执行</t>
+          <t>日计时误差 ≤30 s；打印含月日时分，不能仅用打印机记录</t>
         </is>
       </c>
       <c r="I139" s="2" t="n"/>
@@ -6769,17 +6769,17 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>EX-01</t>
+          <t>GE-11</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>外观与包装</t>
+          <t>输出特性</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6789,17 +6789,17 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>完整包装、产品标志、合格标志、说明书；无腐蚀/脱漆/划伤/毛刺；紧固无松动</t>
+          <t>4.3.2.10 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>测输出接点电压/电流/容量</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>满足制造商规定</t>
         </is>
       </c>
       <c r="I140" s="2" t="n"/>
@@ -6814,37 +6814,37 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>EX-02</t>
+          <t>GE-12</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>供电与接地</t>
+          <t>故障报警（部位/类型）</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>主电 AC 220 V/50 Hz；保护接地；部件供电优先 DC 24 V；电源线独立接线端子</t>
+          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
+          <t>≤100 s 故障声光（声可消可再启动，光保持至排除）；a)/b) 指示部位；c)/d)/e) 指示类型；故障指示灯点亮</t>
         </is>
       </c>
       <c r="I141" s="2" t="n"/>
@@ -6859,17 +6859,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>EX-03</t>
+          <t>GE-13</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>按键与面板（报警控制器）</t>
+          <t>阶段×故障双向互检</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6879,17 +6879,17 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm；指示灯/按键按标准图 1/图 2 顺序排列；中文标注；按键有提示音</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.5/5.3.8</t>
+          <t>① 各阶段中故障均正常显示且不打断当前流程；② 故障先存在时，流程照常推进且故障指示灯全程保持</t>
         </is>
       </c>
       <c r="I142" s="2" t="n"/>
@@ -6904,37 +6904,37 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>EX-04</t>
+          <t>GE-14</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>指示灯颜色</t>
+          <t>故障复位复显与清空</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止（GB 4717 5.3.2.1）。气灭控制器：红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电（GB 16806 4.1.3.2.1）</t>
+          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>① 尚存故障 ≤100 s 重新显示；② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
         </is>
       </c>
       <c r="I143" s="2" t="n"/>
@@ -6949,37 +6949,37 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>EX-05</t>
+          <t>GE-15</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>指示灯可见性与闪动参数</t>
+          <t>自检不动作输出</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：100～500 lx、22.5°，0.8 m/3 m（GB 4717 5.3.2.2）。气灭控制器：5～500 lx、22.5°、3 m；闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz；一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮（GB 16806 4.1.3.2）</t>
+          <t>4.3.4.1 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>自检期间受控设备与输出接点均不动作；超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
         </is>
       </c>
       <c r="I144" s="2" t="n"/>
@@ -6994,37 +6994,37 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>EX-06</t>
+          <t>GE-16</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>外壳防护与燃烧（报警控制器）</t>
+          <t>面板自检</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>≥IP30；非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
+          <t>4.3.4.2 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>手动检查音响、指示灯、显示器</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.8/5.3.1.9</t>
+          <t>全部可手动检查</t>
         </is>
       </c>
       <c r="I145" s="2" t="n"/>
@@ -7039,37 +7039,37 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>EX-07</t>
+          <t>GE-17</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>音响器件</t>
+          <t>主备电转换</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>报警控制器：1 m 处 65～105 dB(A)、接线防脱耐 50 N（GB 4717 5.3.4）。气灭控制器：1 m 处 &gt;65 且 &lt;115 dB(A)（GB 16806 4.1.3.4.1）。两者：85% 额定电压下正常发声</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>断主电/恢复主电</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>两标准分列</t>
+          <t>自动转换、状态指示、主电过流保护、转换不误动作</t>
         </is>
       </c>
       <c r="I146" s="2" t="n"/>
@@ -7084,37 +7084,37 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>EX-08</t>
+          <t>GE-18</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>过负荷/熔断器</t>
+          <t>备电容量</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）；参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+          <t>全程正常工作</t>
         </is>
       </c>
       <c r="I147" s="2" t="n"/>
@@ -7129,37 +7129,37 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>EX-09</t>
+          <t>GE-19</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>端子与导线</t>
+          <t>电压容限</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>端子编号清晰；电池正极红线、负极黑/蓝线；（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
+          <t>4.3.5.2 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
+          <t>全范围正常工作</t>
         </is>
       </c>
       <c r="I148" s="2" t="n"/>
@@ -7174,17 +7174,17 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>EX-10</t>
+          <t>GE-20</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>元件温升（气灭控制器）</t>
+          <t>现场数据断电保存</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7194,17 +7194,17 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>主要元件温升 ≤60℃；变压器等表面 ≤90℃（25±3℃）；电池周围 ≤45℃</t>
+          <t>4.1.5.2.4 b)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>断电 14 d 后上电检查现场设置数据</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
         </is>
       </c>
       <c r="I149" s="2" t="n"/>
@@ -7219,17 +7219,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>GE-21</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>软件资料</t>
+          <t>数据输入防意外执行</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7239,17 +7239,17 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号；程序存于不易丢失存储器；软件防非专门人员改动</t>
+          <t>4.1.5.1.3</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>（外观/设计检查项）</t>
+          <t>各状态下输入数据</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>不引起程序意外执行</t>
         </is>
       </c>
       <c r="I150" s="2" t="n"/>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>EX-01</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>产品标志</t>
+          <t>外观与包装</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
+          <t>完整包装、产品标志、合格标志、说明书；无腐蚀/脱漆/划伤/毛刺；紧固无松动</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 8；GB 16806 7</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="I151" s="2" t="n"/>
@@ -7309,37 +7309,37 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>TT-01</t>
+          <t>EX-02</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>绝缘电阻</t>
+          <t>供电与接地</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>主电 AC 220 V/50 Hz；保护接地；部件供电优先 DC 24 V；电源线独立接线端子</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
+          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
         </is>
       </c>
       <c r="I152" s="2" t="n"/>
@@ -7354,37 +7354,37 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>TT-02</t>
+          <t>EX-03</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>泄漏电流</t>
+          <t>按键与面板（报警控制器）</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm；指示灯/按键按标准图 1/图 2 顺序排列；中文标注；按键有提示音</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>同左（5.14）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
+          <t>GB 4717 5.3.1.5/5.3.8</t>
         </is>
       </c>
       <c r="I153" s="2" t="n"/>
@@ -7399,37 +7399,37 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>TT-03</t>
+          <t>EX-04</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>电气强度</t>
+          <t>指示灯颜色</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>报警控制器：红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止（GB 4717 5.3.2.1）。气灭控制器：红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电（GB 16806 4.1.3.2.1）</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.15，不做</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
+          <t>两标准分列</t>
         </is>
       </c>
       <c r="I154" s="2" t="n"/>
@@ -7444,37 +7444,37 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>TT-04</t>
+          <t>EX-05</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>射频电磁场辐射</t>
+          <t>指示灯可见性与闪动参数</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>报警控制器：100～500 lx、22.5°，0.8 m/3 m（GB 4717 5.3.2.2）。气灭控制器：5～500 lx、22.5°、3 m；闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz；一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮（GB 16806 4.1.3.2）</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.16）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
+          <t>两标准分列</t>
         </is>
       </c>
       <c r="I155" s="2" t="n"/>
@@ -7489,37 +7489,37 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>TT-05</t>
+          <t>EX-06</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>射频传导骚扰</t>
+          <t>外壳防护与燃烧（报警控制器）</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>≥IP30；非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>140 dBμV、0.15～100 MHz（5.17）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：140 dBμV、0.15～80 MHz（6.20）</t>
+          <t>GB 4717 5.3.1.8/5.3.1.9</t>
         </is>
       </c>
       <c r="I156" s="2" t="n"/>
@@ -7534,37 +7534,37 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>TT-06</t>
+          <t>EX-07</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>静电放电</t>
+          <t>音响器件</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>报警控制器：1 m 处 65～105 dB(A)、接线防脱耐 50 N（GB 4717 5.3.4）。气灭控制器：1 m 处 &gt;65 且 &lt;115 dB(A)（GB 16806 4.1.3.4.1）。两者：85% 额定电压下正常发声</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.18）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
+          <t>两标准分列</t>
         </is>
       </c>
       <c r="I157" s="2" t="n"/>
@@ -7579,37 +7579,37 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>TT-07</t>
+          <t>EX-08</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>电快速瞬变</t>
+          <t>过负荷/熔断器</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）；参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
         </is>
       </c>
       <c r="I158" s="2" t="n"/>
@@ -7624,37 +7624,37 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>TT-08</t>
+          <t>EX-09</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>浪涌</t>
+          <t>端子与导线</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>端子编号清晰；电池正极红线、负极黑/蓝线；（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
+          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
         </is>
       </c>
       <c r="I159" s="2" t="n"/>
@@ -7669,37 +7669,37 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>TT-09</t>
+          <t>EX-10</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>电源瞬变</t>
+          <t>元件温升（气灭控制器）</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>主要元件温升 ≤60℃；变压器等表面 ≤90℃（25±3℃）；电池周围 ≤45℃</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>通 9 s/断 1 s×500 次（5.21）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
+          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="I160" s="2" t="n"/>
@@ -7714,37 +7714,37 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>TT-10</t>
+          <t>EX-11</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>电压暂降</t>
+          <t>软件资料</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号；程序存于不易丢失存储器；软件防非专门人员改动</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>40%/20 ms×10；0 V/10 ms×10（5.22）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40%/200 ms×10；0 V/20 ms×10（6.25）</t>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="I161" s="2" t="n"/>
@@ -7759,37 +7759,37 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>TT-11</t>
+          <t>EX-12</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>低温（运行）</t>
+          <t>产品标志</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>见 TT 表</t>
+          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>0℃±3℃、16 h（5.23）</t>
+          <t>（外观/设计检查项）</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
+          <t>GB 4717 8；GB 16806 7</t>
         </is>
       </c>
       <c r="I162" s="2" t="n"/>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>TT-12</t>
+          <t>TT-01</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>恒定湿热（运行）</t>
+          <t>绝缘电阻</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、90%～95%RH、4 d（5.24）</t>
+          <t>500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、4 d（6.27）</t>
+          <t>气灭控制器条件：500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
         </is>
       </c>
       <c r="I163" s="2" t="n"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>TT-13</t>
+          <t>TT-02</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>恒定湿热（耐久）</t>
+          <t>泄漏电流</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.25，不做</t>
+          <t>同左（5.14）</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
+          <t>气灭控制器条件：1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
         </is>
       </c>
       <c r="I164" s="2" t="n"/>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>TT-14</t>
+          <t>TT-03</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>振动（运行）</t>
+          <t>电气强度</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
+          <t>表 4 未列 5.15，不做</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
+          <t>气灭控制器条件：1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
         </is>
       </c>
       <c r="I165" s="2" t="n"/>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>TT-15</t>
+          <t>TT-04</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>碰撞</t>
+          <t>射频电磁场辐射</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.28）</t>
+          <t>同参数（5.16）</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：0.5 J±0.04 J×3 次/易损部件（6.30）</t>
+          <t>气灭控制器条件：10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
         </is>
       </c>
       <c r="I166" s="2" t="n"/>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>TT-16</t>
+          <t>TT-05</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>外壳燃烧（非金属外壳）</t>
+          <t>射频传导骚扰</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140 dBμV、0.15～100 MHz（5.17）</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+          <t>气灭控制器条件：140 dBμV、0.15～80 MHz（6.20）</t>
         </is>
       </c>
       <c r="I167" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>TT-17</t>
+          <t>TT-06</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>备用电池全项</t>
+          <t>静电放电</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
+          <t>同参数（5.18）</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：—（按整机备电试验 PW-04）</t>
+          <t>气灭控制器条件：空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
         </is>
       </c>
       <c r="I168" s="2" t="n"/>
@@ -8068,9 +8068,504 @@
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="2" t="n"/>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>TT-07</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>电快速瞬变</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
+      <c r="K169" s="2" t="n"/>
+      <c r="L169" s="2" t="n"/>
+      <c r="M169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>TT-08</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>浪涌</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
+      <c r="K170" s="2" t="n"/>
+      <c r="L170" s="2" t="n"/>
+      <c r="M170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>TT-09</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>电源瞬变</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>通 9 s/断 1 s×500 次（5.21）</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n"/>
+      <c r="J171" s="2" t="n"/>
+      <c r="K171" s="2" t="n"/>
+      <c r="L171" s="2" t="n"/>
+      <c r="M171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>TT-10</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>电压暂降</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>40%/20 ms×10；0 V/10 ms×10（5.22）</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40%/200 ms×10；0 V/20 ms×10（6.25）</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="n"/>
+      <c r="K172" s="2" t="n"/>
+      <c r="L172" s="2" t="n"/>
+      <c r="M172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>TT-11</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>低温（运行）</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>0℃±3℃、16 h（5.23）</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n"/>
+      <c r="J173" s="2" t="n"/>
+      <c r="K173" s="2" t="n"/>
+      <c r="L173" s="2" t="n"/>
+      <c r="M173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>TT-12</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>恒定湿热（运行）</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>40℃±2℃、90%～95%RH、4 d（5.24）</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40℃±2℃、93%±3%RH、4 d（6.27）</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
+      <c r="K174" s="2" t="n"/>
+      <c r="L174" s="2" t="n"/>
+      <c r="M174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>TT-13</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>恒定湿热（耐久）</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>表 4 未列 5.25，不做</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n"/>
+      <c r="J175" s="2" t="n"/>
+      <c r="K175" s="2" t="n"/>
+      <c r="L175" s="2" t="n"/>
+      <c r="M175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>TT-14</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>振动（运行）</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="n"/>
+      <c r="K176" s="2" t="n"/>
+      <c r="L176" s="2" t="n"/>
+      <c r="M176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>TT-15</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>碰撞</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>同参数（5.28）</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：0.5 J±0.04 J×3 次/易损部件（6.30）</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n"/>
+      <c r="J177" s="2" t="n"/>
+      <c r="K177" s="2" t="n"/>
+      <c r="L177" s="2" t="n"/>
+      <c r="M177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>TT-16</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>外壳燃烧（非金属外壳）</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
+      <c r="K178" s="2" t="n"/>
+      <c r="L178" s="2" t="n"/>
+      <c r="M178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>TT-17</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>备用电池全项</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>见 TT 表</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器条件：—（按整机备电试验 PW-04）</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="n"/>
+      <c r="K179" s="2" t="n"/>
+      <c r="L179" s="2" t="n"/>
+      <c r="M179" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M168"/>
-  <conditionalFormatting sqref="J2:J168">
+  <autoFilter ref="A1:M179"/>
+  <conditionalFormatting sqref="J2:J179">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"通过"</formula>
     </cfRule>
@@ -8079,7 +8574,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8119,7 +8614,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
@@ -8129,7 +8624,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTA(测试执行表!J2:J168)-COUNTIF(测试执行表!J2:J168,"待测")</f>
+        <f>COUNTA(测试执行表!J2:J179)-COUNTIF(测试执行表!J2:J179,"待测")</f>
         <v/>
       </c>
     </row>
@@ -8140,7 +8635,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!J2:J168,"通过")</f>
+        <f>COUNTIF(测试执行表!J2:J179,"通过")</f>
         <v/>
       </c>
     </row>
@@ -8151,7 +8646,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!J2:J168,"不通过")</f>
+        <f>COUNTIF(测试执行表!J2:J179,"不通过")</f>
         <v/>
       </c>
     </row>
@@ -8162,7 +8657,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!J2:J168,"不适用")</f>
+        <f>COUNTIF(测试执行表!J2:J179,"不适用")</f>
         <v/>
       </c>
     </row>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -7284,17 +7284,17 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
           <t>完整包装、产品标志、合格标志、说明书；无腐蚀/脱漆/划伤/毛刺；紧固无松动</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="I151" s="2" t="n"/>
@@ -7329,17 +7329,17 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
           <t>主电 AC 220 V/50 Hz；保护接地；部件供电优先 DC 24 V；电源线独立接线端子</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
         </is>
       </c>
       <c r="I152" s="2" t="n"/>
@@ -7374,17 +7374,17 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.3.1.5/5.3.8</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
           <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm；指示灯/按键按标准图 1/图 2 顺序排列；中文标注；按键有提示音</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.3.1.5/5.3.8</t>
         </is>
       </c>
       <c r="I153" s="2" t="n"/>
@@ -7419,17 +7419,17 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
+          <t>两标准分列</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
           <t>报警控制器：红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止（GB 4717 5.3.2.1）。气灭控制器：红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电（GB 16806 4.1.3.2.1）</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>两标准分列</t>
         </is>
       </c>
       <c r="I154" s="2" t="n"/>
@@ -7464,17 +7464,17 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
+          <t>两标准分列</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
           <t>报警控制器：100～500 lx、22.5°，0.8 m/3 m（GB 4717 5.3.2.2）。气灭控制器：5～500 lx、22.5°、3 m；闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz；一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮（GB 16806 4.1.3.2）</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>两标准分列</t>
         </is>
       </c>
       <c r="I155" s="2" t="n"/>
@@ -7509,17 +7509,17 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.3.1.8/5.3.1.9</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
           <t>≥IP30；非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.3.1.8/5.3.1.9</t>
         </is>
       </c>
       <c r="I156" s="2" t="n"/>
@@ -7554,17 +7554,17 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
+          <t>两标准分列</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
           <t>报警控制器：1 m 处 65～105 dB(A)、接线防脱耐 50 N（GB 4717 5.3.4）。气灭控制器：1 m 处 &gt;65 且 &lt;115 dB(A)（GB 16806 4.1.3.4.1）。两者：85% 额定电压下正常发声</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>两标准分列</t>
         </is>
       </c>
       <c r="I157" s="2" t="n"/>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
           <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）；参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
         </is>
       </c>
       <c r="I158" s="2" t="n"/>
@@ -7644,17 +7644,17 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
           <t>端子编号清晰；电池正极红线、负极黑/蓝线；（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
         </is>
       </c>
       <c r="I159" s="2" t="n"/>
@@ -7689,17 +7689,17 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
+          <t>GB 16806 4.1.3.10</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
           <t>主要元件温升 ≤60℃；变压器等表面 ≤90℃（25±3℃）；电池周围 ≤45℃</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="I160" s="2" t="n"/>
@@ -7734,17 +7734,17 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
           <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号；程序存于不易丢失存储器；软件防非专门人员改动</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="I161" s="2" t="n"/>
@@ -7779,17 +7779,17 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
+          <t>GB 4717 8；GB 16806 7</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>（外观/设计检查项）</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
           <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>（外观/设计检查项）</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>GB 4717 8；GB 16806 7</t>
         </is>
       </c>
       <c r="I162" s="2" t="n"/>
@@ -7829,12 +7829,12 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
+          <t>500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：500 V DC、60 s，≥100 MΩ（5.5/6.16）</t>
+          <t>气灭控制器条件：500 V DC、60 s：端子-机壳 ≥20 MΩ、电源-机壳 ≥50 MΩ（5.13）</t>
         </is>
       </c>
       <c r="I163" s="2" t="n"/>
@@ -7874,12 +7874,12 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>同左（5.14）</t>
+          <t>1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1.06 倍额定电压，≤0.5 mA（5.6/6.17）</t>
+          <t>气灭控制器条件：同左（5.14）</t>
         </is>
       </c>
       <c r="I164" s="2" t="n"/>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.15，不做</t>
+          <t>1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）（5.7/6.18）</t>
+          <t>气灭控制器条件：表 4 未列 5.15，不做</t>
         </is>
       </c>
       <c r="I165" s="2" t="n"/>
@@ -7964,12 +7964,12 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.16）</t>
+          <t>10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10 V/m、80～1 000 MHz、80%AM(1 kHz)（6.19）</t>
+          <t>气灭控制器条件：同参数（5.16）</t>
         </is>
       </c>
       <c r="I166" s="2" t="n"/>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>140 dBμV、0.15～100 MHz（5.17）</t>
+          <t>140 dBμV、0.15～80 MHz（6.20）</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：140 dBμV、0.15～80 MHz（6.20）</t>
+          <t>气灭控制器条件：140 dBμV、0.15～100 MHz（5.17）</t>
         </is>
       </c>
       <c r="I167" s="2" t="n"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.18）</t>
+          <t>空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s（6.21）</t>
+          <t>气灭控制器条件：同参数（5.18）</t>
         </is>
       </c>
       <c r="I168" s="2" t="n"/>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
+          <t>AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3（6.22）</t>
+          <t>气灭控制器条件：AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz（5.19）</t>
         </is>
       </c>
       <c r="I169" s="2" t="n"/>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
+          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次（6.23）</t>
+          <t>气灭控制器条件：AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次（5.20）</t>
         </is>
       </c>
       <c r="I170" s="2" t="n"/>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>通 9 s/断 1 s×500 次（5.21）</t>
+          <t>通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：通 9 s/断 1 s×500 次、6 次/min（6.24）</t>
+          <t>气灭控制器条件：通 9 s/断 1 s×500 次（5.21）</t>
         </is>
       </c>
       <c r="I171" s="2" t="n"/>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>40%/20 ms×10；0 V/10 ms×10（5.22）</t>
+          <t>40%/200 ms×10；0 V/20 ms×10（6.25）</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40%/200 ms×10；0 V/20 ms×10（6.25）</t>
+          <t>气灭控制器条件：40%/20 ms×10；0 V/10 ms×10（5.22）</t>
         </is>
       </c>
       <c r="I172" s="2" t="n"/>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>0℃±3℃、16 h（5.23）</t>
+          <t>-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：-10℃±2℃、16 h、变温 ≤1℃/min（6.26）</t>
+          <t>气灭控制器条件：0℃±3℃、16 h（5.23）</t>
         </is>
       </c>
       <c r="I173" s="2" t="n"/>
@@ -8324,12 +8324,12 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、90%～95%RH、4 d（5.24）</t>
+          <t>40℃±2℃、93%±3%RH、4 d（6.27）</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、4 d（6.27）</t>
+          <t>气灭控制器条件：40℃±2℃、90%～95%RH、4 d（5.24）</t>
         </is>
       </c>
       <c r="I174" s="2" t="n"/>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>表 4 未列 5.25，不做</t>
+          <t>40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h（6.28）</t>
+          <t>气灭控制器条件：表 4 未列 5.25，不做</t>
         </is>
       </c>
       <c r="I175" s="2" t="n"/>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
+          <t>10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环（6.29）</t>
+          <t>气灭控制器条件：10～150 Hz、0.981 m/s²、3 轴各 1 循环（5.26）</t>
         </is>
       </c>
       <c r="I176" s="2" t="n"/>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.28）</t>
+          <t>0.5 J±0.04 J×3 次/易损部件（6.30）</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：0.5 J±0.04 J×3 次/易损部件（6.30）</t>
+          <t>气灭控制器条件：同参数（5.28）</t>
         </is>
       </c>
       <c r="I177" s="2" t="n"/>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+          <t>气灭控制器条件：—</t>
         </is>
       </c>
       <c r="I178" s="2" t="n"/>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
+          <t>—（按整机备电试验 PW-04）</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器条件：—（按整机备电试验 PW-04）</t>
+          <t>气灭控制器条件：GB 16806 附录 A：10 支试样，电压一致性/容量（常温 ≥90 min、-10℃ ≥50 min）/容量保存 ≥0.6/循环 10 次 ≥90%/过放 ≥0.9/5C₂₀ 大电流/密闭效率 ≥95%/防爆/防酸雾/跌落</t>
         </is>
       </c>
       <c r="I179" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -11,7 +11,7 @@
     <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$576</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$582</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M576"/>
+  <dimension ref="A1:M582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -19118,37 +19118,33 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>GE-01</t>
+          <t>UI-29</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
-        </is>
-      </c>
-      <c r="D409" s="2" t="inlineStr">
-        <is>
-          <t>禁止直收触发器件</t>
-        </is>
-      </c>
+          <t>人机菜单(产品级)</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr"/>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>P0（设计红线）</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>4.3.1.2</t>
+          <t>表1 高级向下兼容</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>设计检查 + 尝试将探测器/手报直接接入</t>
+          <t>【建议项·未实现】四级重置二/三级密码（总案）——场景：二/三级操作员忘记密码/人员离职/交接失败，无法登录导致现场消音、复位、手动启停全部不可操作。建议流程：四级（算法密码）登录 → 密码管理 → 选择重置二级或三级 → 二次确认 → 屏显一次性临时密码（随机 6 位，24 h 或一次有效）→ 该级下次登录后强制设置新密码</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I409" s="2" t="n"/>
@@ -19157,7 +19153,7 @@
       <c r="L409" s="2" t="n"/>
       <c r="M409" s="2" t="inlineStr">
         <is>
-          <t>已原子</t>
+          <t>建议项，产品会评审后排期</t>
         </is>
       </c>
     </row>
@@ -19167,44 +19163,44 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>GE-02</t>
+          <t>UI-29.1</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
-        </is>
-      </c>
-      <c r="D410" s="2" t="inlineStr"/>
+          <t>人机菜单(产品级)</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>重置生效</t>
+        </is>
+      </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 ↔ 5.3.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>启动控制全流程（总案）——分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间（操作细化见 §14.1 规程 A/B，规程本身不收录）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>四级执行重置后，旧密码立即失效，临时密码可登录对应级别</t>
         </is>
       </c>
       <c r="I410" s="2" t="n"/>
       <c r="J410" s="2" t="n"/>
       <c r="K410" s="2" t="n"/>
       <c r="L410" s="2" t="n"/>
-      <c r="M410" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -19212,27 +19208,27 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>GE-02.1</t>
+          <t>UI-29.2</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>① 启动声光与记录</t>
+          <t>强制改密</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 a)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
@@ -19242,7 +19238,7 @@
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>接收启动控制信号→发出启动声、光信号并记录时间</t>
+          <t>用临时密码首次登录即强制进入改密流程，未改密不得进入其他操作</t>
         </is>
       </c>
       <c r="I411" s="2" t="n"/>
@@ -19257,27 +19253,27 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>GE-02.2</t>
+          <t>UI-29.3</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>① 启动声可消</t>
+          <t>黑匣子留痕</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 a)</t>
+          <t>B.1.1.1</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
@@ -19287,7 +19283,7 @@
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>启动声可手动消除</t>
+          <t>重置事件记录：操作级别Ⅳ、被重置级别、时间（年月日时分秒）——密码值本身不记录</t>
         </is>
       </c>
       <c r="I412" s="2" t="n"/>
@@ -19302,27 +19298,27 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>GE-02.3</t>
+          <t>UI-29.4</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>① 再启动</t>
+          <t>权限边界</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 a)</t>
+          <t>表1 单向性</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
@@ -19332,7 +19328,7 @@
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>再有启动控制信号输入时可再启动</t>
+          <t>三级不能重置任何密码（含自身）；二级同理；四级不能"设置"四级密码（算法生成，无存储可改）</t>
         </is>
       </c>
       <c r="I413" s="2" t="n"/>
@@ -19347,27 +19343,27 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>GE-02.4</t>
+          <t>UI-29.5</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>气体灭火控制器</t>
+          <t>人机菜单(产品级)</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>② 声光警报器</t>
+          <t>运行无扰</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>建议</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 b)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
@@ -19377,7 +19373,7 @@
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>启动声光警报器</t>
+          <t>重置过程不影响运行状态：火警/联动/巡检照常，不触发复位或退出报警状态</t>
         </is>
       </c>
       <c r="I414" s="2" t="n"/>
@@ -19392,7 +19388,7 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>GE-02.5</t>
+          <t>GE-01</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
@@ -19402,34 +19398,38 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>③ 延时光指示</t>
+          <t>禁止直收触发器件</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P0（设计红线）</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 c)</t>
+          <t>4.3.1.2</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>设计检查 + 尝试将探测器/手报直接接入</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>进入延时：延时期间有延时光指示</t>
+          <t>气灭控制器不应直接接收火灾报警触发器件的火灾报警信号（启动信号须来自消防联动控制器或现场启动按键）</t>
         </is>
       </c>
       <c r="I415" s="2" t="n"/>
       <c r="J415" s="2" t="n"/>
       <c r="K415" s="2" t="n"/>
       <c r="L415" s="2" t="n"/>
-      <c r="M415" s="2" t="n"/>
+      <c r="M415" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>GE-02.6</t>
+          <t>GE-02</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
@@ -19445,11 +19445,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D416" s="2" t="inlineStr">
-        <is>
-          <t>③ 延时显示</t>
-        </is>
-      </c>
+      <c r="D416" s="2" t="inlineStr"/>
       <c r="E416" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -19457,24 +19453,28 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 c)</t>
+          <t>4.3.2.2 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>启动控制全流程（总案）——分别经联动控制器和现场启动按键输入启动控制信号，逐阶段观察并记录时间（操作细化见 §14.1 规程 A/B，规程本身不收录）</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>显示延时时间和保护区域</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I416" s="2" t="n"/>
       <c r="J416" s="2" t="n"/>
       <c r="K416" s="2" t="n"/>
       <c r="L416" s="2" t="n"/>
-      <c r="M416" s="2" t="n"/>
+      <c r="M416" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>GE-02.7</t>
+          <t>GE-02.1</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>③ 封舱动作</t>
+          <t>① 启动声光与记录</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 c)</t>
+          <t>4.3.2.2 a)</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>关闭防火门窗/防火阀+停通风空调</t>
+          <t>接收启动控制信号→发出启动声、光信号并记录时间</t>
         </is>
       </c>
       <c r="I417" s="2" t="n"/>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>GE-02.8</t>
+          <t>GE-02.2</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>④ 喷洒控制信号</t>
+          <t>① 启动声可消</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 d)</t>
+          <t>4.3.2.2 a)</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>延时结束发启动喷洒控制信号+光指示</t>
+          <t>启动声可手动消除</t>
         </is>
       </c>
       <c r="I418" s="2" t="n"/>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>GE-02.9</t>
+          <t>GE-02.3</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
@@ -19582,7 +19582,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>④ 喷洒光警报器</t>
+          <t>① 再启动</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 d)</t>
+          <t>4.3.2.2 a)</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>启动喷洒光警报器</t>
+          <t>再有启动控制信号输入时可再启动</t>
         </is>
       </c>
       <c r="I419" s="2" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>GE-02.10</t>
+          <t>GE-02.4</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>⑤ 喷洒声光</t>
+          <t>② 声光警报器</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.2 e)</t>
+          <t>4.3.2.2 b)</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>喷洒阶段发出相应声光保持至复位并记录时间</t>
+          <t>启动声光警报器</t>
         </is>
       </c>
       <c r="I420" s="2" t="n"/>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>GE-03</t>
+          <t>GE-02.5</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
@@ -19670,7 +19670,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D421" s="2" t="inlineStr"/>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>③ 延时光指示</t>
+        </is>
+      </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -19678,28 +19682,24 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.3 ↔ 5.3.1</t>
+          <t>4.3.2.2 c)</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>延时设置与手动中止（总案）——调整延时值；延时期间执行手动停止</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>进入延时：延时期间有延时光指示</t>
         </is>
       </c>
       <c r="I421" s="2" t="n"/>
       <c r="J421" s="2" t="n"/>
       <c r="K421" s="2" t="n"/>
       <c r="L421" s="2" t="n"/>
-      <c r="M421" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>GE-03.1</t>
+          <t>GE-02.6</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>延时范围</t>
+          <t>③ 延时显示</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.3</t>
+          <t>4.3.2.2 c)</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>延时 0～30 s 可调</t>
+          <t>显示延时时间和保护区域</t>
         </is>
       </c>
       <c r="I422" s="2" t="n"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>GE-03.2</t>
+          <t>GE-02.7</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>手动停止</t>
+          <t>③ 封舱动作</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.3</t>
+          <t>4.3.2.2 c)</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>延时期间能手动停止后续动作</t>
+          <t>关闭防火门窗/防火阀+停通风空调</t>
         </is>
       </c>
       <c r="I423" s="2" t="n"/>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>GE-04</t>
+          <t>GE-02.8</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -19805,7 +19805,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D424" s="2" t="inlineStr"/>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>④ 喷洒控制信号</t>
+        </is>
+      </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -19813,28 +19817,24 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4 ↔ 5.3.1</t>
+          <t>4.3.2.2 d)</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>手/自动与优先级（总案）——切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>延时结束发启动喷洒控制信号+光指示</t>
         </is>
       </c>
       <c r="I424" s="2" t="n"/>
       <c r="J424" s="2" t="n"/>
       <c r="K424" s="2" t="n"/>
       <c r="L424" s="2" t="n"/>
-      <c r="M424" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>GE-04.1</t>
+          <t>GE-02.9</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>状态指示</t>
+          <t>④ 喷洒光警报器</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4</t>
+          <t>4.3.2.2 d)</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
-          <t>有控制状态指示</t>
+          <t>启动喷洒光警报器</t>
         </is>
       </c>
       <c r="I425" s="2" t="n"/>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>GE-04.2</t>
+          <t>GE-02.10</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>复位不改状态</t>
+          <t>⑤ 喷洒声光</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4</t>
+          <t>4.3.2.2 e)</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
-          <t>状态不受复位影响</t>
+          <t>喷洒阶段发出相应声光保持至复位并记录时间</t>
         </is>
       </c>
       <c r="I426" s="2" t="n"/>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>GE-04.3</t>
+          <t>GE-03</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
@@ -19940,11 +19940,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D427" s="2" t="inlineStr">
-        <is>
-          <t>手动插入优先</t>
-        </is>
-      </c>
+      <c r="D427" s="2" t="inlineStr"/>
       <c r="E427" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -19952,24 +19948,28 @@
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4</t>
+          <t>4.3.2.3 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>延时设置与手动中止（总案）——调整延时值；延时期间执行手动停止</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>自动下手动插入优先</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I427" s="2" t="n"/>
       <c r="J427" s="2" t="n"/>
       <c r="K427" s="2" t="n"/>
       <c r="L427" s="2" t="n"/>
-      <c r="M427" s="2" t="n"/>
+      <c r="M427" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>GE-04.4</t>
+          <t>GE-03.1</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>停止后可再启动</t>
+          <t>延时范围</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.4</t>
+          <t>4.3.2.3</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>手动停止后再有启动信号仍按预置逻辑工作</t>
+          <t>延时 0～30 s 可调</t>
         </is>
       </c>
       <c r="I428" s="2" t="n"/>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>GE-05</t>
+          <t>GE-03.2</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
@@ -20032,38 +20032,34 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>声信号优先级</t>
+          <t>手动停止</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.5 ↔ 5.3.1</t>
+          <t>4.3.2.3</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>使喷洒声、启动声、故障声两两同时存在</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
+          <t>延时期间能手动停止后续动作</t>
         </is>
       </c>
       <c r="I429" s="2" t="n"/>
       <c r="J429" s="2" t="n"/>
       <c r="K429" s="2" t="n"/>
       <c r="L429" s="2" t="n"/>
-      <c r="M429" s="2" t="inlineStr">
-        <is>
-          <t>已原子【拆分存疑】——单行排序断言，实测为三对两两比较（见 §14.1 规程 D4～D6），是否按对拆待人审</t>
-        </is>
-      </c>
+      <c r="M429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -20071,7 +20067,7 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>GE-06</t>
+          <t>GE-04</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -20079,11 +20075,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D430" s="2" t="inlineStr">
-        <is>
-          <t>接收联动信号</t>
-        </is>
-      </c>
+      <c r="D430" s="2" t="inlineStr"/>
       <c r="E430" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -20091,17 +20083,17 @@
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.6</t>
+          <t>4.3.2.4 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>消防联动控制器下发联动信号</t>
+          <t>手/自动与优先级（总案）——切换手/自动并复位；自动运行中手动插入；手动停止后再输入启动信号</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>正确接收并按逻辑执行</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I430" s="2" t="n"/>
@@ -20110,7 +20102,7 @@
       <c r="L430" s="2" t="n"/>
       <c r="M430" s="2" t="inlineStr">
         <is>
-          <t>已原子</t>
+          <t>总案</t>
         </is>
       </c>
     </row>
@@ -20120,7 +20112,7 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>GE-07</t>
+          <t>GE-04.1</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
@@ -20128,36 +20120,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D431" s="2" t="inlineStr"/>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>状态指示</t>
+        </is>
+      </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
+          <t>4.3.2.4</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>分区警报器与分区指示（总案）——逐区启动/停止声光警报器</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>有控制状态指示</t>
         </is>
       </c>
       <c r="I431" s="2" t="n"/>
       <c r="J431" s="2" t="n"/>
       <c r="K431" s="2" t="n"/>
       <c r="L431" s="2" t="n"/>
-      <c r="M431" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -20165,7 +20157,7 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>GE-07.1</t>
+          <t>GE-04.2</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -20175,17 +20167,17 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>分区启停</t>
+          <t>复位不改状态</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.7</t>
+          <t>4.3.2.4</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
@@ -20195,7 +20187,7 @@
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>可分区启动和停止保护区域声光警报器</t>
+          <t>状态不受复位影响</t>
         </is>
       </c>
       <c r="I432" s="2" t="n"/>
@@ -20210,7 +20202,7 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>GE-07.2</t>
+          <t>GE-04.3</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
@@ -20220,17 +20212,17 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>分区状态灯</t>
+          <t>手动插入优先</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.8</t>
+          <t>4.3.2.4</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
@@ -20240,7 +20232,7 @@
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>每个保护区域有独立工作状态指示灯</t>
+          <t>自动下手动插入优先</t>
         </is>
       </c>
       <c r="I433" s="2" t="n"/>
@@ -20255,7 +20247,7 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>GE-08</t>
+          <t>GE-04.4</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -20263,7 +20255,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D434" s="2" t="inlineStr"/>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>停止后可再启动</t>
+        </is>
+      </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -20271,28 +20267,24 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9 ↔ 5.3.1</t>
+          <t>4.3.2.4</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>向联动控制器上报（总案）——触发各阶段，在联动控制器（或模拟器）端核对</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>手动停止后再有启动信号仍按预置逻辑工作</t>
         </is>
       </c>
       <c r="I434" s="2" t="n"/>
       <c r="J434" s="2" t="n"/>
       <c r="K434" s="2" t="n"/>
       <c r="L434" s="2" t="n"/>
-      <c r="M434" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -20300,7 +20292,7 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>GE-08.1</t>
+          <t>GE-05</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
@@ -20310,34 +20302,38 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>启动控制信号</t>
+          <t>声信号优先级</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.5 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>使喷洒声、启动声、故障声两两同时存在</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>能发送启动控制信号</t>
+          <t>喷洒声 &gt; 启动控制声 &gt; 故障声</t>
         </is>
       </c>
       <c r="I435" s="2" t="n"/>
       <c r="J435" s="2" t="n"/>
       <c r="K435" s="2" t="n"/>
       <c r="L435" s="2" t="n"/>
-      <c r="M435" s="2" t="n"/>
+      <c r="M435" s="2" t="inlineStr">
+        <is>
+          <t>已原子【拆分存疑】——单行排序断言，实测为三对两两比较（见 §14.1 规程 D4～D6），是否按对拆待人审</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -20345,7 +20341,7 @@
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>GE-08.2</t>
+          <t>GE-06</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -20355,7 +20351,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>延时信号</t>
+          <t>接收联动信号</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -20365,24 +20361,28 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.6</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>消防联动控制器下发联动信号</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
-          <t>能发送延时信号</t>
+          <t>正确接收并按逻辑执行</t>
         </is>
       </c>
       <c r="I436" s="2" t="n"/>
       <c r="J436" s="2" t="n"/>
       <c r="K436" s="2" t="n"/>
       <c r="L436" s="2" t="n"/>
-      <c r="M436" s="2" t="n"/>
+      <c r="M436" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>GE-08.3</t>
+          <t>GE-07</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
@@ -20398,36 +20398,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D437" s="2" t="inlineStr">
-        <is>
-          <t>启动喷洒控制信号</t>
-        </is>
-      </c>
+      <c r="D437" s="2" t="inlineStr"/>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.7/4.3.2.8 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>分区警报器与分区指示（总案）——逐区启动/停止声光警报器</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>能发送启动喷洒控制信号</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I437" s="2" t="n"/>
       <c r="J437" s="2" t="n"/>
       <c r="K437" s="2" t="n"/>
       <c r="L437" s="2" t="n"/>
-      <c r="M437" s="2" t="n"/>
+      <c r="M437" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>GE-08.4</t>
+          <t>GE-07.1</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -20445,17 +20445,17 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>气体喷洒信号</t>
+          <t>分区启停</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.7</t>
         </is>
       </c>
       <c r="G438" s="2" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>能发送气体喷洒信号</t>
+          <t>可分区启动和停止保护区域声光警报器</t>
         </is>
       </c>
       <c r="I438" s="2" t="n"/>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>GE-08.5</t>
+          <t>GE-07.2</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
@@ -20490,17 +20490,17 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>故障信号</t>
+          <t>分区状态灯</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.8</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>能发送故障信号</t>
+          <t>每个保护区域有独立工作状态指示灯</t>
         </is>
       </c>
       <c r="I439" s="2" t="n"/>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>GE-08.6</t>
+          <t>GE-08</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -20533,11 +20533,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D440" s="2" t="inlineStr">
-        <is>
-          <t>阀动作信息</t>
-        </is>
-      </c>
+      <c r="D440" s="2" t="inlineStr"/>
       <c r="E440" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -20545,24 +20541,28 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.9</t>
+          <t>4.3.2.9 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>向联动控制器上报（总案）——触发各阶段，在联动控制器（或模拟器）端核对</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
-          <t>能发送选择阀和瓶头阀动作信息</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I440" s="2" t="n"/>
       <c r="J440" s="2" t="n"/>
       <c r="K440" s="2" t="n"/>
       <c r="L440" s="2" t="n"/>
-      <c r="M440" s="2" t="n"/>
+      <c r="M440" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>GE-09</t>
+          <t>GE-08.1</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
@@ -20578,7 +20578,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D441" s="2" t="inlineStr"/>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>启动控制信号</t>
+        </is>
+      </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -20586,28 +20590,24 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.11 ↔ 5.3.1</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>复位与状态重建（总案）——启动保持状态下手动复位，计时</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>能发送启动控制信号</t>
         </is>
       </c>
       <c r="I441" s="2" t="n"/>
       <c r="J441" s="2" t="n"/>
       <c r="K441" s="2" t="n"/>
       <c r="L441" s="2" t="n"/>
-      <c r="M441" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>GE-09.1</t>
+          <t>GE-08.2</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>复位按键</t>
+          <t>延时信号</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.11</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>设复位按键</t>
+          <t>能发送延时信号</t>
         </is>
       </c>
       <c r="I442" s="2" t="n"/>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>GE-09.2</t>
+          <t>GE-08.3</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>状态重建</t>
+          <t>启动喷洒控制信号</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.11</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
+          <t>能发送启动喷洒控制信号</t>
         </is>
       </c>
       <c r="I443" s="2" t="n"/>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>GE-10</t>
+          <t>GE-08.4</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
@@ -20713,36 +20713,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D444" s="2" t="inlineStr"/>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>气体喷洒信号</t>
+        </is>
+      </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12 ↔ 5.3.1</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>计时精度（总案）——连续运行 24 h 比对</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>能发送气体喷洒信号</t>
         </is>
       </c>
       <c r="I444" s="2" t="n"/>
       <c r="J444" s="2" t="n"/>
       <c r="K444" s="2" t="n"/>
       <c r="L444" s="2" t="n"/>
-      <c r="M444" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>GE-10.1</t>
+          <t>GE-08.5</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
@@ -20760,17 +20760,17 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>日计时误差</t>
+          <t>故障信号</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>日计时误差 ≤30 s</t>
+          <t>能发送故障信号</t>
         </is>
       </c>
       <c r="I445" s="2" t="n"/>
@@ -20795,7 +20795,7 @@
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>GE-10.2</t>
+          <t>GE-08.6</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
@@ -20805,17 +20805,17 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>打印时间格式</t>
+          <t>阀动作信息</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12</t>
+          <t>4.3.2.9</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
@@ -20825,7 +20825,7 @@
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>打印含月日时分</t>
+          <t>能发送选择阀和瓶头阀动作信息</t>
         </is>
       </c>
       <c r="I446" s="2" t="n"/>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>GE-10.3</t>
+          <t>GE-09</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
@@ -20848,36 +20848,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D447" s="2" t="inlineStr">
-        <is>
-          <t>记录通道</t>
-        </is>
-      </c>
+      <c r="D447" s="2" t="inlineStr"/>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.12</t>
+          <t>4.3.2.11 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>复位与状态重建（总案）——启动保持状态下手动复位，计时</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>不能仅用打印机记录</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I447" s="2" t="n"/>
       <c r="J447" s="2" t="n"/>
       <c r="K447" s="2" t="n"/>
       <c r="L447" s="2" t="n"/>
-      <c r="M447" s="2" t="n"/>
+      <c r="M447" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>GE-11</t>
+          <t>GE-09.1</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
@@ -20895,38 +20895,34 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>输出特性</t>
+          <t>复位按键</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>4.3.2.10 ↔ 5.3.1</t>
+          <t>4.3.2.11</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>测输出接点电压/电流/容量</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>满足制造商规定</t>
+          <t>设复位按键</t>
         </is>
       </c>
       <c r="I448" s="2" t="n"/>
       <c r="J448" s="2" t="n"/>
       <c r="K448" s="2" t="n"/>
       <c r="L448" s="2" t="n"/>
-      <c r="M448" s="2" t="inlineStr">
-        <is>
-          <t>已原子</t>
-        </is>
-      </c>
+      <c r="M448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -20934,7 +20930,7 @@
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>GE-12</t>
+          <t>GE-09.2</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
@@ -20942,7 +20938,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D449" s="2" t="inlineStr"/>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>状态重建</t>
+        </is>
+      </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -20950,28 +20950,24 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
+          <t>4.3.2.11</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>故障报警（部位/类型）（总案）——分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>复位后仍存在的状态和信息保持或 ≤20 s 重新建立</t>
         </is>
       </c>
       <c r="I449" s="2" t="n"/>
       <c r="J449" s="2" t="n"/>
       <c r="K449" s="2" t="n"/>
       <c r="L449" s="2" t="n"/>
-      <c r="M449" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -20979,7 +20975,7 @@
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>GE-12.1</t>
+          <t>GE-10</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
@@ -20987,36 +20983,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D450" s="2" t="inlineStr">
-        <is>
-          <t>故障声光时限</t>
-        </is>
-      </c>
+      <c r="D450" s="2" t="inlineStr"/>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1</t>
+          <t>4.3.2.12 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>计时精度（总案）——连续运行 24 h 比对</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>≤100 s 故障声光</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I450" s="2" t="n"/>
       <c r="J450" s="2" t="n"/>
       <c r="K450" s="2" t="n"/>
       <c r="L450" s="2" t="n"/>
-      <c r="M450" s="2" t="n"/>
+      <c r="M450" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -21024,7 +21020,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>GE-12.2</t>
+          <t>GE-10.1</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -21034,17 +21030,17 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>声可消可再启动</t>
+          <t>日计时误差</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1</t>
+          <t>4.3.2.12</t>
         </is>
       </c>
       <c r="G451" s="2" t="inlineStr">
@@ -21054,7 +21050,7 @@
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>故障声可消可再启动</t>
+          <t>日计时误差 ≤30 s</t>
         </is>
       </c>
       <c r="I451" s="2" t="n"/>
@@ -21069,7 +21065,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>GE-12.3</t>
+          <t>GE-10.2</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -21079,17 +21075,17 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>光保持</t>
+          <t>打印时间格式</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1</t>
+          <t>4.3.2.12</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
@@ -21099,7 +21095,7 @@
       </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>故障光保持至排除</t>
+          <t>打印含月日时分</t>
         </is>
       </c>
       <c r="I452" s="2" t="n"/>
@@ -21114,7 +21110,7 @@
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>GE-12.4</t>
+          <t>GE-10.3</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
@@ -21124,17 +21120,17 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>部位指示</t>
+          <t>记录通道</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.2 a)/b)</t>
+          <t>4.3.2.12</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
@@ -21144,7 +21140,7 @@
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>a)/b) 指示部位</t>
+          <t>不能仅用打印机记录</t>
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
@@ -21159,7 +21155,7 @@
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>GE-12.5</t>
+          <t>GE-11</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
@@ -21169,34 +21165,38 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>类型指示</t>
+          <t>输出特性</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.2 c)/d)/e)</t>
+          <t>4.3.2.10 ↔ 5.3.1</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>测输出接点电压/电流/容量</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>c)/d)/e) 指示类型</t>
+          <t>满足制造商规定</t>
         </is>
       </c>
       <c r="I454" s="2" t="n"/>
       <c r="J454" s="2" t="n"/>
       <c r="K454" s="2" t="n"/>
       <c r="L454" s="2" t="n"/>
-      <c r="M454" s="2" t="n"/>
+      <c r="M454" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>GE-12.6</t>
+          <t>GE-12</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
@@ -21212,11 +21212,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D455" s="2" t="inlineStr">
-        <is>
-          <t>故障灯</t>
-        </is>
-      </c>
+      <c r="D455" s="2" t="inlineStr"/>
       <c r="E455" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -21224,24 +21220,28 @@
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.1</t>
+          <t>4.3.3.1/4.3.3.2 ↔ 5.3.2</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>故障报警（部位/类型）（总案）——分别制造：a) 警报器连线断/短/接地；b) 驱动部件、现场启停按键连线断/短/接地；c) 充电器-备电断/短；d) 备电-负载断/短；e) 主电欠压。计时</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>故障指示灯点亮</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
       <c r="J455" s="2" t="n"/>
       <c r="K455" s="2" t="n"/>
       <c r="L455" s="2" t="n"/>
-      <c r="M455" s="2" t="n"/>
+      <c r="M455" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>GE-13</t>
+          <t>GE-12.1</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -21257,36 +21257,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D456" s="2" t="inlineStr"/>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>故障声光时限</t>
+        </is>
+      </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.3.1</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>阶段×故障双向互检（总案）——双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>≤100 s 故障声光</t>
         </is>
       </c>
       <c r="I456" s="2" t="n"/>
       <c r="J456" s="2" t="n"/>
       <c r="K456" s="2" t="n"/>
       <c r="L456" s="2" t="n"/>
-      <c r="M456" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>GE-13.1</t>
+          <t>GE-12.2</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -21304,17 +21304,17 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>① 阶段中故障显示</t>
+          <t>声可消可再启动</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.3.1</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>各阶段中制造的故障均正常显示</t>
+          <t>故障声可消可再启动</t>
         </is>
       </c>
       <c r="I457" s="2" t="n"/>
@@ -21339,7 +21339,7 @@
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>GE-13.2</t>
+          <t>GE-12.3</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -21349,17 +21349,17 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>① 不打断流程</t>
+          <t>光保持</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.3.1</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>不打断当前流程</t>
+          <t>故障光保持至排除</t>
         </is>
       </c>
       <c r="I458" s="2" t="n"/>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>GE-13.3</t>
+          <t>GE-12.4</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
@@ -21394,17 +21394,17 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>② 流程照常推进</t>
+          <t>部位指示</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.3.2 a)/b)</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>故障先存在时，流程照常推进</t>
+          <t>a)/b) 指示部位</t>
         </is>
       </c>
       <c r="I459" s="2" t="n"/>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>GE-13.4</t>
+          <t>GE-12.5</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
@@ -21439,17 +21439,17 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>② 故障灯全程保持</t>
+          <t>类型指示</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>↔ 5.3.2.2.2</t>
+          <t>4.3.3.2 c)/d)/e)</t>
         </is>
       </c>
       <c r="G460" s="2" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>故障指示灯全程保持</t>
+          <t>c)/d)/e) 指示类型</t>
         </is>
       </c>
       <c r="I460" s="2" t="n"/>
@@ -21474,7 +21474,7 @@
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>GE-14</t>
+          <t>GE-12.6</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
@@ -21482,7 +21482,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D461" s="2" t="inlineStr"/>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>故障灯</t>
+        </is>
+      </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -21490,28 +21494,24 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
+          <t>4.3.3.1</t>
         </is>
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>故障复位复显与清空（总案）——① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>故障指示灯点亮</t>
         </is>
       </c>
       <c r="I461" s="2" t="n"/>
       <c r="J461" s="2" t="n"/>
       <c r="K461" s="2" t="n"/>
       <c r="L461" s="2" t="n"/>
-      <c r="M461" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -21519,7 +21519,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>GE-14.1</t>
+          <t>GE-13</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -21527,36 +21527,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D462" s="2" t="inlineStr">
-        <is>
-          <t>尚存故障复显</t>
-        </is>
-      </c>
+      <c r="D462" s="2" t="inlineStr"/>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.3</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>阶段×故障双向互检（总案）——双向各测一遍：① 分别在启动控制、延时、启动喷洒、气体喷洒状态中制造故障；② 先使故障存在，再分别进入上述四个阶段</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>① 尚存故障 ≤100 s 重新显示</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I462" s="2" t="n"/>
       <c r="J462" s="2" t="n"/>
       <c r="K462" s="2" t="n"/>
       <c r="L462" s="2" t="n"/>
-      <c r="M462" s="2" t="n"/>
+      <c r="M462" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>GE-14.2</t>
+          <t>GE-13.1</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
@@ -21574,17 +21574,17 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>全清无残留</t>
+          <t>① 阶段中故障显示</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>4.3.3.3</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
+          <t>各阶段中制造的故障均正常显示</t>
         </is>
       </c>
       <c r="I463" s="2" t="n"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>GE-15</t>
+          <t>GE-13.2</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
@@ -21617,36 +21617,36 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D464" s="2" t="inlineStr"/>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>① 不打断流程</t>
+        </is>
+      </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.1 ↔ 5.3.3</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>自检不动作输出（总案）——自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>不打断当前流程</t>
         </is>
       </c>
       <c r="I464" s="2" t="n"/>
       <c r="J464" s="2" t="n"/>
       <c r="K464" s="2" t="n"/>
       <c r="L464" s="2" t="n"/>
-      <c r="M464" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>GE-15.1</t>
+          <t>GE-13.3</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
@@ -21664,17 +21664,17 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>输出不动作</t>
+          <t>② 流程照常推进</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.1</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G465" s="2" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>自检期间受控设备与输出接点均不动作</t>
+          <t>故障先存在时，流程照常推进</t>
         </is>
       </c>
       <c r="I465" s="2" t="n"/>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>GE-15.2</t>
+          <t>GE-13.4</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
@@ -21709,17 +21709,17 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>不阻断灭火控制</t>
+          <t>② 故障灯全程保持</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.1</t>
+          <t>↔ 5.3.2.2.2</t>
         </is>
       </c>
       <c r="G466" s="2" t="inlineStr">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
+          <t>故障指示灯全程保持</t>
         </is>
       </c>
       <c r="I466" s="2" t="n"/>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>GE-16</t>
+          <t>GE-14</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -21752,11 +21752,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D467" s="2" t="inlineStr">
-        <is>
-          <t>面板自检</t>
-        </is>
-      </c>
+      <c r="D467" s="2" t="inlineStr"/>
       <c r="E467" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -21764,17 +21760,17 @@
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>4.3.4.2 ↔ 5.3.3</t>
+          <t>4.3.3.3 ↔ 5.3.2.2.5</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>手动检查音响、指示灯、显示器</t>
+          <t>故障复位复显与清空（总案）——① 保留故障源手动复位，计时；② 排除所有故障源后观察（自动恢复的不复位；未自清的手动复位）</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>全部可手动检查</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I467" s="2" t="n"/>
@@ -21783,7 +21779,7 @@
       <c r="L467" s="2" t="n"/>
       <c r="M467" s="2" t="inlineStr">
         <is>
-          <t>已原子</t>
+          <t>总案</t>
         </is>
       </c>
     </row>
@@ -21793,7 +21789,7 @@
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>GE-17</t>
+          <t>GE-14.1</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
@@ -21801,7 +21797,11 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D468" s="2" t="inlineStr"/>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>尚存故障复显</t>
+        </is>
+      </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -21809,28 +21809,24 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>4.3.3.3</t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>主备电转换（总案）——断主电/恢复主电</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>① 尚存故障 ≤100 s 重新显示</t>
         </is>
       </c>
       <c r="I468" s="2" t="n"/>
       <c r="J468" s="2" t="n"/>
       <c r="K468" s="2" t="n"/>
       <c r="L468" s="2" t="n"/>
-      <c r="M468" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -21838,7 +21834,7 @@
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>GE-17.1</t>
+          <t>GE-14.2</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
@@ -21848,7 +21844,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>自动转换</t>
+          <t>全清无残留</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -21858,7 +21854,7 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1</t>
+          <t>4.3.3.3</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
@@ -21868,7 +21864,7 @@
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>自动转换</t>
+          <t>② 全部排除后指示完全清空、无"幽灵故障"残留（与 FT-05 ② 同构）</t>
         </is>
       </c>
       <c r="I469" s="2" t="n"/>
@@ -21883,7 +21879,7 @@
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>GE-17.2</t>
+          <t>GE-15</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
@@ -21891,11 +21887,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D470" s="2" t="inlineStr">
-        <is>
-          <t>状态指示</t>
-        </is>
-      </c>
+      <c r="D470" s="2" t="inlineStr"/>
       <c r="E470" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -21903,24 +21895,28 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1</t>
+          <t>4.3.4.1 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>自检不动作输出（总案）——自检期间监视受控设备与输出接点；自检 &gt;1 min 时使非自检部位启动</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>状态指示</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I470" s="2" t="n"/>
       <c r="J470" s="2" t="n"/>
       <c r="K470" s="2" t="n"/>
       <c r="L470" s="2" t="n"/>
-      <c r="M470" s="2" t="n"/>
+      <c r="M470" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -21928,7 +21924,7 @@
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>GE-17.3</t>
+          <t>GE-15.1</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
@@ -21938,7 +21934,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>主电过流保护</t>
+          <t>输出不动作</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -21948,7 +21944,7 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1</t>
+          <t>4.3.4.1</t>
         </is>
       </c>
       <c r="G471" s="2" t="inlineStr">
@@ -21958,7 +21954,7 @@
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>主电过流保护</t>
+          <t>自检期间受控设备与输出接点均不动作</t>
         </is>
       </c>
       <c r="I471" s="2" t="n"/>
@@ -21973,7 +21969,7 @@
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>GE-17.4</t>
+          <t>GE-15.2</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
@@ -21983,7 +21979,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>转换不误动作</t>
+          <t>不阻断灭火控制</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -21993,7 +21989,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1</t>
+          <t>4.3.4.1</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
@@ -22003,7 +21999,7 @@
       </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>转换不误动作</t>
+          <t>超 1 min 或不能自动停止时不影响非自检部位及本机灭火控制功能</t>
         </is>
       </c>
       <c r="I472" s="2" t="n"/>
@@ -22018,7 +22014,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>GE-18</t>
+          <t>GE-16</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -22028,27 +22024,27 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>备电容量</t>
+          <t>面板自检</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.1 ↔ 5.3.4</t>
+          <t>4.3.4.2 ↔ 5.3.3</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
+          <t>手动检查音响、指示灯、显示器</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>全程正常工作</t>
+          <t>全部可手动检查</t>
         </is>
       </c>
       <c r="I473" s="2" t="n"/>
@@ -22067,7 +22063,7 @@
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>GE-19</t>
+          <t>GE-17</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
@@ -22075,11 +22071,7 @@
           <t>气体灭火控制器</t>
         </is>
       </c>
-      <c r="D474" s="2" t="inlineStr">
-        <is>
-          <t>电压容限</t>
-        </is>
-      </c>
+      <c r="D474" s="2" t="inlineStr"/>
       <c r="E474" s="2" t="inlineStr">
         <is>
           <t>P0</t>
@@ -22087,17 +22079,17 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>4.3.5.2 ↔ 5.3.4</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
+          <t>主备电转换（总案）——断主电/恢复主电</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
         <is>
-          <t>全范围正常工作</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I474" s="2" t="n"/>
@@ -22106,7 +22098,7 @@
       <c r="L474" s="2" t="n"/>
       <c r="M474" s="2" t="inlineStr">
         <is>
-          <t>已原子</t>
+          <t>总案</t>
         </is>
       </c>
     </row>
@@ -22116,7 +22108,7 @@
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>GE-20</t>
+          <t>GE-17.1</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
@@ -22126,38 +22118,34 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>现场数据断电保存</t>
+          <t>自动转换</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.2.4 b)</t>
+          <t>4.3.5.1</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>断电 14 d 后上电检查现场设置数据</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
+          <t>自动转换</t>
         </is>
       </c>
       <c r="I475" s="2" t="n"/>
       <c r="J475" s="2" t="n"/>
       <c r="K475" s="2" t="n"/>
       <c r="L475" s="2" t="n"/>
-      <c r="M475" s="2" t="inlineStr">
-        <is>
-          <t>已原子</t>
-        </is>
-      </c>
+      <c r="M475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -22165,7 +22153,7 @@
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>GE-21</t>
+          <t>GE-17.2</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
@@ -22175,38 +22163,34 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>数据输入防意外执行</t>
+          <t>状态指示</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>4.1.5.1.3</t>
+          <t>4.3.5.1</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>各状态下输入数据</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>不引起程序意外执行</t>
+          <t>状态指示</t>
         </is>
       </c>
       <c r="I476" s="2" t="n"/>
       <c r="J476" s="2" t="n"/>
       <c r="K476" s="2" t="n"/>
       <c r="L476" s="2" t="n"/>
-      <c r="M476" s="2" t="inlineStr">
-        <is>
-          <t>已原子</t>
-        </is>
-      </c>
+      <c r="M476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -22214,44 +22198,44 @@
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>EX-01</t>
+          <t>GE-17.3</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
-        </is>
-      </c>
-      <c r="D477" s="2" t="inlineStr"/>
+          <t>气体灭火控制器</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>主电过流保护</t>
+        </is>
+      </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>4.3.5.1</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>外观与包装（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>主电过流保护</t>
         </is>
       </c>
       <c r="I477" s="2" t="n"/>
       <c r="J477" s="2" t="n"/>
       <c r="K477" s="2" t="n"/>
       <c r="L477" s="2" t="n"/>
-      <c r="M477" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -22259,27 +22243,27 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>EX-01.1</t>
+          <t>GE-17.4</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>包装与随机件</t>
+          <t>转换不误动作</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>4.3.5.1</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
@@ -22289,7 +22273,7 @@
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>完整包装、产品标志、合格标志、说明书</t>
+          <t>转换不误动作</t>
         </is>
       </c>
       <c r="I478" s="2" t="n"/>
@@ -22304,44 +22288,48 @@
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>EX-01.2</t>
+          <t>GE-18</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>表面质量</t>
+          <t>备电容量</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>4.3.5.1 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>备电供电：正常监视 8 h → 启动状态 30 min</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>无腐蚀/脱漆/划伤/毛刺</t>
+          <t>全程正常工作</t>
         </is>
       </c>
       <c r="I479" s="2" t="n"/>
       <c r="J479" s="2" t="n"/>
       <c r="K479" s="2" t="n"/>
       <c r="L479" s="2" t="n"/>
-      <c r="M479" s="2" t="n"/>
+      <c r="M479" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -22349,44 +22337,48 @@
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>EX-01.3</t>
+          <t>GE-19</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>紧固件</t>
+          <t>电压容限</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.2；GB 16806 5.1.5</t>
+          <t>4.3.5.2 ↔ 5.3.4</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>输入 187 V / 220 V / 242 V（频率偏差 ≤±1%）做基本功能试验</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>紧固无松动</t>
+          <t>全范围正常工作</t>
         </is>
       </c>
       <c r="I480" s="2" t="n"/>
       <c r="J480" s="2" t="n"/>
       <c r="K480" s="2" t="n"/>
       <c r="L480" s="2" t="n"/>
-      <c r="M480" s="2" t="n"/>
+      <c r="M480" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -22394,33 +22386,37 @@
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>EX-02</t>
+          <t>GE-20</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
-        </is>
-      </c>
-      <c r="D481" s="2" t="inlineStr"/>
+          <t>气体灭火控制器</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>现场数据断电保存</t>
+        </is>
+      </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
+          <t>4.1.5.2.4 b)</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>供电与接地（总案）</t>
+          <t>断电 14 d 后上电检查现场设置数据</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>保存 ≥14 d（或恢复供电 1 h 内可恢复）</t>
         </is>
       </c>
       <c r="I481" s="2" t="n"/>
@@ -22429,7 +22425,7 @@
       <c r="L481" s="2" t="n"/>
       <c r="M481" s="2" t="inlineStr">
         <is>
-          <t>总案</t>
+          <t>已原子</t>
         </is>
       </c>
     </row>
@@ -22439,44 +22435,48 @@
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>EX-02.1</t>
+          <t>GE-21</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>结构与外观</t>
+          <t>气体灭火控制器</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>主电规格</t>
+          <t>数据输入防意外执行</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.2；GB 16806 4.3.1.1</t>
+          <t>4.1.5.1.3</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>各状态下输入数据</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>主电 AC 220 V/50 Hz</t>
+          <t>不引起程序意外执行</t>
         </is>
       </c>
       <c r="I482" s="2" t="n"/>
       <c r="J482" s="2" t="n"/>
       <c r="K482" s="2" t="n"/>
       <c r="L482" s="2" t="n"/>
-      <c r="M482" s="2" t="n"/>
+      <c r="M482" s="2" t="inlineStr">
+        <is>
+          <t>已原子</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>EX-02.2</t>
+          <t>EX-01</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
@@ -22492,11 +22492,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D483" s="2" t="inlineStr">
-        <is>
-          <t>保护接地</t>
-        </is>
-      </c>
+      <c r="D483" s="2" t="inlineStr"/>
       <c r="E483" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22504,24 +22500,28 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.3</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>外观与包装（总案）</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>保护接地</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I483" s="2" t="n"/>
       <c r="J483" s="2" t="n"/>
       <c r="K483" s="2" t="n"/>
       <c r="L483" s="2" t="n"/>
-      <c r="M483" s="2" t="n"/>
+      <c r="M483" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>EX-02.3</t>
+          <t>EX-01.1</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>部件供电</t>
+          <t>包装与随机件</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.4</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>部件供电优先 DC 24 V</t>
+          <t>完整包装、产品标志、合格标志、说明书</t>
         </is>
       </c>
       <c r="I484" s="2" t="n"/>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>EX-02.4</t>
+          <t>EX-01.2</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>电源接线端子</t>
+          <t>表面质量</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.2</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>电源线独立接线端子</t>
+          <t>无腐蚀/脱漆/划伤/毛刺</t>
         </is>
       </c>
       <c r="I485" s="2" t="n"/>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>EX-03</t>
+          <t>EX-01.3</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
@@ -22627,7 +22627,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D486" s="2" t="inlineStr"/>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>紧固件</t>
+        </is>
+      </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22635,28 +22639,24 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.5/5.3.8</t>
+          <t>GB 4717 5.2；GB 16806 5.1.5</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>按键与面板（报警控制器）（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>紧固无松动</t>
         </is>
       </c>
       <c r="I486" s="2" t="n"/>
       <c r="J486" s="2" t="n"/>
       <c r="K486" s="2" t="n"/>
       <c r="L486" s="2" t="n"/>
-      <c r="M486" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>EX-03.1</t>
+          <t>EX-02</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
@@ -22672,11 +22672,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D487" s="2" t="inlineStr">
-        <is>
-          <t>按键尺寸间隔</t>
-        </is>
-      </c>
+      <c r="D487" s="2" t="inlineStr"/>
       <c r="E487" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22684,24 +22680,28 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.5</t>
+          <t>GB 4717 5.3.1.2～5.3.1.4；GB 16806 4.3.1.1</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>供电与接地（总案）</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
         <is>
-          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I487" s="2" t="n"/>
       <c r="J487" s="2" t="n"/>
       <c r="K487" s="2" t="n"/>
       <c r="L487" s="2" t="n"/>
-      <c r="M487" s="2" t="n"/>
+      <c r="M487" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>EX-03.2</t>
+          <t>EX-02.1</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>布局排列</t>
+          <t>主电规格</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.5</t>
+          <t>GB 4717 5.3.1.2；GB 16806 4.3.1.1</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
@@ -22739,7 +22739,7 @@
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>指示灯/按键按标准图 1/图 2 顺序排列</t>
+          <t>主电 AC 220 V/50 Hz</t>
         </is>
       </c>
       <c r="I488" s="2" t="n"/>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>EX-03.3</t>
+          <t>EX-02.2</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>中文标注</t>
+          <t>保护接地</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -22774,7 +22774,7 @@
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.8</t>
+          <t>GB 4717 5.3.1.3</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
-          <t>中文标注</t>
+          <t>保护接地</t>
         </is>
       </c>
       <c r="I489" s="2" t="n"/>
@@ -22799,7 +22799,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>EX-03.4</t>
+          <t>EX-02.3</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>按键提示音</t>
+          <t>部件供电</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.8</t>
+          <t>GB 4717 5.3.1.4</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
@@ -22829,7 +22829,7 @@
       </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
-          <t>按键有提示音</t>
+          <t>部件供电优先 DC 24 V</t>
         </is>
       </c>
       <c r="I490" s="2" t="n"/>
@@ -22844,7 +22844,7 @@
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>EX-04</t>
+          <t>EX-02.4</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
@@ -22852,7 +22852,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D491" s="2" t="inlineStr"/>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>电源接线端子</t>
+        </is>
+      </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22860,28 +22864,24 @@
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.2.1；GB 16806 4.1.3.2.1</t>
+          <t>GB 4717 5.3.1.2</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>指示灯颜色（总案，两标准分列）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>电源线独立接线端子</t>
         </is>
       </c>
       <c r="I491" s="2" t="n"/>
       <c r="J491" s="2" t="n"/>
       <c r="K491" s="2" t="n"/>
       <c r="L491" s="2" t="n"/>
-      <c r="M491" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>EX-04.1</t>
+          <t>EX-03</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
@@ -22897,11 +22897,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
-        <is>
-          <t>报警控制器灯色</t>
-        </is>
-      </c>
+      <c r="D492" s="2" t="inlineStr"/>
       <c r="E492" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22909,24 +22905,28 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.2.1</t>
+          <t>GB 4717 5.3.1.5/5.3.8</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>按键与面板（报警控制器）（总案）</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I492" s="2" t="n"/>
       <c r="J492" s="2" t="n"/>
       <c r="K492" s="2" t="n"/>
       <c r="L492" s="2" t="n"/>
-      <c r="M492" s="2" t="n"/>
+      <c r="M492" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -22934,7 +22934,7 @@
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>EX-04.2</t>
+          <t>EX-03.1</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器灯色</t>
+          <t>按键尺寸间隔</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.2.1</t>
+          <t>GB 4717 5.3.1.5</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电</t>
+          <t>按键 ≥12 mm×12 mm（或 φ12）、间隔 ≥10 mm</t>
         </is>
       </c>
       <c r="I493" s="2" t="n"/>
@@ -22979,7 +22979,7 @@
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>EX-05</t>
+          <t>EX-03.2</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
@@ -22987,7 +22987,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D494" s="2" t="inlineStr"/>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>布局排列</t>
+        </is>
+      </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -22995,28 +22999,24 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.2.2；GB 16806 4.1.3.2</t>
+          <t>GB 4717 5.3.1.5</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>指示灯可见性与闪动参数（总案，两标准分列）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>指示灯/按键按标准图 1/图 2 顺序排列</t>
         </is>
       </c>
       <c r="I494" s="2" t="n"/>
       <c r="J494" s="2" t="n"/>
       <c r="K494" s="2" t="n"/>
       <c r="L494" s="2" t="n"/>
-      <c r="M494" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>EX-05.1</t>
+          <t>EX-03.3</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>报警控制器可见性</t>
+          <t>中文标注</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.2.2</t>
+          <t>GB 4717 5.3.8</t>
         </is>
       </c>
       <c r="G495" s="2" t="inlineStr">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>100～500 lx、22.5°，0.8 m/3 m</t>
+          <t>中文标注</t>
         </is>
       </c>
       <c r="I495" s="2" t="n"/>
@@ -23069,7 +23069,7 @@
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>EX-05.2</t>
+          <t>EX-03.4</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>气灭控制器可见性</t>
+          <t>按键提示音</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.2</t>
+          <t>GB 4717 5.3.8</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>5～500 lx、22.5°、3 m</t>
+          <t>按键有提示音</t>
         </is>
       </c>
       <c r="I496" s="2" t="n"/>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>EX-05.3</t>
+          <t>EX-04</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
@@ -23122,11 +23122,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D497" s="2" t="inlineStr">
-        <is>
-          <t>气灭闪动参数</t>
-        </is>
-      </c>
+      <c r="D497" s="2" t="inlineStr"/>
       <c r="E497" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23134,24 +23130,28 @@
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.2</t>
+          <t>GB 4717 5.3.2.1；GB 16806 4.1.3.2.1</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>指示灯颜色（总案，两标准分列）</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I497" s="2" t="n"/>
       <c r="J497" s="2" t="n"/>
       <c r="K497" s="2" t="n"/>
       <c r="L497" s="2" t="n"/>
-      <c r="M497" s="2" t="n"/>
+      <c r="M497" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>EX-05.4</t>
+          <t>EX-04.1</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>气灭一灯兼显规则</t>
+          <t>报警控制器灯色</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23179,7 +23179,7 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.2</t>
+          <t>GB 4717 5.3.2.1</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -23189,7 +23189,7 @@
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮</t>
+          <t>红=火警/监管/反馈/启动/延时/检查开启，黄=故障/系统故障/屏蔽/消音，绿=主备电/手动/自动/停止</t>
         </is>
       </c>
       <c r="I498" s="2" t="n"/>
@@ -23204,7 +23204,7 @@
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>EX-06</t>
+          <t>EX-04.2</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
@@ -23212,7 +23212,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D499" s="2" t="inlineStr"/>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器灯色</t>
+        </is>
+      </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23220,28 +23224,24 @@
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.8/5.3.1.9</t>
+          <t>GB 16806 4.1.3.2.1</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>外壳防护与燃烧（报警控制器）（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>红=火警/反馈/启动和延时，黄=故障/屏蔽/回路自检，绿=主备电</t>
         </is>
       </c>
       <c r="I499" s="2" t="n"/>
       <c r="J499" s="2" t="n"/>
       <c r="K499" s="2" t="n"/>
       <c r="L499" s="2" t="n"/>
-      <c r="M499" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>EX-06.1</t>
+          <t>EX-05</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
@@ -23257,11 +23257,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D500" s="2" t="inlineStr">
-        <is>
-          <t>防护等级</t>
-        </is>
-      </c>
+      <c r="D500" s="2" t="inlineStr"/>
       <c r="E500" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23269,24 +23265,28 @@
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.8</t>
+          <t>GB 4717 5.3.2.2；GB 16806 4.1.3.2</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>指示灯可见性与闪动参数（总案，两标准分列）</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>≥IP30</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I500" s="2" t="n"/>
       <c r="J500" s="2" t="n"/>
       <c r="K500" s="2" t="n"/>
       <c r="L500" s="2" t="n"/>
-      <c r="M500" s="2" t="n"/>
+      <c r="M500" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>EX-06.2</t>
+          <t>EX-05.1</t>
         </is>
       </c>
       <c r="C501" s="2" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>非金属外壳燃烧</t>
+          <t>报警控制器可见性</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.1.9</t>
+          <t>GB 4717 5.3.2.2</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
+          <t>100～500 lx、22.5°，0.8 m/3 m</t>
         </is>
       </c>
       <c r="I501" s="2" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>EX-07</t>
+          <t>EX-05.2</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
@@ -23347,7 +23347,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D502" s="2" t="inlineStr"/>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>气灭控制器可见性</t>
+        </is>
+      </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23355,28 +23359,24 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.4；GB 16806 4.1.3.4.1</t>
+          <t>GB 16806 4.1.3.2</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>音响器件（总案，两标准分列）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>5～500 lx、22.5°、3 m</t>
         </is>
       </c>
       <c r="I502" s="2" t="n"/>
       <c r="J502" s="2" t="n"/>
       <c r="K502" s="2" t="n"/>
       <c r="L502" s="2" t="n"/>
-      <c r="M502" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>EX-07.1</t>
+          <t>EX-05.3</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>报警控制器声压级</t>
+          <t>气灭闪动参数</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.4</t>
+          <t>GB 16806 4.1.3.2</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>1 m 处 65～105 dB(A)</t>
+          <t>闪动灯单次点亮 ≥0.25 s，启动灯闪频 ≥1 Hz、故障灯 ≥0.2 Hz</t>
         </is>
       </c>
       <c r="I503" s="2" t="n"/>
@@ -23429,7 +23429,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>EX-07.2</t>
+          <t>EX-05.4</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>报警控制器接线防脱</t>
+          <t>气灭一灯兼显规则</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -23449,7 +23449,7 @@
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.4</t>
+          <t>GB 16806 4.1.3.2</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>接线防脱耐 50 N</t>
+          <t>一灯兼显故障/屏蔽/自检时：故障闪亮、屏蔽与自检常亮</t>
         </is>
       </c>
       <c r="I504" s="2" t="n"/>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>EX-07.3</t>
+          <t>EX-06</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr">
@@ -23482,11 +23482,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D505" s="2" t="inlineStr">
-        <is>
-          <t>气灭控制器声压级</t>
-        </is>
-      </c>
+      <c r="D505" s="2" t="inlineStr"/>
       <c r="E505" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23494,24 +23490,28 @@
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.4.1</t>
+          <t>GB 4717 5.3.1.8/5.3.1.9</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>外壳防护与燃烧（报警控制器）（总案）</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>1 m 处 &gt;65 且 &lt;115 dB(A)</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I505" s="2" t="n"/>
       <c r="J505" s="2" t="n"/>
       <c r="K505" s="2" t="n"/>
       <c r="L505" s="2" t="n"/>
-      <c r="M505" s="2" t="n"/>
+      <c r="M505" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>EX-07.4</t>
+          <t>EX-06.1</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
@@ -23529,7 +23529,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>低压发声</t>
+          <t>防护等级</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>两标准</t>
+          <t>GB 4717 5.3.1.8</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>两者：85% 额定电压下正常发声</t>
+          <t>≥IP30</t>
         </is>
       </c>
       <c r="I506" s="2" t="n"/>
@@ -23564,7 +23564,7 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>EX-08</t>
+          <t>EX-06.2</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
@@ -23572,7 +23572,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D507" s="2" t="inlineStr"/>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>非金属外壳燃烧</t>
+        </is>
+      </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23580,28 +23584,24 @@
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+          <t>GB 4717 5.3.1.9</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>过负荷/熔断器（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>非金属外壳过附录 A 燃烧试验（样块 80×10 mm，燃烧长度 ≤50 mm）</t>
         </is>
       </c>
       <c r="I507" s="2" t="n"/>
       <c r="J507" s="2" t="n"/>
       <c r="K507" s="2" t="n"/>
       <c r="L507" s="2" t="n"/>
-      <c r="M507" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M507" s="2" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>EX-08.1</t>
+          <t>EX-07</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
@@ -23617,11 +23617,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D508" s="2" t="inlineStr">
-        <is>
-          <t>保护设定</t>
-        </is>
-      </c>
+      <c r="D508" s="2" t="inlineStr"/>
       <c r="E508" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23629,24 +23625,28 @@
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+          <t>GB 4717 5.3.4；GB 16806 4.1.3.4.1</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>音响器件（总案，两标准分列）</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I508" s="2" t="n"/>
       <c r="J508" s="2" t="n"/>
       <c r="K508" s="2" t="n"/>
       <c r="L508" s="2" t="n"/>
-      <c r="M508" s="2" t="n"/>
+      <c r="M508" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>EX-08.2</t>
+          <t>EX-07.1</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
@@ -23664,7 +23664,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>参数标识</t>
+          <t>报警控制器声压级</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
+          <t>GB 4717 5.3.4</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
+          <t>1 m 处 65～105 dB(A)</t>
         </is>
       </c>
       <c r="I509" s="2" t="n"/>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>EX-09</t>
+          <t>EX-07.2</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
@@ -23707,7 +23707,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D510" s="2" t="inlineStr"/>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>报警控制器接线防脱</t>
+        </is>
+      </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23715,28 +23719,24 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
+          <t>GB 4717 5.3.4</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>端子与导线（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>接线防脱耐 50 N</t>
         </is>
       </c>
       <c r="I510" s="2" t="n"/>
       <c r="J510" s="2" t="n"/>
       <c r="K510" s="2" t="n"/>
       <c r="L510" s="2" t="n"/>
-      <c r="M510" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>EX-09.1</t>
+          <t>EX-07.3</t>
         </is>
       </c>
       <c r="C511" s="2" t="inlineStr">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>端子编号</t>
+          <t>气灭控制器声压级</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.6</t>
+          <t>GB 16806 4.1.3.4.1</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>端子编号清晰</t>
+          <t>1 m 处 &gt;65 且 &lt;115 dB(A)</t>
         </is>
       </c>
       <c r="I511" s="2" t="n"/>
@@ -23789,7 +23789,7 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>EX-09.2</t>
+          <t>EX-07.4</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>电池线色</t>
+          <t>低压发声</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -23809,7 +23809,7 @@
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.3.7.2</t>
+          <t>两标准</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>电池正极红线、负极黑/蓝线</t>
+          <t>两者：85% 额定电压下正常发声</t>
         </is>
       </c>
       <c r="I512" s="2" t="n"/>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>EX-09.3</t>
+          <t>EX-08</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
@@ -23842,11 +23842,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D513" s="2" t="inlineStr">
-        <is>
-          <t>配线阻燃</t>
-        </is>
-      </c>
+      <c r="D513" s="2" t="inlineStr"/>
       <c r="E513" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23854,24 +23850,28 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.9</t>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>过负荷/熔断器（总案）</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I513" s="2" t="n"/>
       <c r="J513" s="2" t="n"/>
       <c r="K513" s="2" t="n"/>
       <c r="L513" s="2" t="n"/>
-      <c r="M513" s="2" t="n"/>
+      <c r="M513" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -23879,7 +23879,7 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>EX-10</t>
+          <t>EX-08.1</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
@@ -23887,7 +23887,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D514" s="2" t="inlineStr"/>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>保护设定</t>
+        </is>
+      </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23895,28 +23899,24 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>元件温升（气灭控制器）（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>保护设定 ≤2 倍额定电流（&gt;6 A 时 1.5 倍）</t>
         </is>
       </c>
       <c r="I514" s="2" t="n"/>
       <c r="J514" s="2" t="n"/>
       <c r="K514" s="2" t="n"/>
       <c r="L514" s="2" t="n"/>
-      <c r="M514" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>EX-10.1</t>
+          <t>EX-08.2</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>主要元件温升</t>
+          <t>参数标识</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>GB 4717 5.3.5；GB 16806 4.1.3.5</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>主要元件温升 ≤60℃</t>
+          <t>参数标识清晰（GB 4717 另要求字高 ≥1.5 mm、DC/AC 分标）</t>
         </is>
       </c>
       <c r="I515" s="2" t="n"/>
@@ -23969,7 +23969,7 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>EX-10.2</t>
+          <t>EX-09</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
@@ -23977,11 +23977,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D516" s="2" t="inlineStr">
-        <is>
-          <t>变压器表面</t>
-        </is>
-      </c>
+      <c r="D516" s="2" t="inlineStr"/>
       <c r="E516" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -23989,24 +23985,28 @@
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>GB 4717 5.3.6/5.3.7.2；GB 16806 4.1.3.6/4.1.3.7.1/4.1.3.9</t>
         </is>
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>端子与导线（总案）</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>变压器等表面 ≤90℃（25±3℃）</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I516" s="2" t="n"/>
       <c r="J516" s="2" t="n"/>
       <c r="K516" s="2" t="n"/>
       <c r="L516" s="2" t="n"/>
-      <c r="M516" s="2" t="n"/>
+      <c r="M516" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>EX-10.3</t>
+          <t>EX-09.1</t>
         </is>
       </c>
       <c r="C517" s="2" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>电池周围</t>
+          <t>端子编号</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 4.1.3.10</t>
+          <t>GB 4717 5.3.6</t>
         </is>
       </c>
       <c r="G517" s="2" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>电池周围 ≤45℃</t>
+          <t>端子编号清晰</t>
         </is>
       </c>
       <c r="I517" s="2" t="n"/>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>EX-09.2</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
@@ -24067,7 +24067,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D518" s="2" t="inlineStr"/>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>电池线色</t>
+        </is>
+      </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -24075,28 +24079,24 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>GB 4717 5.3.7.2</t>
         </is>
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>软件资料（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>电池正极红线、负极黑/蓝线</t>
         </is>
       </c>
       <c r="I518" s="2" t="n"/>
       <c r="J518" s="2" t="n"/>
       <c r="K518" s="2" t="n"/>
       <c r="L518" s="2" t="n"/>
-      <c r="M518" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>EX-11.1</t>
+          <t>EX-09.3</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>资料齐备</t>
+          <t>配线阻燃</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>GB 16806 4.1.3.9</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号</t>
+          <t>（GB 16806）主电路配线阻燃（工作温度 &gt;105℃）、线槽氧指数 ≥28</t>
         </is>
       </c>
       <c r="I519" s="2" t="n"/>
@@ -24149,7 +24149,7 @@
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>EX-11.2</t>
+          <t>EX-10</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
@@ -24157,11 +24157,7 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D520" s="2" t="inlineStr">
-        <is>
-          <t>存储介质</t>
-        </is>
-      </c>
+      <c r="D520" s="2" t="inlineStr"/>
       <c r="E520" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -24169,24 +24165,28 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>元件温升（气灭控制器）（总案）</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>程序存于不易丢失存储器</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I520" s="2" t="n"/>
       <c r="J520" s="2" t="n"/>
       <c r="K520" s="2" t="n"/>
       <c r="L520" s="2" t="n"/>
-      <c r="M520" s="2" t="n"/>
+      <c r="M520" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>EX-11.3</t>
+          <t>EX-10.1</t>
         </is>
       </c>
       <c r="C521" s="2" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>防改动</t>
+          <t>主要元件温升</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
+          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>软件防非专门人员改动</t>
+          <t>主要元件温升 ≤60℃</t>
         </is>
       </c>
       <c r="I521" s="2" t="n"/>
@@ -24239,7 +24239,7 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>EX-10.2</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
@@ -24247,7 +24247,11 @@
           <t>结构与外观</t>
         </is>
       </c>
-      <c r="D522" s="2" t="inlineStr"/>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>变压器表面</t>
+        </is>
+      </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -24255,28 +24259,24 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 8；GB 16806 7</t>
+          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>产品标志</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
+          <t>变压器等表面 ≤90℃（25±3℃）</t>
         </is>
       </c>
       <c r="I522" s="2" t="n"/>
       <c r="J522" s="2" t="n"/>
       <c r="K522" s="2" t="n"/>
       <c r="L522" s="2" t="n"/>
-      <c r="M522" s="2" t="inlineStr">
-        <is>
-          <t>已原子（单次标志核对）</t>
-        </is>
-      </c>
+      <c r="M522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -24284,44 +24284,44 @@
       </c>
       <c r="B523" s="2" t="inlineStr">
         <is>
-          <t>TT-01</t>
+          <t>EX-10.3</t>
         </is>
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
-        </is>
-      </c>
-      <c r="D523" s="2" t="inlineStr"/>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>电池周围</t>
+        </is>
+      </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.13；GB 16806 5.5/6.16</t>
+          <t>GB 16806 4.1.3.10</t>
         </is>
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>绝缘电阻（总案）——500 V DC、60 s</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>电池周围 ≤45℃</t>
         </is>
       </c>
       <c r="I523" s="2" t="n"/>
       <c r="J523" s="2" t="n"/>
       <c r="K523" s="2" t="n"/>
       <c r="L523" s="2" t="n"/>
-      <c r="M523" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M523" s="2" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -24329,44 +24329,44 @@
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>TT-01.1</t>
+          <t>EX-11</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
-        </is>
-      </c>
-      <c r="D524" s="2" t="inlineStr">
-        <is>
-          <t>报警：端子-机壳</t>
-        </is>
-      </c>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr"/>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.13</t>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>软件资料（总案）</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
-          <t>端子-机壳 ≥20 MΩ</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I524" s="2" t="n"/>
       <c r="J524" s="2" t="n"/>
       <c r="K524" s="2" t="n"/>
       <c r="L524" s="2" t="n"/>
-      <c r="M524" s="2" t="n"/>
+      <c r="M524" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -24374,27 +24374,27 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>TT-01.2</t>
+          <t>EX-11.1</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>报警：电源-机壳</t>
+          <t>资料齐备</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.13</t>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="G525" s="2" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>电源-机壳 ≥50 MΩ</t>
+          <t>主程序流程/结构图、模块说明、存储器地址分配、软件版本号</t>
         </is>
       </c>
       <c r="I525" s="2" t="n"/>
@@ -24419,27 +24419,27 @@
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>TT-01.3</t>
+          <t>EX-11.2</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
+          <t>结构与外观</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>气灭：绝缘电阻</t>
+          <t>存储介质</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 5.5/6.16</t>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
@@ -24449,7 +24449,7 @@
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>500 V DC、60 s，≥100 MΩ</t>
+          <t>程序存于不易丢失存储器</t>
         </is>
       </c>
       <c r="I526" s="2" t="n"/>
@@ -24464,44 +24464,44 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>TT-02</t>
+          <t>EX-11.3</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
-        </is>
-      </c>
-      <c r="D527" s="2" t="inlineStr"/>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>防改动</t>
+        </is>
+      </c>
       <c r="E527" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.14；GB 16806 5.6/6.17</t>
+          <t>GB 4717 5.4.15；GB 16806 4.1.5</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>泄漏电流（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>软件防非专门人员改动</t>
         </is>
       </c>
       <c r="I527" s="2" t="n"/>
       <c r="J527" s="2" t="n"/>
       <c r="K527" s="2" t="n"/>
       <c r="L527" s="2" t="n"/>
-      <c r="M527" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M527" s="2" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -24509,44 +24509,44 @@
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>TT-02.1</t>
+          <t>EX-12</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>型式试验</t>
-        </is>
-      </c>
-      <c r="D528" s="2" t="inlineStr">
-        <is>
-          <t>报警：泄漏电流</t>
-        </is>
-      </c>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr"/>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.14</t>
+          <t>GB 4717 8；GB 16806 7</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>产品标志</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>同左（5.14，原文如此）</t>
+          <t>名称型号、标准编号、生产者、制造日期与编号、供电参数、软件版本号、质检合格标志</t>
         </is>
       </c>
       <c r="I528" s="2" t="n"/>
       <c r="J528" s="2" t="n"/>
       <c r="K528" s="2" t="n"/>
       <c r="L528" s="2" t="n"/>
-      <c r="M528" s="2" t="n"/>
+      <c r="M528" s="2" t="inlineStr">
+        <is>
+          <t>已原子（单次标志核对）</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>TT-02.2</t>
+          <t>TT-01</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
@@ -24562,11 +24562,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D529" s="2" t="inlineStr">
-        <is>
-          <t>气灭：泄漏电流</t>
-        </is>
-      </c>
+      <c r="D529" s="2" t="inlineStr"/>
       <c r="E529" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24574,24 +24570,28 @@
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 5.6/6.17</t>
+          <t>GB 4717 5.13；GB 16806 5.5/6.16</t>
         </is>
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>绝缘电阻（总案）——500 V DC、60 s</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
         <is>
-          <t>1.06 倍额定电压，≤0.5 mA</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I529" s="2" t="n"/>
       <c r="J529" s="2" t="n"/>
       <c r="K529" s="2" t="n"/>
       <c r="L529" s="2" t="n"/>
-      <c r="M529" s="2" t="n"/>
+      <c r="M529" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>TT-03</t>
+          <t>TT-01.1</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
@@ -24609,7 +24609,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>电气强度</t>
+          <t>报警：端子-机壳</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -24619,28 +24619,24 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 5.7/6.18</t>
+          <t>GB 4717 5.13</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>报警控制器表 4 未列 5.15 不做；气灭控制器做</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）</t>
+          <t>端子-机壳 ≥20 MΩ</t>
         </is>
       </c>
       <c r="I530" s="2" t="n"/>
       <c r="J530" s="2" t="n"/>
       <c r="K530" s="2" t="n"/>
       <c r="L530" s="2" t="n"/>
-      <c r="M530" s="2" t="inlineStr">
-        <is>
-          <t>已原子（仅气灭一侧）</t>
-        </is>
-      </c>
+      <c r="M530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -24648,7 +24644,7 @@
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>TT-04</t>
+          <t>TT-01.2</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
@@ -24656,7 +24652,11 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D531" s="2" t="inlineStr"/>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>报警：电源-机壳</t>
+        </is>
+      </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24664,28 +24664,24 @@
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.16；GB 16806 6.19</t>
+          <t>GB 4717 5.13</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>射频电磁场辐射（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>电源-机壳 ≥50 MΩ</t>
         </is>
       </c>
       <c r="I531" s="2" t="n"/>
       <c r="J531" s="2" t="n"/>
       <c r="K531" s="2" t="n"/>
       <c r="L531" s="2" t="n"/>
-      <c r="M531" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M531" s="2" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -24693,7 +24689,7 @@
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>TT-04.1</t>
+          <t>TT-01.3</t>
         </is>
       </c>
       <c r="C532" s="2" t="inlineStr">
@@ -24703,7 +24699,7 @@
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>报警</t>
+          <t>气灭：绝缘电阻</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -24713,7 +24709,7 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.16</t>
+          <t>GB 16806 5.5/6.16</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
@@ -24723,7 +24719,7 @@
       </c>
       <c r="H532" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.16）</t>
+          <t>500 V DC、60 s，≥100 MΩ</t>
         </is>
       </c>
       <c r="I532" s="2" t="n"/>
@@ -24738,7 +24734,7 @@
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>TT-04.2</t>
+          <t>TT-02</t>
         </is>
       </c>
       <c r="C533" s="2" t="inlineStr">
@@ -24746,11 +24742,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D533" s="2" t="inlineStr">
-        <is>
-          <t>气灭</t>
-        </is>
-      </c>
+      <c r="D533" s="2" t="inlineStr"/>
       <c r="E533" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24758,24 +24750,28 @@
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.19</t>
+          <t>GB 4717 5.14；GB 16806 5.6/6.17</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>泄漏电流（总案）</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>10 V/m、80～1 000 MHz、80%AM(1 kHz)</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I533" s="2" t="n"/>
       <c r="J533" s="2" t="n"/>
       <c r="K533" s="2" t="n"/>
       <c r="L533" s="2" t="n"/>
-      <c r="M533" s="2" t="n"/>
+      <c r="M533" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -24783,7 +24779,7 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>TT-05</t>
+          <t>TT-02.1</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
@@ -24791,7 +24787,11 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D534" s="2" t="inlineStr"/>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>报警：泄漏电流</t>
+        </is>
+      </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24799,28 +24799,24 @@
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.17；GB 16806 6.20</t>
+          <t>GB 4717 5.14</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>射频传导骚扰（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>同左（5.14，原文如此）</t>
         </is>
       </c>
       <c r="I534" s="2" t="n"/>
       <c r="J534" s="2" t="n"/>
       <c r="K534" s="2" t="n"/>
       <c r="L534" s="2" t="n"/>
-      <c r="M534" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -24828,7 +24824,7 @@
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>TT-05.1</t>
+          <t>TT-02.2</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
@@ -24838,7 +24834,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>报警</t>
+          <t>气灭：泄漏电流</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -24848,7 +24844,7 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.17</t>
+          <t>GB 16806 5.6/6.17</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
@@ -24858,7 +24854,7 @@
       </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>140 dBμV、0.15～100 MHz</t>
+          <t>1.06 倍额定电压，≤0.5 mA</t>
         </is>
       </c>
       <c r="I535" s="2" t="n"/>
@@ -24873,7 +24869,7 @@
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>TT-05.2</t>
+          <t>TT-03</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
@@ -24883,7 +24879,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>气灭</t>
+          <t>电气强度</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -24893,24 +24889,28 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.20</t>
+          <t>GB 16806 5.7/6.18</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>报警控制器表 4 未列 5.15 不做；气灭控制器做</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>140 dBμV、0.15～80 MHz</t>
+          <t>1 250 V/50 Hz、60 s、升降压 100～500 V/s、不击穿（≤20 mA）</t>
         </is>
       </c>
       <c r="I536" s="2" t="n"/>
       <c r="J536" s="2" t="n"/>
       <c r="K536" s="2" t="n"/>
       <c r="L536" s="2" t="n"/>
-      <c r="M536" s="2" t="n"/>
+      <c r="M536" s="2" t="inlineStr">
+        <is>
+          <t>已原子（仅气灭一侧）</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>TT-06</t>
+          <t>TT-04</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
@@ -24934,12 +24934,12 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.18；GB 16806 6.21</t>
+          <t>GB 4717 5.16；GB 16806 6.19</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>静电放电（总案）</t>
+          <t>射频电磁场辐射（总案）</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>TT-06.1</t>
+          <t>TT-04.1</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.18</t>
+          <t>GB 4717 5.16</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="H538" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.18）</t>
+          <t>同参数（5.16）</t>
         </is>
       </c>
       <c r="I538" s="2" t="n"/>
@@ -25008,7 +25008,7 @@
       </c>
       <c r="B539" s="2" t="inlineStr">
         <is>
-          <t>TT-06.2</t>
+          <t>TT-04.2</t>
         </is>
       </c>
       <c r="C539" s="2" t="inlineStr">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.21</t>
+          <t>GB 16806 6.19</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
@@ -25038,7 +25038,7 @@
       </c>
       <c r="H539" s="2" t="inlineStr">
         <is>
-          <t>空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s</t>
+          <t>10 V/m、80～1 000 MHz、80%AM(1 kHz)</t>
         </is>
       </c>
       <c r="I539" s="2" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>TT-07</t>
+          <t>TT-05</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
@@ -25069,12 +25069,12 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.19；GB 16806 6.22</t>
+          <t>GB 4717 5.17；GB 16806 6.20</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>电快速瞬变（总案）</t>
+          <t>射频传导骚扰（总案）</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="B541" s="2" t="inlineStr">
         <is>
-          <t>TT-07.1</t>
+          <t>TT-05.1</t>
         </is>
       </c>
       <c r="C541" s="2" t="inlineStr">
@@ -25118,7 +25118,7 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.19</t>
+          <t>GB 4717 5.17</t>
         </is>
       </c>
       <c r="G541" s="2" t="inlineStr">
@@ -25128,7 +25128,7 @@
       </c>
       <c r="H541" s="2" t="inlineStr">
         <is>
-          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz</t>
+          <t>140 dBμV、0.15～100 MHz</t>
         </is>
       </c>
       <c r="I541" s="2" t="n"/>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="B542" s="2" t="inlineStr">
         <is>
-          <t>TT-07.2</t>
+          <t>TT-05.2</t>
         </is>
       </c>
       <c r="C542" s="2" t="inlineStr">
@@ -25163,7 +25163,7 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.22</t>
+          <t>GB 16806 6.20</t>
         </is>
       </c>
       <c r="G542" s="2" t="inlineStr">
@@ -25173,7 +25173,7 @@
       </c>
       <c r="H542" s="2" t="inlineStr">
         <is>
-          <t>AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3</t>
+          <t>140 dBμV、0.15～80 MHz</t>
         </is>
       </c>
       <c r="I542" s="2" t="n"/>
@@ -25188,7 +25188,7 @@
       </c>
       <c r="B543" s="2" t="inlineStr">
         <is>
-          <t>TT-08</t>
+          <t>TT-06</t>
         </is>
       </c>
       <c r="C543" s="2" t="inlineStr">
@@ -25204,12 +25204,12 @@
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.20；GB 16806 6.23</t>
+          <t>GB 4717 5.18；GB 16806 6.21</t>
         </is>
       </c>
       <c r="G543" s="2" t="inlineStr">
         <is>
-          <t>浪涌（总案）</t>
+          <t>静电放电（总案）</t>
         </is>
       </c>
       <c r="H543" s="2" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="B544" s="2" t="inlineStr">
         <is>
-          <t>TT-08.1</t>
+          <t>TT-06.1</t>
         </is>
       </c>
       <c r="C544" s="2" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.20</t>
+          <t>GB 4717 5.18</t>
         </is>
       </c>
       <c r="G544" s="2" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="H544" s="2" t="inlineStr">
         <is>
-          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次</t>
+          <t>同参数（5.18）</t>
         </is>
       </c>
       <c r="I544" s="2" t="n"/>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B545" s="2" t="inlineStr">
         <is>
-          <t>TT-08.2</t>
+          <t>TT-06.2</t>
         </is>
       </c>
       <c r="C545" s="2" t="inlineStr">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.23</t>
+          <t>GB 16806 6.21</t>
         </is>
       </c>
       <c r="G545" s="2" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="H545" s="2" t="inlineStr">
         <is>
-          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次</t>
+          <t>空气 8 kV / 接触 6 kV、每点 10 次、间隔 ≥1 s</t>
         </is>
       </c>
       <c r="I545" s="2" t="n"/>
@@ -25323,7 +25323,7 @@
       </c>
       <c r="B546" s="2" t="inlineStr">
         <is>
-          <t>TT-09</t>
+          <t>TT-07</t>
         </is>
       </c>
       <c r="C546" s="2" t="inlineStr">
@@ -25339,12 +25339,12 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.21；GB 16806 6.24</t>
+          <t>GB 4717 5.19；GB 16806 6.22</t>
         </is>
       </c>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>电源瞬变（总案）</t>
+          <t>电快速瞬变（总案）</t>
         </is>
       </c>
       <c r="H546" s="2" t="inlineStr">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="B547" s="2" t="inlineStr">
         <is>
-          <t>TT-09.1</t>
+          <t>TT-07.1</t>
         </is>
       </c>
       <c r="C547" s="2" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.21</t>
+          <t>GB 4717 5.19</t>
         </is>
       </c>
       <c r="G547" s="2" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="H547" s="2" t="inlineStr">
         <is>
-          <t>通 9 s/断 1 s×500 次</t>
+          <t>AC 线 2 kV/2.5 kHz、其他线 1 kV/5 kHz</t>
         </is>
       </c>
       <c r="I547" s="2" t="n"/>
@@ -25413,7 +25413,7 @@
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>TT-09.2</t>
+          <t>TT-07.2</t>
         </is>
       </c>
       <c r="C548" s="2" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.24</t>
+          <t>GB 16806 6.22</t>
         </is>
       </c>
       <c r="G548" s="2" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="H548" s="2" t="inlineStr">
         <is>
-          <t>通 9 s/断 1 s×500 次、6 次/min</t>
+          <t>AC 线 2 kV/5 kHz、其他线 1 kV/5 kHz、每次 1 min×3</t>
         </is>
       </c>
       <c r="I548" s="2" t="n"/>
@@ -25458,7 +25458,7 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>TT-10</t>
+          <t>TT-08</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
@@ -25474,12 +25474,12 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.22；GB 16806 6.25</t>
+          <t>GB 4717 5.20；GB 16806 6.23</t>
         </is>
       </c>
       <c r="G549" s="2" t="inlineStr">
         <is>
-          <t>电压暂降（总案）</t>
+          <t>浪涌（总案）</t>
         </is>
       </c>
       <c r="H549" s="2" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="B550" s="2" t="inlineStr">
         <is>
-          <t>TT-10.1</t>
+          <t>TT-08.1</t>
         </is>
       </c>
       <c r="C550" s="2" t="inlineStr">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.22</t>
+          <t>GB 4717 5.20</t>
         </is>
       </c>
       <c r="G550" s="2" t="inlineStr">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="H550" s="2" t="inlineStr">
         <is>
-          <t>40%/20 ms×10；0 V/10 ms×10</t>
+          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV；5 次</t>
         </is>
       </c>
       <c r="I550" s="2" t="n"/>
@@ -25548,7 +25548,7 @@
       </c>
       <c r="B551" s="2" t="inlineStr">
         <is>
-          <t>TT-10.2</t>
+          <t>TT-08.2</t>
         </is>
       </c>
       <c r="C551" s="2" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.25</t>
+          <t>GB 16806 6.23</t>
         </is>
       </c>
       <c r="G551" s="2" t="inlineStr">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="H551" s="2" t="inlineStr">
         <is>
-          <t>40%/200 ms×10；0 V/20 ms×10</t>
+          <t>AC 线-线 1 kV、线-地 2 kV；其他线-地 1 kV、线-线 0.5 kV；5 次</t>
         </is>
       </c>
       <c r="I551" s="2" t="n"/>
@@ -25593,7 +25593,7 @@
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>TT-11</t>
+          <t>TT-09</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
@@ -25609,12 +25609,12 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.23；GB 16806 6.26</t>
+          <t>GB 4717 5.21；GB 16806 6.24</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>低温（运行）（总案）</t>
+          <t>电源瞬变（总案）</t>
         </is>
       </c>
       <c r="H552" s="2" t="inlineStr">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="B553" s="2" t="inlineStr">
         <is>
-          <t>TT-11.1</t>
+          <t>TT-09.1</t>
         </is>
       </c>
       <c r="C553" s="2" t="inlineStr">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.23</t>
+          <t>GB 4717 5.21</t>
         </is>
       </c>
       <c r="G553" s="2" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="H553" s="2" t="inlineStr">
         <is>
-          <t>0℃±3℃、16 h</t>
+          <t>通 9 s/断 1 s×500 次</t>
         </is>
       </c>
       <c r="I553" s="2" t="n"/>
@@ -25683,7 +25683,7 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>TT-11.2</t>
+          <t>TT-09.2</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
@@ -25703,7 +25703,7 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.26</t>
+          <t>GB 16806 6.24</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
@@ -25713,7 +25713,7 @@
       </c>
       <c r="H554" s="2" t="inlineStr">
         <is>
-          <t>-10℃±2℃、16 h、变温 ≤1℃/min</t>
+          <t>通 9 s/断 1 s×500 次、6 次/min</t>
         </is>
       </c>
       <c r="I554" s="2" t="n"/>
@@ -25728,7 +25728,7 @@
       </c>
       <c r="B555" s="2" t="inlineStr">
         <is>
-          <t>TT-12</t>
+          <t>TT-10</t>
         </is>
       </c>
       <c r="C555" s="2" t="inlineStr">
@@ -25744,12 +25744,12 @@
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.24；GB 16806 6.27</t>
+          <t>GB 4717 5.22；GB 16806 6.25</t>
         </is>
       </c>
       <c r="G555" s="2" t="inlineStr">
         <is>
-          <t>恒定湿热（运行）（总案）</t>
+          <t>电压暂降（总案）</t>
         </is>
       </c>
       <c r="H555" s="2" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>TT-12.1</t>
+          <t>TT-10.1</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
@@ -25793,7 +25793,7 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.24</t>
+          <t>GB 4717 5.22</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H556" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、90%～95%RH、4 d</t>
+          <t>40%/20 ms×10；0 V/10 ms×10</t>
         </is>
       </c>
       <c r="I556" s="2" t="n"/>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>TT-12.2</t>
+          <t>TT-10.2</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
@@ -25838,7 +25838,7 @@
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.27</t>
+          <t>GB 16806 6.25</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="H557" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、93%±3%RH、4 d</t>
+          <t>40%/200 ms×10；0 V/20 ms×10</t>
         </is>
       </c>
       <c r="I557" s="2" t="n"/>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>TT-13</t>
+          <t>TT-11</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
@@ -25871,11 +25871,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D558" s="2" t="inlineStr">
-        <is>
-          <t>恒定湿热（耐久）</t>
-        </is>
-      </c>
+      <c r="D558" s="2" t="inlineStr"/>
       <c r="E558" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25883,17 +25879,17 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.28</t>
+          <t>GB 4717 5.23；GB 16806 6.26</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>报警控制器表 4 未列 5.25 不做；气灭控制器做</t>
+          <t>低温（运行）（总案）</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
         <is>
-          <t>40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I558" s="2" t="n"/>
@@ -25902,7 +25898,7 @@
       <c r="L558" s="2" t="n"/>
       <c r="M558" s="2" t="inlineStr">
         <is>
-          <t>已原子（仅气灭一侧）</t>
+          <t>总案</t>
         </is>
       </c>
     </row>
@@ -25912,7 +25908,7 @@
       </c>
       <c r="B559" s="2" t="inlineStr">
         <is>
-          <t>TT-14</t>
+          <t>TT-11.1</t>
         </is>
       </c>
       <c r="C559" s="2" t="inlineStr">
@@ -25920,7 +25916,11 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D559" s="2" t="inlineStr"/>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>报警</t>
+        </is>
+      </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25928,28 +25928,24 @@
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.26；GB 16806 6.29</t>
+          <t>GB 4717 5.23</t>
         </is>
       </c>
       <c r="G559" s="2" t="inlineStr">
         <is>
-          <t>振动（运行）（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>0℃±3℃、16 h</t>
         </is>
       </c>
       <c r="I559" s="2" t="n"/>
       <c r="J559" s="2" t="n"/>
       <c r="K559" s="2" t="n"/>
       <c r="L559" s="2" t="n"/>
-      <c r="M559" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M559" s="2" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -25957,7 +25953,7 @@
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>TT-14.1</t>
+          <t>TT-11.2</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
@@ -25967,7 +25963,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>报警</t>
+          <t>气灭</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -25977,7 +25973,7 @@
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.26</t>
+          <t>GB 16806 6.26</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
@@ -25987,7 +25983,7 @@
       </c>
       <c r="H560" s="2" t="inlineStr">
         <is>
-          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环</t>
+          <t>-10℃±2℃、16 h、变温 ≤1℃/min</t>
         </is>
       </c>
       <c r="I560" s="2" t="n"/>
@@ -26002,7 +25998,7 @@
       </c>
       <c r="B561" s="2" t="inlineStr">
         <is>
-          <t>TT-14.2</t>
+          <t>TT-12</t>
         </is>
       </c>
       <c r="C561" s="2" t="inlineStr">
@@ -26010,11 +26006,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D561" s="2" t="inlineStr">
-        <is>
-          <t>气灭</t>
-        </is>
-      </c>
+      <c r="D561" s="2" t="inlineStr"/>
       <c r="E561" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26022,24 +26014,28 @@
       </c>
       <c r="F561" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.29</t>
+          <t>GB 4717 5.24；GB 16806 6.27</t>
         </is>
       </c>
       <c r="G561" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>恒定湿热（运行）（总案）</t>
         </is>
       </c>
       <c r="H561" s="2" t="inlineStr">
         <is>
-          <t>10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I561" s="2" t="n"/>
       <c r="J561" s="2" t="n"/>
       <c r="K561" s="2" t="n"/>
       <c r="L561" s="2" t="n"/>
-      <c r="M561" s="2" t="n"/>
+      <c r="M561" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -26047,7 +26043,7 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>TT-15</t>
+          <t>TT-12.1</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
@@ -26055,7 +26051,11 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D562" s="2" t="inlineStr"/>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>报警</t>
+        </is>
+      </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26063,28 +26063,24 @@
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.28；GB 16806 6.30</t>
+          <t>GB 4717 5.24</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>碰撞（总案）</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>40℃±2℃、90%～95%RH、4 d</t>
         </is>
       </c>
       <c r="I562" s="2" t="n"/>
       <c r="J562" s="2" t="n"/>
       <c r="K562" s="2" t="n"/>
       <c r="L562" s="2" t="n"/>
-      <c r="M562" s="2" t="inlineStr">
-        <is>
-          <t>总案</t>
-        </is>
-      </c>
+      <c r="M562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -26092,7 +26088,7 @@
       </c>
       <c r="B563" s="2" t="inlineStr">
         <is>
-          <t>TT-15.1</t>
+          <t>TT-12.2</t>
         </is>
       </c>
       <c r="C563" s="2" t="inlineStr">
@@ -26102,7 +26098,7 @@
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>报警</t>
+          <t>气灭</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
@@ -26112,7 +26108,7 @@
       </c>
       <c r="F563" s="2" t="inlineStr">
         <is>
-          <t>GB 4717 5.28</t>
+          <t>GB 16806 6.27</t>
         </is>
       </c>
       <c r="G563" s="2" t="inlineStr">
@@ -26122,7 +26118,7 @@
       </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
-          <t>同参数（5.28）</t>
+          <t>40℃±2℃、93%±3%RH、4 d</t>
         </is>
       </c>
       <c r="I563" s="2" t="n"/>
@@ -26137,7 +26133,7 @@
       </c>
       <c r="B564" s="2" t="inlineStr">
         <is>
-          <t>TT-15.2</t>
+          <t>TT-13</t>
         </is>
       </c>
       <c r="C564" s="2" t="inlineStr">
@@ -26147,7 +26143,7 @@
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>气灭</t>
+          <t>恒定湿热（耐久）</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -26157,24 +26153,28 @@
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 6.30</t>
+          <t>GB 16806 6.28</t>
         </is>
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>报警控制器表 4 未列 5.25 不做；气灭控制器做</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>0.5 J±0.04 J×3 次/易损部件</t>
+          <t>40℃±2℃、93%±3%RH、21 d 不通电、恢复 12 h</t>
         </is>
       </c>
       <c r="I564" s="2" t="n"/>
       <c r="J564" s="2" t="n"/>
       <c r="K564" s="2" t="n"/>
       <c r="L564" s="2" t="n"/>
-      <c r="M564" s="2" t="n"/>
+      <c r="M564" s="2" t="inlineStr">
+        <is>
+          <t>已原子（仅气灭一侧）</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="B565" s="2" t="inlineStr">
         <is>
-          <t>TT-16</t>
+          <t>TT-14</t>
         </is>
       </c>
       <c r="C565" s="2" t="inlineStr">
@@ -26198,17 +26198,17 @@
       </c>
       <c r="F565" s="2" t="inlineStr">
         <is>
-          <t>附录 A</t>
+          <t>GB 4717 5.26；GB 16806 6.29</t>
         </is>
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>外壳燃烧（非金属外壳）</t>
+          <t>振动（运行）（总案）</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I565" s="2" t="n"/>
@@ -26217,7 +26217,7 @@
       <c r="L565" s="2" t="n"/>
       <c r="M565" s="2" t="inlineStr">
         <is>
-          <t>已原子【拆分存疑】——原文该参数落在气灭控制器列，但"附录 A（备用电池）"是 GB 16806 的附录、外壳燃烧是 GB 4717 附录 A；疑与 TT-17 两列互换，未改写、待人审核对</t>
+          <t>总案</t>
         </is>
       </c>
     </row>
@@ -26227,7 +26227,7 @@
       </c>
       <c r="B566" s="2" t="inlineStr">
         <is>
-          <t>TT-17</t>
+          <t>TT-14.1</t>
         </is>
       </c>
       <c r="C566" s="2" t="inlineStr">
@@ -26235,7 +26235,11 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D566" s="2" t="inlineStr"/>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>报警</t>
+        </is>
+      </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26243,28 +26247,24 @@
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>GB 4717 5.26</t>
         </is>
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>备用电池全项（总案）——原文置于报警控制器列（GB 16806 附录 A：10 支试样）；气灭控制器列为"—（按整机备电试验 PW-04）"</t>
+          <t>（见父案步骤）</t>
         </is>
       </c>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>见子项</t>
+          <t>10～150 Hz、0.981 m/s²、3 轴各 1 循环</t>
         </is>
       </c>
       <c r="I566" s="2" t="n"/>
       <c r="J566" s="2" t="n"/>
       <c r="K566" s="2" t="n"/>
       <c r="L566" s="2" t="n"/>
-      <c r="M566" s="2" t="inlineStr">
-        <is>
-          <t>总案【拆分存疑】——列归属疑与 TT-16 互换（备用电池附录 A 属 GB 16806/气灭侧，PW-04 属报警侧），未改写、待人审核对</t>
-        </is>
-      </c>
+      <c r="M566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>TT-17.1</t>
+          <t>TT-14.2</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>电压一致性</t>
+          <t>气灭</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
@@ -26292,7 +26292,7 @@
       </c>
       <c r="F567" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>GB 16806 6.29</t>
         </is>
       </c>
       <c r="G567" s="2" t="inlineStr">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="H567" s="2" t="inlineStr">
         <is>
-          <t>电压一致性</t>
+          <t>10～150 Hz、5 m/s²、1 oct/min、3 轴各 1 循环</t>
         </is>
       </c>
       <c r="I567" s="2" t="n"/>
@@ -26317,7 +26317,7 @@
       </c>
       <c r="B568" s="2" t="inlineStr">
         <is>
-          <t>TT-17.2</t>
+          <t>TT-15</t>
         </is>
       </c>
       <c r="C568" s="2" t="inlineStr">
@@ -26325,11 +26325,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D568" s="2" t="inlineStr">
-        <is>
-          <t>容量</t>
-        </is>
-      </c>
+      <c r="D568" s="2" t="inlineStr"/>
       <c r="E568" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26337,24 +26333,28 @@
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>GB 4717 5.28；GB 16806 6.30</t>
         </is>
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>碰撞（总案）</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
         <is>
-          <t>容量（常温 ≥90 min、-10℃ ≥50 min）</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I568" s="2" t="n"/>
       <c r="J568" s="2" t="n"/>
       <c r="K568" s="2" t="n"/>
       <c r="L568" s="2" t="n"/>
-      <c r="M568" s="2" t="n"/>
+      <c r="M568" s="2" t="inlineStr">
+        <is>
+          <t>总案</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>TT-17.3</t>
+          <t>TT-15.1</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>容量保存</t>
+          <t>报警</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="F569" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>GB 4717 5.28</t>
         </is>
       </c>
       <c r="G569" s="2" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>容量保存 ≥0.6</t>
+          <t>同参数（5.28）</t>
         </is>
       </c>
       <c r="I569" s="2" t="n"/>
@@ -26407,7 +26407,7 @@
       </c>
       <c r="B570" s="2" t="inlineStr">
         <is>
-          <t>TT-17.4</t>
+          <t>TT-15.2</t>
         </is>
       </c>
       <c r="C570" s="2" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>循环</t>
+          <t>气灭</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -26427,7 +26427,7 @@
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>GB 16806 6.30</t>
         </is>
       </c>
       <c r="G570" s="2" t="inlineStr">
@@ -26437,7 +26437,7 @@
       </c>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>循环 10 次 ≥90%</t>
+          <t>0.5 J±0.04 J×3 次/易损部件</t>
         </is>
       </c>
       <c r="I570" s="2" t="n"/>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="B571" s="2" t="inlineStr">
         <is>
-          <t>TT-17.5</t>
+          <t>TT-16</t>
         </is>
       </c>
       <c r="C571" s="2" t="inlineStr">
@@ -26460,11 +26460,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D571" s="2" t="inlineStr">
-        <is>
-          <t>过放</t>
-        </is>
-      </c>
+      <c r="D571" s="2" t="inlineStr"/>
       <c r="E571" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26472,24 +26468,28 @@
       </c>
       <c r="F571" s="2" t="inlineStr">
         <is>
-          <t>GB 16806 附录 A</t>
+          <t>附录 A</t>
         </is>
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>外壳燃烧（非金属外壳）</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>过放 ≥0.9</t>
+          <t>附录 A：样块 80×10 mm、氧含量 28%、气流 40 mm/s、施焰 30 s；燃烧长度 ≤50 mm</t>
         </is>
       </c>
       <c r="I571" s="2" t="n"/>
       <c r="J571" s="2" t="n"/>
       <c r="K571" s="2" t="n"/>
       <c r="L571" s="2" t="n"/>
-      <c r="M571" s="2" t="n"/>
+      <c r="M571" s="2" t="inlineStr">
+        <is>
+          <t>已原子【拆分存疑】——原文该参数落在气灭控制器列，但"附录 A（备用电池）"是 GB 16806 的附录、外壳燃烧是 GB 4717 附录 A；疑与 TT-17 两列互换，未改写、待人审核对</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>TT-17.6</t>
+          <t>TT-17</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
@@ -26505,11 +26505,7 @@
           <t>型式试验</t>
         </is>
       </c>
-      <c r="D572" s="2" t="inlineStr">
-        <is>
-          <t>大电流</t>
-        </is>
-      </c>
+      <c r="D572" s="2" t="inlineStr"/>
       <c r="E572" s="2" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26522,19 +26518,23 @@
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>（见父案步骤）</t>
+          <t>备用电池全项（总案）——原文置于报警控制器列（GB 16806 附录 A：10 支试样）；气灭控制器列为"—（按整机备电试验 PW-04）"</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
         <is>
-          <t>5C₂₀ 大电流</t>
+          <t>见子项</t>
         </is>
       </c>
       <c r="I572" s="2" t="n"/>
       <c r="J572" s="2" t="n"/>
       <c r="K572" s="2" t="n"/>
       <c r="L572" s="2" t="n"/>
-      <c r="M572" s="2" t="n"/>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>总案【拆分存疑】——列归属疑与 TT-16 互换（备用电池附录 A 属 GB 16806/气灭侧，PW-04 属报警侧），未改写、待人审核对</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="B573" s="2" t="inlineStr">
         <is>
-          <t>TT-17.7</t>
+          <t>TT-17.1</t>
         </is>
       </c>
       <c r="C573" s="2" t="inlineStr">
@@ -26552,7 +26552,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>密闭效率</t>
+          <t>电压一致性</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="H573" s="2" t="inlineStr">
         <is>
-          <t>密闭效率 ≥95%</t>
+          <t>电压一致性</t>
         </is>
       </c>
       <c r="I573" s="2" t="n"/>
@@ -26587,7 +26587,7 @@
       </c>
       <c r="B574" s="2" t="inlineStr">
         <is>
-          <t>TT-17.8</t>
+          <t>TT-17.2</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>防爆</t>
+          <t>容量</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="H574" s="2" t="inlineStr">
         <is>
-          <t>防爆</t>
+          <t>容量（常温 ≥90 min、-10℃ ≥50 min）</t>
         </is>
       </c>
       <c r="I574" s="2" t="n"/>
@@ -26632,7 +26632,7 @@
       </c>
       <c r="B575" s="2" t="inlineStr">
         <is>
-          <t>TT-17.9</t>
+          <t>TT-17.3</t>
         </is>
       </c>
       <c r="C575" s="2" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>防酸雾</t>
+          <t>容量保存</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="H575" s="2" t="inlineStr">
         <is>
-          <t>防酸雾</t>
+          <t>容量保存 ≥0.6</t>
         </is>
       </c>
       <c r="I575" s="2" t="n"/>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="B576" s="2" t="inlineStr">
         <is>
-          <t>TT-17.10</t>
+          <t>TT-17.4</t>
         </is>
       </c>
       <c r="C576" s="2" t="inlineStr">
@@ -26687,7 +26687,7 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>跌落</t>
+          <t>循环</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>跌落</t>
+          <t>循环 10 次 ≥90%</t>
         </is>
       </c>
       <c r="I576" s="2" t="n"/>
@@ -26716,9 +26716,279 @@
       <c r="L576" s="2" t="n"/>
       <c r="M576" s="2" t="n"/>
     </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.5</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>过放</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>过放 ≥0.9</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="n"/>
+      <c r="J577" s="2" t="n"/>
+      <c r="K577" s="2" t="n"/>
+      <c r="L577" s="2" t="n"/>
+      <c r="M577" s="2" t="n"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.6</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>大电流</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>5C₂₀ 大电流</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="n"/>
+      <c r="J578" s="2" t="n"/>
+      <c r="K578" s="2" t="n"/>
+      <c r="L578" s="2" t="n"/>
+      <c r="M578" s="2" t="n"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.7</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>密闭效率</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>密闭效率 ≥95%</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="n"/>
+      <c r="J579" s="2" t="n"/>
+      <c r="K579" s="2" t="n"/>
+      <c r="L579" s="2" t="n"/>
+      <c r="M579" s="2" t="n"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.8</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>防爆</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>防爆</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="n"/>
+      <c r="J580" s="2" t="n"/>
+      <c r="K580" s="2" t="n"/>
+      <c r="L580" s="2" t="n"/>
+      <c r="M580" s="2" t="n"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.9</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>防酸雾</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>防酸雾</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="n"/>
+      <c r="J581" s="2" t="n"/>
+      <c r="K581" s="2" t="n"/>
+      <c r="L581" s="2" t="n"/>
+      <c r="M581" s="2" t="n"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>TT-17.10</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>跌落</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>GB 16806 附录 A</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>（见父案步骤）</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>跌落</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="n"/>
+      <c r="J582" s="2" t="n"/>
+      <c r="K582" s="2" t="n"/>
+      <c r="L582" s="2" t="n"/>
+      <c r="M582" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M576"/>
-  <conditionalFormatting sqref="J2:J576">
+  <autoFilter ref="A1:M582"/>
+  <conditionalFormatting sqref="J2:J582">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"通过"</formula>
     </cfRule>
@@ -26727,7 +26997,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J582" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
     </dataValidation>
   </dataValidations>
@@ -26767,7 +27037,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3">
@@ -26777,7 +27047,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTA(测试执行表!J2:J576)-COUNTIF(测试执行表!J2:J576,"待测")</f>
+        <f>COUNTA(测试执行表!J2:J582)-COUNTIF(测试执行表!J2:J582,"待测")</f>
         <v/>
       </c>
     </row>
@@ -26788,7 +27058,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!J2:J576,"通过")</f>
+        <f>COUNTIF(测试执行表!J2:J582,"通过")</f>
         <v/>
       </c>
     </row>
@@ -26799,7 +27069,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!J2:J576,"不通过")</f>
+        <f>COUNTIF(测试执行表!J2:J582,"不通过")</f>
         <v/>
       </c>
     </row>
@@ -26810,7 +27080,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!J2:J576,"不适用")</f>
+        <f>COUNTIF(测试执行表!J2:J582,"不适用")</f>
         <v/>
       </c>
     </row>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -2387,12 +2387,20 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="3" t="n"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>产品决策2026-08-19：不做二次确认/多信号确认，首信号直接报警——可选条款（准许设有）未实现＝合规，判不适用；若未来实现该功能需恢复测试</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -2441,12 +2449,20 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="3" t="n"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -2495,12 +2511,20 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="3" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
@@ -2549,12 +2573,20 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="3" t="n"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="n"/>
     </row>
     <row r="37">
@@ -2603,16 +2635,20 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="n"/>
     </row>
     <row r="38">
@@ -2661,12 +2697,20 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="3" t="n"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="n"/>
     </row>
     <row r="39">
@@ -2715,12 +2759,20 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="3" t="n"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -2769,12 +2821,20 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="3" t="n"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="n"/>
     </row>
     <row r="41">
@@ -2815,7 +2875,7 @@
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K41" s="2" t="n"/>
@@ -2826,7 +2886,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>待条件：需第2只烟感（不同部位二次确认，可选功能；未实现则改判不适用）</t>
+          <t>产品决策2026-08-19：不做二次确认/多信号确认，首信号直接报警——可选条款（准许设有）未实现＝合规，判不适用；若未来实现该功能需恢复测试</t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
@@ -2873,7 +2933,7 @@
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -2884,7 +2944,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 FA-09</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N42" s="2" t="n"/>
@@ -2931,7 +2991,7 @@
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K43" s="2" t="n"/>
@@ -2942,7 +3002,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 FA-09</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N43" s="2" t="n"/>
@@ -2989,7 +3049,7 @@
       <c r="I44" s="3" t="n"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -3000,7 +3060,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 FA-09</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N44" s="2" t="n"/>
@@ -5863,7 +5923,7 @@
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K105" s="2" t="n"/>
@@ -5874,7 +5934,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>待条件：需第2个火警触发部位＋多信号确认输出逻辑（可选功能；未实现则改判不适用）</t>
+          <t>产品决策2026-08-19：不做二次确认/多信号确认，首信号直接报警——可选条款（准许设有）未实现＝合规，判不适用；若未来实现该功能需恢复测试</t>
         </is>
       </c>
       <c r="N105" s="2" t="n"/>
@@ -5921,7 +5981,7 @@
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K106" s="2" t="n"/>
@@ -5932,7 +5992,7 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N106" s="2" t="n"/>
@@ -5979,7 +6039,7 @@
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K107" s="2" t="n"/>
@@ -5990,7 +6050,7 @@
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N107" s="2" t="n"/>
@@ -6037,7 +6097,7 @@
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K108" s="2" t="n"/>
@@ -6048,7 +6108,7 @@
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N108" s="2" t="n"/>
@@ -6095,7 +6155,7 @@
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K109" s="2" t="n"/>
@@ -6106,7 +6166,7 @@
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N109" s="2" t="n"/>
@@ -6153,7 +6213,7 @@
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K110" s="2" t="n"/>
@@ -6164,7 +6224,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N110" s="2" t="n"/>
@@ -6211,7 +6271,7 @@
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K111" s="2" t="n"/>
@@ -6222,7 +6282,7 @@
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>待条件：同 LC-10</t>
+          <t>同父案：产品决策不做二次/多信号确认，判不适用</t>
         </is>
       </c>
       <c r="N111" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -14,6 +14,7 @@
     <sheet name="缺陷汇总" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$634</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'缺陷汇总'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33350,6 +33351,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M634"/>
   <dataValidations count="11">
     <dataValidation sqref="J2:J606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -8,14 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="测试执行表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="菜单覆盖" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="统计" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="分组统计" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="缺陷汇总" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="菜单覆盖" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="缺陷汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="分组统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$634</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'缺陷汇总'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,8 +77,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -101,11 +105,25 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -140,6 +158,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4044,9 +4069,17 @@
         </is>
       </c>
       <c r="I64" s="3" t="n"/>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="n"/>
-      <c r="L64" s="2" t="n"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M64" s="3" t="n"/>
       <c r="N64" s="2" t="n"/>
     </row>
@@ -4090,9 +4123,17 @@
         </is>
       </c>
       <c r="I65" s="3" t="n"/>
-      <c r="J65" s="2" t="n"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M65" s="3" t="n"/>
       <c r="N65" s="2" t="n"/>
     </row>
@@ -4136,9 +4177,17 @@
         </is>
       </c>
       <c r="I66" s="3" t="n"/>
-      <c r="J66" s="2" t="n"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M66" s="3" t="n"/>
       <c r="N66" s="2" t="n"/>
     </row>
@@ -4274,9 +4323,17 @@
         </is>
       </c>
       <c r="I69" s="3" t="n"/>
-      <c r="J69" s="2" t="n"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M69" s="3" t="n"/>
       <c r="N69" s="2" t="n"/>
     </row>
@@ -33397,1072 +33454,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>大类</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>菜单项</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>对应用例</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>用例数</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>用例总数</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>COUNTA(测试执行表!$B$2:$B$606)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>★ 真正已测(通过+不通过)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"通过")+COUNTIF(测试执行表!$J$2:$J$606,"不通过")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="B4">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"通过")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>不通过</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>待测/暂不</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>未填</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>照片上的权限</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>历史记录</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>DP-05、DP-06、DP-07、DP-08、DP-09、DP-10…</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>控制器信息</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>UI-02</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>级联从机</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>UI-05、UI-05.1、UI-05.2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>设备总览</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>UI-03、UI-03.1、UI-03.2、UI-03.3、UI-03.4、UI-03.5…</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="B5">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"不通过")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>单点查询</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>UI-04、UI-04.1、UI-04.2、UI-04.3、UI-04.4、UI-04.5</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"不适用")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>查询</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>检查信息</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CK-01、CK-01.1、CK-01.2、CK-01.3、CK-01.4、CK-02…</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>操作员</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"待测")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>节点设备监控</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>UI-07、UI-07.1、UI-07.2、UI-07.3、UI-07.4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>暂不测试</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(测试执行表!$J$2:$J$606,"暂不测试")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>通讯成功率</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>UI-08、UI-08.1、UI-08.2、UI-08.3、UI-08.4、UI-08.5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>完全未填</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>COUNTBLANK(测试执行表!$J$2:$J$606)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>机内设备监控</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>UI-09、UI-09.1、UI-09.2、UI-09.3、UI-09.4、UI-09.5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>通过率(通过/真正已测)</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>IF(B3=0,"-",B4/B3)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>启停控制</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>UI-10、UI-10.1、UI-10.2、UI-10.3、UI-10.4、UI-10.5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>屏蔽控制</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>SH-01、SH-01.1、SH-01.2、SH-01.3、SH-01.4、SH-02…</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>用户登陆</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>UI-12、UI-12.1、UI-12.2、UI-12.3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>基础设置</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>UI-14、UI-14.1、UI-14.2、UI-14.3、UI-14.4、UI-14.5…</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>密码设置</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>UI-13、UI-13.1、UI-13.2、UI-13.3、UI-13.4、UI-13.5</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 改 Ⅲ 级密码按 OP-02.2 应拒绝 Ⅱ 级；菜单标「操作」级需核</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>联网设置</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>UI-15、UI-15.1、UI-15.2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 参数修改属「输入/更改数据」，OP-02.2 要求 Ⅱ 级拒绝</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>节点设置</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>UI-16、UI-16.1、UI-16.2</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 点表编辑属「数据修改」，OP-03.1 要求 Ⅲ 级；菜单标「操作」级需核</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>操作模式设置</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>UI-17、UI-17.1、UI-17.2、UI-17.3</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>点位注册</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>UI-18、UI-18.1、UI-18.2、UI-18.3、UI-18.4、UI-18.5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>配置导入</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>UI-19、UI-19.1、UI-19.2、UI-19.3</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>联动编程</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>UI-20、UI-20.1、UI-20.2</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>调试助手</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>UI-21、UI-21.1、UI-21.2、UI-21.3、UI-21.4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>联网注册</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>UI-22</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>调试</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>直控调试</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>调试员</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ 与「调试助手」共用 UI-21，菜单上是两个独立入口，建议拆为 UI-21.1/.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>维护</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>固件升级</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>UI-23、UI-23.1、UI-23.2、UI-23.3</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>生产商</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>维护</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>记录导出</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>UI-24、UI-24.1、UI-24.2、UI-24.3</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>生产商</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>维护</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>恢复出厂设置</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>UI-25、UI-25.1、UI-25.2、UI-25.3、UI-25.4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>生产商</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>覆盖率(真正已测/总数)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>IF(B2=0,"-",B3/B2)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34475,134 +33594,1072 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>值</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>大类</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>菜单项</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>对应用例</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>用例数</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>待测/暂不</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>未填</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>照片上的权限</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>用例总数</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>COUNTA(测试执行表!$B$2:$B$606)</f>
-        <v/>
-      </c>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>历史记录</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>DP-05、DP-06、DP-07、DP-08、DP-09、DP-10…</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>★ 真正已测(通过+不通过)</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"通过")+COUNTIF(测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>控制器信息</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>UI-02</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>级联从机</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>UI-05、UI-05.1、UI-05.2</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>设备总览</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>UI-03、UI-03.1、UI-03.2、UI-03.3、UI-03.4、UI-03.5…</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"不适用")</f>
-        <v/>
-      </c>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>单点查询</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>UI-04、UI-04.1、UI-04.2、UI-04.3、UI-04.4、UI-04.5</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>待测</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"待测")</f>
-        <v/>
-      </c>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>查询</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>检查信息</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>CK-01、CK-01.1、CK-01.2、CK-01.3、CK-01.4、CK-02…</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>操作员</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>暂不测试</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>COUNTIF(测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>节点设备监控</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>UI-07、UI-07.1、UI-07.2、UI-07.3、UI-07.4</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>完全未填</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTBLANK(测试执行表!$J$2:$J$606)</f>
-        <v/>
-      </c>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>通讯成功率</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>UI-08、UI-08.1、UI-08.2、UI-08.3、UI-08.4、UI-08.5</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>通过率(通过/真正已测)</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>IF(B3=0,"-",B4/B3)</f>
-        <v/>
-      </c>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>机内设备监控</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>UI-09、UI-09.1、UI-09.2、UI-09.3、UI-09.4、UI-09.5</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>覆盖率(真正已测/总数)</t>
-        </is>
-      </c>
-      <c r="B11" s="11">
-        <f>IF(B2=0,"-",B3/B2)</f>
-        <v/>
-      </c>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>启停控制</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>UI-10、UI-10.1、UI-10.2、UI-10.3、UI-10.4、UI-10.5</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>SH-01、SH-01.1、SH-01.2、SH-01.3、SH-01.4、SH-02…</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>用户登陆</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>UI-12、UI-12.1、UI-12.2、UI-12.3</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>基础设置</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>UI-14、UI-14.1、UI-14.2、UI-14.3、UI-14.4、UI-14.5…</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>密码设置</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>UI-13、UI-13.1、UI-13.2、UI-13.3、UI-13.4、UI-13.5</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ 改 Ⅲ 级密码按 OP-02.2 应拒绝 Ⅱ 级；菜单标「操作」级需核</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>联网设置</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>UI-15、UI-15.1、UI-15.2</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ 参数修改属「输入/更改数据」，OP-02.2 要求 Ⅱ 级拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>节点设置</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>UI-16、UI-16.1、UI-16.2</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ 点表编辑属「数据修改」，OP-03.1 要求 Ⅲ 级；菜单标「操作」级需核</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>操作模式设置</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>UI-17、UI-17.1、UI-17.2、UI-17.3</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>点位注册</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>UI-18、UI-18.1、UI-18.2、UI-18.3、UI-18.4、UI-18.5</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>配置导入</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>UI-19、UI-19.1、UI-19.2、UI-19.3</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>联动编程</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>UI-20、UI-20.1、UI-20.2</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>调试助手</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>UI-21、UI-21.1、UI-21.2、UI-21.3、UI-21.4</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>联网注册</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>UI-22</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>直控调试</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>调试员</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ 与「调试助手」共用 UI-21，菜单上是两个独立入口，建议拆为 UI-21.1/.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>固件升级</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>UI-23、UI-23.1、UI-23.2、UI-23.3</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>生产商</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>记录导出</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>UI-24、UI-24.1、UI-24.2、UI-24.3</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>生产商</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>维护</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>恢复出厂设置</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>UI-25、UI-25.1、UI-25.2、UI-25.3、UI-25.4</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>生产商</t>
+        </is>
+      </c>
+      <c r="J27" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34615,506 +34672,1151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>用例数</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>不通过</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>待测/暂不</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
-        <is>
-          <t>未填</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>用例号</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>菜单归属</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>级</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>实测结果</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>疑似同源缺陷</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>火灾报警</t>
-        </is>
-      </c>
-      <c r="B2" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A2)</f>
-        <v/>
-      </c>
-      <c r="C2" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A2,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D2" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A2,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E2" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A2,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A2,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F2" s="2">
-        <f>$B2-COUNTIFS(测试执行表!$C$2:$C$606,$A2,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>FA-04</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>报警延时功能未设置（未实现）</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>报警控制(联动输出)</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A3)</f>
-        <v/>
-      </c>
-      <c r="C3" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A3,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D3" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A3,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E3" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A3,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A3,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F3" s="2">
-        <f>$B3-COUNTIFS(测试执行表!$C$2:$C$606,$A3,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>FA-04.1</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>最大延时</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>同 FA-04</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>故障报警</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A4,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D4" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A4,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E4" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A4,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A4,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F4" s="2">
-        <f>$B4-COUNTIFS(测试执行表!$C$2:$C$606,$A4,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>FA-04.2</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>延时光指示</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>同 FA-04</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>屏蔽</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A5)</f>
-        <v/>
-      </c>
-      <c r="C5" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A5,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D5" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A5,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E5" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A5,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A5,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F5" s="2">
-        <f>$B5-COUNTIFS(测试执行表!$C$2:$C$606,$A5,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>FA-04.3</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>倒计时显示</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>同 FA-04</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>监管报警</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A6,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D6" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A6,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E6" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A6,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A6,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F6" s="2">
-        <f>$B6-COUNTIFS(测试执行表!$C$2:$C$606,$A6,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>FA-04.4</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>设置信息可查</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>同 FA-04</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>自检</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A7,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D7" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A7,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E7" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A7,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A7,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F7" s="2">
-        <f>$B7-COUNTIFS(测试执行表!$C$2:$C$606,$A7,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>FA-11</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>信息显示时间缺年份("01月02日 00:20:58"),不满足年月日时分秒</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>显示与查询</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A8,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D8" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A8,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E8" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A8,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A8,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F8" s="2">
-        <f>$B8-COUNTIFS(测试执行表!$C$2:$C$606,$A8,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>ST-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>开机自检·故障优先显示</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>现在卡到启动页面了</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>检查功能</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A9,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D9" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A9,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E9" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A9,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A9,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F9" s="2">
-        <f>$B9-COUNTIFS(测试执行表!$C$2:$C$606,$A9,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>DP-05</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 历史记录</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>历史记录·全部查询按钮</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>全部查询按钮点击无响应</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>电源</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A10)</f>
-        <v/>
-      </c>
-      <c r="C10" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A10,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D10" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A10,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E10" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A10,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A10,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <f>$B10-COUNTIFS(测试执行表!$C$2:$C$606,$A10,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>UI-01.3</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 历史记录</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>菜单页信息项完整</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>缺少其他</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>看门狗</t>
-        </is>
-      </c>
-      <c r="B11" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A11)</f>
-        <v/>
-      </c>
-      <c r="C11" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A11,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D11" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A11,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E11" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A11,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A11,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F11" s="2">
-        <f>$B11-COUNTIFS(测试执行表!$C$2:$C$606,$A11,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>UI-02</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 控制器信息</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>控制器信息</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>没有容量</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>通信</t>
-        </is>
-      </c>
-      <c r="B12" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A12,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D12" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A12,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E12" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A12,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A12,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F12" s="2">
-        <f>$B12-COUNTIFS(测试执行表!$C$2:$C$606,$A12,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>UI-04.3</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 单点查询</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>单点查询·返回按钮</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>显示的菜单按钮，点击到了菜单页</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>存储单元(黑匣子)</t>
-        </is>
-      </c>
-      <c r="B13" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A13,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D13" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A13,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E13" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A13,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A13,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F13" s="2">
-        <f>$B13-COUNTIFS(测试执行表!$C$2:$C$606,$A13,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>UI-05.1</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 级联从机</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>级联从机·无从机显示</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>无从机的情况下，有显示对勾的</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>操作级别</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A14,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D14" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A14,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E14" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A14,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A14,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F14" s="2">
-        <f>$B14-COUNTIFS(测试执行表!$C$2:$C$606,$A14,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>UI-07.4</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 节点设备监控</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>节点监控·返回按钮</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>显示的是菜单按钮，点击跳到菜单页（与 UI-26/27、UI-03.4/.6、UI-04.3、UI-05.2、UI-18.3、UI-01.4 同源）</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>人机菜单(产品级)</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A15,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D15" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A15,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E15" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A15,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A15,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <f>$B15-COUNTIFS(测试执行表!$C$2:$C$606,$A15,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>UI-08.4</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 通讯成功率</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>通讯成功率·返回按钮</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>显示的是菜单按钮，点击跳到菜单页（全局导航缺陷，同源第 11 处）</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>气体灭火控制器</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A16)</f>
-        <v/>
-      </c>
-      <c r="C16" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A16,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D16" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A16,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E16" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A16,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A16,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F16" s="2">
-        <f>$B16-COUNTIFS(测试执行表!$C$2:$C$606,$A16,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>UI-10.4</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 启停控制</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>启停·返回按钮响应</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>⚠️与其他页不同：本页返回按钮显示正确，但点击无响应。属全局导航缺陷的第二亚型（显示对/不响应），另一亚型为显示成菜单按钮</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>结构与外观</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A17)</f>
-        <v/>
-      </c>
-      <c r="C17" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A17,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D17" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A17,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E17" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A17,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A17,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F17" s="2">
-        <f>$B17-COUNTIFS(测试执行表!$C$2:$C$606,$A17,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
-      </c>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>UI-11.1</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>屏蔽·空地址输入校验</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>❌ 空输入可点击且生效：物理屏蔽灯点亮并发声。控制器进入"虚假屏蔽态"（无任何设备被屏蔽却亮屏蔽灯），与 SH-01.4「屏蔽总灯亮并显示屏蔽时间」语义冲突；须复核 CK-08 屏蔽数量列此时显示值</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>型式试验</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <f>COUNTIF(测试执行表!$C$2:$C$606,$A18)</f>
-        <v/>
-      </c>
-      <c r="C18" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A18,测试执行表!$J$2:$J$606,"通过")</f>
-        <v/>
-      </c>
-      <c r="D18" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A18,测试执行表!$J$2:$J$606,"不通过")</f>
-        <v/>
-      </c>
-      <c r="E18" s="2">
-        <f>COUNTIFS(测试执行表!$C$2:$C$606,$A18,测试执行表!$J$2:$J$606,"待测")+COUNTIFS(测试执行表!$C$2:$C$606,$A18,测试执行表!$J$2:$J$606,"暂不测试")</f>
-        <v/>
-      </c>
-      <c r="F18" s="2">
-        <f>$B18-COUNTIFS(测试执行表!$C$2:$C$606,$A18,测试执行表!$J$2:$J$606,"&lt;&gt;")</f>
-        <v/>
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>UI-11.4</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>解除屏蔽·声信号未随状态停止</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>❌ 解除屏蔽后物理屏蔽灯已关闭，但声音未停；必须手动按消音键声音才消失 → 声信号与状态解耦</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>UI-11.5</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>消音灯常亮·不自动复位</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>❌ 物理消音灯一直亮着不复位。⚠️安全风险：若消音态未退出，下一次真火警时(a)值班员会误判"已消过音"(b)火警声可能被压制。须立即验证：当前消音灯亮态下触发新火警(加烟/按手报)，看消音灯是否熄灭、火警声是否响起(FA-06.4 / LC-11.4)。注：FT-04.1「新故障声再启动」已测通过，但火警侧未验</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>UI-11.6</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>屏蔽页·返回按钮响应</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>❌ 返回按钮无响应（全局导航缺陷·亚型B：显示对/不响应）</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>UI-13.4</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 密码设置</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>密码设置·返回按钮</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>❌ 返回按钮不正确（全局导航缺陷）</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>UI-14.5</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 基础设置</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>基础设置·返回按钮</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>❌ 返回按钮不正确（全局导航缺陷）</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>UI-14.6</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 基础设置</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>⚠️系统时钟停在00年</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>❌ 当前值 = 00年01月02日 05:36:11 → 年份为00，系上电累计计时而非真实时间。⚠️根因关联：已判不通过的 FA-11「信息显示时间缺年份」与 UI-28 很可能不是显示层丢字段，而是时钟本身无效。影响面：全部黑匣子事件时间戳、SH-01.4屏蔽时间、CM-03授时。建议动作：在本页设为真实时间→确定→复查 UI-14.1(生效)/UI-14.3(日误差≤6s)/FA-11/UI-28，一次可收4条</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>UI-14.7</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 基础设置</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>⚠️声音使能可关闭强制声信号</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>❌ 界面提供分项开关且当前状态为：报警✓开 / 监管☐关 / 启动☐关 / 反馈☐关。⚠️「监管」声被关闭直接抵触 SV-01.1。待判别：该开关若控制的是标准强制的报警声→设计违标；若仅控制按键提示音→改判不适用。判别方法：保持当前状态触发一次监管报警，无声则违标成立。注意 SV 组8条用例全部以"监管声能响"为前提，此项不定论则 SV 组无法测</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>UI-16</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 节点设置</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>节点设置：菜单入口存在，点击无响应（功能未开发）</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>UI-17.1</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 操作模式设置</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>操作模式·返回按钮</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>❌ 显示的是菜单按钮，点击跳到菜单页（全局导航缺陷·亚型A）</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>UI-17.3</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>设置 / 操作模式设置</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>⚠️免打扰模式·状态可区分与值班提示</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>❌ 测试人现场提出：该模式为开发人员使用，但缺少对值班人员的明显提示，存在影响正常功能而不自知的风险。对照 OP-05.3，此非"建议"而是标准要求：需验证 ①主界面是否有常驻区别标识（非仅本设置页内）②顶栏状态是否变化 ③上传/打印信息是否带区别标识 ④是否有超时自动退回正常运行</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>UI-18.3</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>调试 / 点位注册</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>设备注册·返回按钮</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>左上角返回按钮点击无响应</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>UI-19</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>调试 / 配置导入</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>功能未实现（菜单入口存在，功能未开发）</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>UI-20</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>调试 / 联动编程</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>功能未实现（菜单入口存在，功能未开发）</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>UI-26</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>检查页右上角返回按钮</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>右上角为菜单按钮,点击进入信息显示页,非返回主页</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>UI-27</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>信息显示页右上角返回按钮</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>右上角同样非返回</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>UI-28</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>信息显示时间格式</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>时间显示"01月02日 00:20:58"缺年份</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>UI-01.4</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 历史记录</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>菜单页·详情返回</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>无法返回到菜单页</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>DP-11</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 历史记录</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>历史记录·详情返回按钮</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>应该显示返回按钮，显示了菜单按钮。点击按钮无响应</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>DP-13</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 历史记录</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>历史记录·按回路查询</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>回路1有故障，查询回路1地址1，应该有数据，查询列表也无数据，查询回路1，地址2，却有数据</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>UI-18.5</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>调试 / 点位注册</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>点位注册·右上角返回按钮</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>❌ 显示的是菜单按钮，点击跳到菜单列表页（全局导航缺陷·亚型A：显示错）。注：本页左上角返回按钮另有"点击无响应"问题(UI-18.3，亚型B)，两个按钮各自有问题</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>UI-03.4</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 设备总览</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>设备总览·列表返回按钮</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>点击无响应</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>UI-03.6</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 设备总览</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>设备总览·详情返回按钮</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>显示的菜单按钮，点击无响应</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>UI-05.2</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>查询 / 级联从机</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>级联从机·返回按钮</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>显示的菜单按钮，点击到了菜单页</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>★ 全局导航缺陷</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -35128,1155 +35830,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>用例号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>菜单归属</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>级</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>实测结果</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>疑似同源缺陷</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>用例数</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>待测/暂不</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>未填</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FA-04</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>报警延时功能未设置（未实现）</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>火灾报警</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(测试执行表!C2:C634,A2)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>B2-C2-D2-E2-F2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FA-04.1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>最大延时</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>同 FA-04</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>报警控制(联动输出)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF(测试执行表!C2:C634,A3)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>B3-C3-D3-E3-F3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FA-04.2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>延时光指示</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>同 FA-04</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(测试执行表!C2:C634,A4)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>B4-C4-D4-E4-F4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FA-04.3</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>倒计时显示</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>同 FA-04</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>屏蔽</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(测试执行表!C2:C634,A5)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>B5-C5-D5-E5-F5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FA-04.4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>设置信息可查</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>同 FA-04</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>监管报警</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(测试执行表!C2:C634,A6)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>B6-C6-D6-E6-F6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FA-11</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>信息显示时间缺年份("01月02日 00:20:58"),不满足年月日时分秒</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>自检</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF(测试执行表!C2:C634,A7)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>B7-C7-D7-E7-F7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ST-05</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>开机自检·故障优先显示</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>现在卡到启动页面了</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>显示与查询</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(测试执行表!C2:C634,A8)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>B8-C8-D8-E8-F8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>DP-05</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 历史记录</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>历史记录·全部查询按钮</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>全部查询按钮点击无响应</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>检查功能</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>COUNTIF(测试执行表!C2:C634,A9)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>B9-C9-D9-E9-F9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>UI-01.3</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 历史记录</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>菜单页信息项完整</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>缺少其他</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>电源</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>COUNTIF(测试执行表!C2:C634,A10)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>B10-C10-D10-E10-F10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>UI-02</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 控制器信息</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>控制器信息</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>没有容量</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>看门狗</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(测试执行表!C2:C634,A11)</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>B11-C11-D11-E11-F11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>UI-04.3</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 单点查询</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>单点查询·返回按钮</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>显示的菜单按钮，点击到了菜单页</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>COUNTIF(测试执行表!C2:C634,A12)</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>B12-C12-D12-E12-F12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>UI-05.1</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 级联从机</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>级联从机·无从机显示</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>无从机的情况下，有显示对勾的</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>存储单元(黑匣子)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(测试执行表!C2:C634,A13)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>B13-C13-D13-E13-F13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>UI-07.4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 节点设备监控</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>节点监控·返回按钮</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>显示的是菜单按钮，点击跳到菜单页（与 UI-26/27、UI-03.4/.6、UI-04.3、UI-05.2、UI-18.3、UI-01.4 同源）</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>操作级别</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTIF(测试执行表!C2:C634,A14)</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>B14-C14-D14-E14-F14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>UI-08.4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 通讯成功率</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>通讯成功率·返回按钮</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>显示的是菜单按钮，点击跳到菜单页（全局导航缺陷，同源第 11 处）</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>气体灭火控制器</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(测试执行表!C2:C634,A15)</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>B15-C15-D15-E15-F15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>UI-10.4</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 启停控制</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>启停·返回按钮响应</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>⚠️与其他页不同：本页返回按钮显示正确，但点击无响应。属全局导航缺陷的第二亚型（显示对/不响应），另一亚型为显示成菜单按钮</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>结构与外观</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(测试执行表!C2:C634,A16)</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>B16-C16-D16-E16-F16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>UI-11.1</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 屏蔽控制</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>屏蔽·空地址输入校验</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>❌ 空输入可点击且生效：物理屏蔽灯点亮并发声。控制器进入"虚假屏蔽态"（无任何设备被屏蔽却亮屏蔽灯），与 SH-01.4「屏蔽总灯亮并显示屏蔽时间」语义冲突；须复核 CK-08 屏蔽数量列此时显示值</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>人机菜单(产品级)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>COUNTIF(测试执行表!C2:C634,A17)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>B17-C17-D17-E17-F17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>UI-11.4</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 屏蔽控制</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>解除屏蔽·声信号未随状态停止</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>❌ 解除屏蔽后物理屏蔽灯已关闭，但声音未停；必须手动按消音键声音才消失 → 声信号与状态解耦</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>型式试验</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>COUNTIF(测试执行表!C2:C634,A18)</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"通过")</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"不通过")</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"不适用")</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"暂不测试")</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>B18-C18-D18-E18-F18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>UI-11.5</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 屏蔽控制</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>消音灯常亮·不自动复位</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>❌ 物理消音灯一直亮着不复位。⚠️安全风险：若消音态未退出，下一次真火警时(a)值班员会误判"已消过音"(b)火警声可能被压制。须立即验证：当前消音灯亮态下触发新火警(加烟/按手报)，看消音灯是否熄灭、火警声是否响起(FA-06.4 / LC-11.4)。注：FT-04.1「新故障声再启动」已测通过，但火警侧未验</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>UI-11.6</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>监控&amp;控制 / 屏蔽控制</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>屏蔽页·返回按钮响应</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>❌ 返回按钮无响应（全局导航缺陷·亚型B：显示对/不响应）</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>UI-13.4</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 密码设置</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>密码设置·返回按钮</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>❌ 返回按钮不正确（全局导航缺陷）</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>UI-14.5</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 基础设置</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>基础设置·返回按钮</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>❌ 返回按钮不正确（全局导航缺陷）</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>UI-14.6</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 基础设置</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>⚠️系统时钟停在00年</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>❌ 当前值 = 00年01月02日 05:36:11 → 年份为00，系上电累计计时而非真实时间。⚠️根因关联：已判不通过的 FA-11「信息显示时间缺年份」与 UI-28 很可能不是显示层丢字段，而是时钟本身无效。影响面：全部黑匣子事件时间戳、SH-01.4屏蔽时间、CM-03授时。建议动作：在本页设为真实时间→确定→复查 UI-14.1(生效)/UI-14.3(日误差≤6s)/FA-11/UI-28，一次可收4条</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>UI-14.7</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 基础设置</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>⚠️声音使能可关闭强制声信号</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>❌ 界面提供分项开关且当前状态为：报警✓开 / 监管☐关 / 启动☐关 / 反馈☐关。⚠️「监管」声被关闭直接抵触 SV-01.1。待判别：该开关若控制的是标准强制的报警声→设计违标；若仅控制按键提示音→改判不适用。判别方法：保持当前状态触发一次监管报警，无声则违标成立。注意 SV 组8条用例全部以"监管声能响"为前提，此项不定论则 SV 组无法测</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>UI-16</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 节点设置</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>节点设置：菜单入口存在，点击无响应（功能未开发）</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>UI-17.1</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 操作模式设置</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>操作模式·返回按钮</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>❌ 显示的是菜单按钮，点击跳到菜单页（全局导航缺陷·亚型A）</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>UI-17.3</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>设置 / 操作模式设置</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>⚠️免打扰模式·状态可区分与值班提示</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>❌ 测试人现场提出：该模式为开发人员使用，但缺少对值班人员的明显提示，存在影响正常功能而不自知的风险。对照 OP-05.3，此非"建议"而是标准要求：需验证 ①主界面是否有常驻区别标识（非仅本设置页内）②顶栏状态是否变化 ③上传/打印信息是否带区别标识 ④是否有超时自动退回正常运行</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>UI-18.3</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>调试 / 点位注册</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>设备注册·返回按钮</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>左上角返回按钮点击无响应</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>UI-19</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>调试 / 配置导入</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>功能未实现（菜单入口存在，功能未开发）</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>UI-20</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>调试 / 联动编程</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>功能未实现（菜单入口存在，功能未开发）</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>UI-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>检查页右上角返回按钮</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>右上角为菜单按钮,点击进入信息显示页,非返回主页</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>UI-27</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>信息显示页右上角返回按钮</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>右上角同样非返回</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>UI-28</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>信息显示时间格式</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>时间显示"01月02日 00:20:58"缺年份</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>UI-01.4</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 历史记录</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>菜单页·详情返回</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>无法返回到菜单页</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>DP-11</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 历史记录</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>历史记录·详情返回按钮</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>应该显示返回按钮，显示了菜单按钮。点击按钮无响应</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>DP-13</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 历史记录</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>历史记录·按回路查询</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>回路1有故障，查询回路1地址1，应该有数据，查询列表也无数据，查询回路1，地址2，却有数据</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>UI-18.5</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>调试 / 点位注册</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>点位注册·右上角返回按钮</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>❌ 显示的是菜单按钮，点击跳到菜单列表页（全局导航缺陷·亚型A：显示错）。注：本页左上角返回按钮另有"点击无响应"问题(UI-18.3，亚型B)，两个按钮各自有问题</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>UI-03.4</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 设备总览</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>设备总览·列表返回按钮</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>点击无响应</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>UI-03.6</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 设备总览</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>设备总览·详情返回按钮</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>显示的菜单按钮，点击无响应</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>UI-05.2</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>查询 / 级联从机</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>级联从机·返回按钮</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>显示的菜单按钮，点击到了菜单页</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>★ 全局导航缺陷</t>
-        </is>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>SUM(B2:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="10">
+        <f>SUM(C2:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>SUM(D2:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>SUM(E2:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>SUM(F2:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>SUM(G2:G18)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -14,7 +14,7 @@
     <sheet name="分组统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$634</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$635</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N634"/>
+  <dimension ref="A1:N635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1699,7 +1699,7 @@
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>待条件：需线型/吸气式等独立供电探测器；说明书不声明支持则改判不适用</t>
+          <t>待条件：需线型/吸气式等独立供电探测器；说明书不声明支持则改判不适用；⚠️标通过与待条件（需独立供电探测器）矛盾，请复核是否误点</t>
         </is>
       </c>
       <c r="N20" s="2" t="n"/>
@@ -1751,7 +1751,11 @@
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="3" t="inlineStr">
@@ -1801,7 +1805,11 @@
         </is>
       </c>
       <c r="I22" s="3" t="n"/>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="3" t="n"/>
@@ -1847,7 +1855,11 @@
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="3" t="n"/>
@@ -3127,7 +3139,11 @@
         </is>
       </c>
       <c r="I45" s="3" t="n"/>
-      <c r="J45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="3" t="n"/>
@@ -3173,7 +3189,11 @@
         </is>
       </c>
       <c r="I46" s="3" t="n"/>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="3" t="n"/>
@@ -3219,7 +3239,11 @@
         </is>
       </c>
       <c r="I47" s="3" t="n"/>
-      <c r="J47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="3" t="n"/>
@@ -3319,7 +3343,11 @@
         </is>
       </c>
       <c r="I49" s="3" t="n"/>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="3" t="n"/>
@@ -3423,7 +3451,11 @@
         </is>
       </c>
       <c r="I51" s="3" t="n"/>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="3" t="n"/>
@@ -3755,7 +3787,11 @@
         </is>
       </c>
       <c r="I57" s="3" t="n"/>
-      <c r="J57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="3" t="n"/>
@@ -3801,7 +3837,11 @@
         </is>
       </c>
       <c r="I58" s="3" t="n"/>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="3" t="n"/>
@@ -3843,7 +3883,11 @@
         </is>
       </c>
       <c r="I59" s="3" t="n"/>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="3" t="n"/>
@@ -3889,7 +3933,11 @@
         </is>
       </c>
       <c r="I60" s="3" t="n"/>
-      <c r="J60" s="2" t="n"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="3" t="n"/>
@@ -3935,7 +3983,11 @@
         </is>
       </c>
       <c r="I61" s="3" t="n"/>
-      <c r="J61" s="2" t="n"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="3" t="n"/>
@@ -3981,7 +4033,11 @@
         </is>
       </c>
       <c r="I62" s="3" t="n"/>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="3" t="n"/>
@@ -4027,7 +4083,11 @@
         </is>
       </c>
       <c r="I63" s="3" t="n"/>
-      <c r="J63" s="2" t="n"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="3" t="n"/>
@@ -4231,7 +4291,11 @@
         </is>
       </c>
       <c r="I67" s="3" t="n"/>
-      <c r="J67" s="2" t="n"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="3" t="n"/>
@@ -4277,7 +4341,11 @@
         </is>
       </c>
       <c r="I68" s="3" t="n"/>
-      <c r="J68" s="2" t="n"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="3" t="n"/>
@@ -4435,7 +4503,11 @@
         </is>
       </c>
       <c r="I71" s="3" t="n"/>
-      <c r="J71" s="2" t="n"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="3" t="n"/>
@@ -4477,7 +4549,11 @@
         </is>
       </c>
       <c r="I72" s="3" t="n"/>
-      <c r="J72" s="2" t="n"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="3" t="n"/>
@@ -4523,7 +4599,11 @@
         </is>
       </c>
       <c r="I73" s="3" t="n"/>
-      <c r="J73" s="2" t="n"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="3" t="n"/>
@@ -4569,7 +4649,11 @@
         </is>
       </c>
       <c r="I74" s="3" t="n"/>
-      <c r="J74" s="2" t="n"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="3" t="n"/>
@@ -4615,7 +4699,11 @@
         </is>
       </c>
       <c r="I75" s="3" t="n"/>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="3" t="n"/>
@@ -4661,7 +4749,11 @@
         </is>
       </c>
       <c r="I76" s="3" t="n"/>
-      <c r="J76" s="2" t="n"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="3" t="n"/>
@@ -4703,7 +4795,11 @@
         </is>
       </c>
       <c r="I77" s="3" t="n"/>
-      <c r="J77" s="2" t="n"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="3" t="n"/>
@@ -4749,7 +4845,11 @@
         </is>
       </c>
       <c r="I78" s="3" t="n"/>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="3" t="n"/>
@@ -4795,7 +4895,11 @@
         </is>
       </c>
       <c r="I79" s="3" t="n"/>
-      <c r="J79" s="2" t="n"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="3" t="n"/>
@@ -4841,7 +4945,11 @@
         </is>
       </c>
       <c r="I80" s="3" t="n"/>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="3" t="n"/>
@@ -4883,7 +4991,11 @@
         </is>
       </c>
       <c r="I81" s="3" t="n"/>
-      <c r="J81" s="2" t="n"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="3" t="inlineStr">
@@ -4933,7 +5045,11 @@
         </is>
       </c>
       <c r="I82" s="3" t="n"/>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="3" t="n"/>
@@ -4979,7 +5095,11 @@
         </is>
       </c>
       <c r="I83" s="3" t="n"/>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="3" t="n"/>
@@ -5025,7 +5145,11 @@
         </is>
       </c>
       <c r="I84" s="3" t="n"/>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="3" t="n"/>
@@ -5071,7 +5195,11 @@
         </is>
       </c>
       <c r="I85" s="3" t="n"/>
-      <c r="J85" s="2" t="n"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="3" t="n"/>
@@ -5117,7 +5245,11 @@
         </is>
       </c>
       <c r="I86" s="3" t="n"/>
-      <c r="J86" s="2" t="n"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="3" t="n"/>
@@ -5163,7 +5295,11 @@
         </is>
       </c>
       <c r="I87" s="3" t="n"/>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="3" t="n"/>
@@ -5209,7 +5345,11 @@
         </is>
       </c>
       <c r="I88" s="3" t="n"/>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="3" t="n"/>
@@ -5255,7 +5395,11 @@
         </is>
       </c>
       <c r="I89" s="3" t="n"/>
-      <c r="J89" s="2" t="n"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="n"/>
       <c r="M89" s="3" t="n"/>
@@ -5301,7 +5445,11 @@
         </is>
       </c>
       <c r="I90" s="3" t="n"/>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
       <c r="M90" s="3" t="n"/>
@@ -5347,7 +5495,11 @@
         </is>
       </c>
       <c r="I91" s="3" t="n"/>
-      <c r="J91" s="2" t="n"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="n"/>
       <c r="M91" s="3" t="n"/>
@@ -5393,7 +5545,11 @@
         </is>
       </c>
       <c r="I92" s="3" t="n"/>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="3" t="n"/>
@@ -5439,7 +5595,11 @@
         </is>
       </c>
       <c r="I93" s="3" t="n"/>
-      <c r="J93" s="2" t="n"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="n"/>
       <c r="M93" s="3" t="n"/>
@@ -5481,7 +5641,11 @@
         </is>
       </c>
       <c r="I94" s="3" t="n"/>
-      <c r="J94" s="2" t="n"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="n"/>
       <c r="M94" s="3" t="n"/>
@@ -5527,7 +5691,11 @@
         </is>
       </c>
       <c r="I95" s="3" t="n"/>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="3" t="n"/>
@@ -5573,7 +5741,11 @@
         </is>
       </c>
       <c r="I96" s="3" t="n"/>
-      <c r="J96" s="2" t="n"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="3" t="n"/>
@@ -5619,7 +5791,11 @@
         </is>
       </c>
       <c r="I97" s="3" t="n"/>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="n"/>
       <c r="M97" s="3" t="n"/>
@@ -5665,7 +5841,11 @@
         </is>
       </c>
       <c r="I98" s="3" t="n"/>
-      <c r="J98" s="2" t="n"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="n"/>
       <c r="M98" s="3" t="n"/>
@@ -5707,7 +5887,11 @@
         </is>
       </c>
       <c r="I99" s="3" t="n"/>
-      <c r="J99" s="2" t="n"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
       <c r="M99" s="3" t="n"/>
@@ -5753,7 +5937,11 @@
         </is>
       </c>
       <c r="I100" s="3" t="n"/>
-      <c r="J100" s="2" t="n"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
       <c r="M100" s="3" t="n"/>
@@ -5799,7 +5987,11 @@
         </is>
       </c>
       <c r="I101" s="3" t="n"/>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
       <c r="M101" s="3" t="n"/>
@@ -5845,7 +6037,11 @@
         </is>
       </c>
       <c r="I102" s="3" t="n"/>
-      <c r="J102" s="2" t="n"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="3" t="n"/>
@@ -5891,7 +6087,11 @@
         </is>
       </c>
       <c r="I103" s="3" t="n"/>
-      <c r="J103" s="2" t="n"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="3" t="n"/>
@@ -5937,7 +6137,11 @@
         </is>
       </c>
       <c r="I104" s="3" t="n"/>
-      <c r="J104" s="2" t="n"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="3" t="n"/>
@@ -6381,7 +6585,11 @@
         </is>
       </c>
       <c r="I112" s="3" t="n"/>
-      <c r="J112" s="2" t="n"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="3" t="n"/>
@@ -6427,7 +6635,11 @@
         </is>
       </c>
       <c r="I113" s="3" t="n"/>
-      <c r="J113" s="2" t="n"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
       <c r="M113" s="3" t="n"/>
@@ -6473,7 +6685,11 @@
         </is>
       </c>
       <c r="I114" s="3" t="n"/>
-      <c r="J114" s="2" t="n"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="3" t="n"/>
@@ -6519,7 +6735,11 @@
         </is>
       </c>
       <c r="I115" s="3" t="n"/>
-      <c r="J115" s="2" t="n"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="n"/>
       <c r="M115" s="3" t="n"/>
@@ -6677,7 +6897,11 @@
         </is>
       </c>
       <c r="I118" s="3" t="n"/>
-      <c r="J118" s="2" t="n"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="n"/>
       <c r="M118" s="3" t="n"/>
@@ -6723,7 +6947,11 @@
         </is>
       </c>
       <c r="I119" s="3" t="n"/>
-      <c r="J119" s="2" t="n"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="n"/>
       <c r="M119" s="3" t="n"/>
@@ -6771,7 +6999,7 @@
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K120" s="2" t="n"/>
@@ -6782,7 +7010,7 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>待条件：需消防电气控制装置对端（FECbus）</t>
+          <t>待条件：需消防电气控制装置对端（FECbus）；⚠️标通过与待条件（需FECbus对端）矛盾，请复核</t>
         </is>
       </c>
       <c r="N120" s="2" t="n"/>
@@ -6823,7 +7051,11 @@
         </is>
       </c>
       <c r="I121" s="3" t="n"/>
-      <c r="J121" s="2" t="n"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K121" s="2" t="n"/>
       <c r="L121" s="2" t="n"/>
       <c r="M121" s="3" t="n"/>
@@ -6869,7 +7101,11 @@
         </is>
       </c>
       <c r="I122" s="3" t="n"/>
-      <c r="J122" s="2" t="n"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K122" s="2" t="n"/>
       <c r="L122" s="2" t="n"/>
       <c r="M122" s="3" t="n"/>
@@ -6915,7 +7151,11 @@
         </is>
       </c>
       <c r="I123" s="3" t="n"/>
-      <c r="J123" s="2" t="n"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K123" s="2" t="n"/>
       <c r="L123" s="2" t="n"/>
       <c r="M123" s="3" t="n"/>
@@ -6961,7 +7201,11 @@
         </is>
       </c>
       <c r="I124" s="3" t="n"/>
-      <c r="J124" s="2" t="n"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K124" s="2" t="n"/>
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="3" t="n"/>
@@ -7007,7 +7251,11 @@
         </is>
       </c>
       <c r="I125" s="3" t="n"/>
-      <c r="J125" s="2" t="n"/>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K125" s="2" t="n"/>
       <c r="L125" s="2" t="n"/>
       <c r="M125" s="3" t="n"/>
@@ -7053,7 +7301,11 @@
         </is>
       </c>
       <c r="I126" s="3" t="n"/>
-      <c r="J126" s="2" t="n"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K126" s="2" t="n"/>
       <c r="L126" s="2" t="n"/>
       <c r="M126" s="3" t="n"/>
@@ -7099,7 +7351,11 @@
         </is>
       </c>
       <c r="I127" s="3" t="n"/>
-      <c r="J127" s="2" t="n"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="3" t="n"/>
@@ -7357,7 +7613,11 @@
         </is>
       </c>
       <c r="I132" s="3" t="n"/>
-      <c r="J132" s="2" t="n"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="n"/>
       <c r="L132" s="2" t="n"/>
       <c r="M132" s="3" t="n"/>
@@ -7403,7 +7663,11 @@
         </is>
       </c>
       <c r="I133" s="3" t="n"/>
-      <c r="J133" s="2" t="n"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K133" s="2" t="n"/>
       <c r="L133" s="2" t="n"/>
       <c r="M133" s="3" t="n"/>
@@ -7449,7 +7713,11 @@
         </is>
       </c>
       <c r="I134" s="3" t="n"/>
-      <c r="J134" s="2" t="n"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
       <c r="M134" s="3" t="n"/>
@@ -7707,7 +7975,11 @@
         </is>
       </c>
       <c r="I139" s="3" t="n"/>
-      <c r="J139" s="2" t="n"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K139" s="2" t="n"/>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="3" t="n"/>
@@ -7753,7 +8025,11 @@
         </is>
       </c>
       <c r="I140" s="3" t="n"/>
-      <c r="J140" s="2" t="n"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="n"/>
       <c r="M140" s="3" t="n"/>
@@ -7795,7 +8071,11 @@
         </is>
       </c>
       <c r="I141" s="3" t="n"/>
-      <c r="J141" s="2" t="n"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K141" s="2" t="n"/>
       <c r="L141" s="2" t="n"/>
       <c r="M141" s="3" t="n"/>
@@ -7949,7 +8229,11 @@
         </is>
       </c>
       <c r="I144" s="3" t="n"/>
-      <c r="J144" s="2" t="n"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="n"/>
       <c r="M144" s="3" t="n"/>
@@ -23653,7 +23937,11 @@
         </is>
       </c>
       <c r="I444" s="3" t="n"/>
-      <c r="J444" s="2" t="n"/>
+      <c r="J444" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K444" s="2" t="n"/>
       <c r="L444" s="2" t="n"/>
       <c r="M444" s="3" t="n"/>
@@ -23699,7 +23987,11 @@
         </is>
       </c>
       <c r="I445" s="3" t="n"/>
-      <c r="J445" s="2" t="n"/>
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K445" s="2" t="n"/>
       <c r="L445" s="2" t="n"/>
       <c r="M445" s="3" t="n"/>
@@ -23745,7 +24037,11 @@
         </is>
       </c>
       <c r="I446" s="3" t="n"/>
-      <c r="J446" s="2" t="n"/>
+      <c r="J446" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K446" s="2" t="n"/>
       <c r="L446" s="2" t="n"/>
       <c r="M446" s="3" t="n"/>
@@ -23791,7 +24087,11 @@
         </is>
       </c>
       <c r="I447" s="3" t="n"/>
-      <c r="J447" s="2" t="n"/>
+      <c r="J447" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K447" s="2" t="n"/>
       <c r="L447" s="2" t="n"/>
       <c r="M447" s="3" t="n"/>
@@ -23837,7 +24137,11 @@
         </is>
       </c>
       <c r="I448" s="3" t="n"/>
-      <c r="J448" s="2" t="n"/>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K448" s="2" t="n"/>
       <c r="L448" s="2" t="n"/>
       <c r="M448" s="3" t="n"/>
@@ -23883,7 +24187,11 @@
         </is>
       </c>
       <c r="I449" s="3" t="n"/>
-      <c r="J449" s="2" t="n"/>
+      <c r="J449" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K449" s="2" t="n"/>
       <c r="L449" s="2" t="n"/>
       <c r="M449" s="3" t="n"/>
@@ -23929,7 +24237,11 @@
         </is>
       </c>
       <c r="I450" s="3" t="n"/>
-      <c r="J450" s="2" t="n"/>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K450" s="2" t="n"/>
       <c r="L450" s="2" t="n"/>
       <c r="M450" s="3" t="n"/>
@@ -23975,7 +24287,11 @@
         </is>
       </c>
       <c r="I451" s="3" t="n"/>
-      <c r="J451" s="2" t="n"/>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K451" s="2" t="n"/>
       <c r="L451" s="2" t="n"/>
       <c r="M451" s="3" t="n"/>
@@ -24021,7 +24337,11 @@
         </is>
       </c>
       <c r="I452" s="3" t="n"/>
-      <c r="J452" s="2" t="n"/>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K452" s="2" t="n"/>
       <c r="L452" s="2" t="n"/>
       <c r="M452" s="3" t="n"/>
@@ -24067,7 +24387,11 @@
         </is>
       </c>
       <c r="I453" s="3" t="n"/>
-      <c r="J453" s="2" t="n"/>
+      <c r="J453" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K453" s="2" t="n"/>
       <c r="L453" s="2" t="n"/>
       <c r="M453" s="3" t="n"/>
@@ -24113,7 +24437,11 @@
         </is>
       </c>
       <c r="I454" s="3" t="n"/>
-      <c r="J454" s="2" t="n"/>
+      <c r="J454" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K454" s="2" t="n"/>
       <c r="L454" s="2" t="n"/>
       <c r="M454" s="3" t="n"/>
@@ -24155,10 +24483,18 @@
         </is>
       </c>
       <c r="I455" s="3" t="n"/>
-      <c r="J455" s="2" t="n"/>
+      <c r="J455" s="2" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
       <c r="K455" s="2" t="n"/>
       <c r="L455" s="2" t="n"/>
-      <c r="M455" s="3" t="n"/>
+      <c r="M455" s="3" t="inlineStr">
+        <is>
+          <t>⚠️红线：延时0～30s可调+手动停止是GB16806必做项，不通过必须整改（非可选）</t>
+        </is>
+      </c>
       <c r="N455" s="2" t="n"/>
     </row>
     <row r="456">
@@ -24201,7 +24537,11 @@
         </is>
       </c>
       <c r="I456" s="3" t="n"/>
-      <c r="J456" s="2" t="n"/>
+      <c r="J456" s="2" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
       <c r="K456" s="2" t="n"/>
       <c r="L456" s="2" t="n"/>
       <c r="M456" s="3" t="n"/>
@@ -24247,7 +24587,11 @@
         </is>
       </c>
       <c r="I457" s="3" t="n"/>
-      <c r="J457" s="2" t="n"/>
+      <c r="J457" s="2" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
       <c r="K457" s="2" t="n"/>
       <c r="L457" s="2" t="n"/>
       <c r="M457" s="3" t="n"/>
@@ -24289,7 +24633,11 @@
         </is>
       </c>
       <c r="I458" s="3" t="n"/>
-      <c r="J458" s="2" t="n"/>
+      <c r="J458" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K458" s="2" t="n"/>
       <c r="L458" s="2" t="n"/>
       <c r="M458" s="3" t="n"/>
@@ -24335,7 +24683,11 @@
         </is>
       </c>
       <c r="I459" s="3" t="n"/>
-      <c r="J459" s="2" t="n"/>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K459" s="2" t="n"/>
       <c r="L459" s="2" t="n"/>
       <c r="M459" s="3" t="n"/>
@@ -24381,7 +24733,11 @@
         </is>
       </c>
       <c r="I460" s="3" t="n"/>
-      <c r="J460" s="2" t="n"/>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K460" s="2" t="n"/>
       <c r="L460" s="2" t="n"/>
       <c r="M460" s="3" t="n"/>
@@ -24427,7 +24783,11 @@
         </is>
       </c>
       <c r="I461" s="3" t="n"/>
-      <c r="J461" s="2" t="n"/>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K461" s="2" t="n"/>
       <c r="L461" s="2" t="n"/>
       <c r="M461" s="3" t="n"/>
@@ -24473,7 +24833,11 @@
         </is>
       </c>
       <c r="I462" s="3" t="n"/>
-      <c r="J462" s="2" t="n"/>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K462" s="2" t="n"/>
       <c r="L462" s="2" t="n"/>
       <c r="M462" s="3" t="n"/>
@@ -24519,7 +24883,11 @@
         </is>
       </c>
       <c r="I463" s="3" t="n"/>
-      <c r="J463" s="2" t="n"/>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K463" s="2" t="n"/>
       <c r="L463" s="2" t="n"/>
       <c r="M463" s="3" t="n"/>
@@ -24565,7 +24933,11 @@
         </is>
       </c>
       <c r="I464" s="3" t="n"/>
-      <c r="J464" s="2" t="n"/>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K464" s="2" t="n"/>
       <c r="L464" s="2" t="n"/>
       <c r="M464" s="3" t="n"/>
@@ -24607,7 +24979,11 @@
         </is>
       </c>
       <c r="I465" s="3" t="n"/>
-      <c r="J465" s="2" t="n"/>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K465" s="2" t="n"/>
       <c r="L465" s="2" t="n"/>
       <c r="M465" s="3" t="n"/>
@@ -24653,7 +25029,11 @@
         </is>
       </c>
       <c r="I466" s="3" t="n"/>
-      <c r="J466" s="2" t="n"/>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K466" s="2" t="n"/>
       <c r="L466" s="2" t="n"/>
       <c r="M466" s="3" t="n"/>
@@ -24699,7 +25079,11 @@
         </is>
       </c>
       <c r="I467" s="3" t="n"/>
-      <c r="J467" s="2" t="n"/>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K467" s="2" t="n"/>
       <c r="L467" s="2" t="n"/>
       <c r="M467" s="3" t="n"/>
@@ -24787,7 +25171,11 @@
         </is>
       </c>
       <c r="I469" s="3" t="n"/>
-      <c r="J469" s="2" t="n"/>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K469" s="2" t="n"/>
       <c r="L469" s="2" t="n"/>
       <c r="M469" s="3" t="n"/>
@@ -24833,7 +25221,11 @@
         </is>
       </c>
       <c r="I470" s="3" t="n"/>
-      <c r="J470" s="2" t="n"/>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K470" s="2" t="n"/>
       <c r="L470" s="2" t="n"/>
       <c r="M470" s="3" t="n"/>
@@ -24879,7 +25271,11 @@
         </is>
       </c>
       <c r="I471" s="3" t="n"/>
-      <c r="J471" s="2" t="n"/>
+      <c r="J471" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K471" s="2" t="n"/>
       <c r="L471" s="2" t="n"/>
       <c r="M471" s="3" t="n"/>
@@ -24925,7 +25321,11 @@
         </is>
       </c>
       <c r="I472" s="3" t="n"/>
-      <c r="J472" s="2" t="n"/>
+      <c r="J472" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K472" s="2" t="n"/>
       <c r="L472" s="2" t="n"/>
       <c r="M472" s="3" t="n"/>
@@ -24971,7 +25371,11 @@
         </is>
       </c>
       <c r="I473" s="3" t="n"/>
-      <c r="J473" s="2" t="n"/>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K473" s="2" t="n"/>
       <c r="L473" s="2" t="n"/>
       <c r="M473" s="3" t="n"/>
@@ -25017,7 +25421,11 @@
         </is>
       </c>
       <c r="I474" s="3" t="n"/>
-      <c r="J474" s="2" t="n"/>
+      <c r="J474" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K474" s="2" t="n"/>
       <c r="L474" s="2" t="n"/>
       <c r="M474" s="3" t="n"/>
@@ -25059,7 +25467,11 @@
         </is>
       </c>
       <c r="I475" s="3" t="n"/>
-      <c r="J475" s="2" t="n"/>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K475" s="2" t="n"/>
       <c r="L475" s="2" t="n"/>
       <c r="M475" s="3" t="n"/>
@@ -25105,7 +25517,11 @@
         </is>
       </c>
       <c r="I476" s="3" t="n"/>
-      <c r="J476" s="2" t="n"/>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K476" s="2" t="n"/>
       <c r="L476" s="2" t="n"/>
       <c r="M476" s="3" t="n"/>
@@ -25151,7 +25567,11 @@
         </is>
       </c>
       <c r="I477" s="3" t="n"/>
-      <c r="J477" s="2" t="n"/>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K477" s="2" t="n"/>
       <c r="L477" s="2" t="n"/>
       <c r="M477" s="3" t="n"/>
@@ -25193,7 +25613,11 @@
         </is>
       </c>
       <c r="I478" s="3" t="n"/>
-      <c r="J478" s="2" t="n"/>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K478" s="2" t="n"/>
       <c r="L478" s="2" t="n"/>
       <c r="M478" s="3" t="n"/>
@@ -25239,7 +25663,11 @@
         </is>
       </c>
       <c r="I479" s="3" t="n"/>
-      <c r="J479" s="2" t="n"/>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K479" s="2" t="n"/>
       <c r="L479" s="2" t="n"/>
       <c r="M479" s="3" t="n"/>
@@ -25343,7 +25771,11 @@
         </is>
       </c>
       <c r="I481" s="3" t="n"/>
-      <c r="J481" s="2" t="n"/>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K481" s="2" t="n"/>
       <c r="L481" s="2" t="n"/>
       <c r="M481" s="3" t="n"/>
@@ -25389,7 +25821,11 @@
         </is>
       </c>
       <c r="I482" s="3" t="n"/>
-      <c r="J482" s="2" t="n"/>
+      <c r="J482" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K482" s="2" t="n"/>
       <c r="L482" s="2" t="n"/>
       <c r="M482" s="3" t="n"/>
@@ -25431,7 +25867,11 @@
         </is>
       </c>
       <c r="I483" s="3" t="n"/>
-      <c r="J483" s="2" t="n"/>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K483" s="2" t="n"/>
       <c r="L483" s="2" t="n"/>
       <c r="M483" s="3" t="n"/>
@@ -25477,7 +25917,11 @@
         </is>
       </c>
       <c r="I484" s="3" t="n"/>
-      <c r="J484" s="2" t="n"/>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K484" s="2" t="n"/>
       <c r="L484" s="2" t="n"/>
       <c r="M484" s="3" t="n"/>
@@ -25523,7 +25967,11 @@
         </is>
       </c>
       <c r="I485" s="3" t="n"/>
-      <c r="J485" s="2" t="n"/>
+      <c r="J485" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K485" s="2" t="n"/>
       <c r="L485" s="2" t="n"/>
       <c r="M485" s="3" t="n"/>
@@ -25569,7 +26017,11 @@
         </is>
       </c>
       <c r="I486" s="3" t="n"/>
-      <c r="J486" s="2" t="n"/>
+      <c r="J486" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K486" s="2" t="n"/>
       <c r="L486" s="2" t="n"/>
       <c r="M486" s="3" t="n"/>
@@ -25615,7 +26067,11 @@
         </is>
       </c>
       <c r="I487" s="3" t="n"/>
-      <c r="J487" s="2" t="n"/>
+      <c r="J487" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K487" s="2" t="n"/>
       <c r="L487" s="2" t="n"/>
       <c r="M487" s="3" t="n"/>
@@ -25661,7 +26117,11 @@
         </is>
       </c>
       <c r="I488" s="3" t="n"/>
-      <c r="J488" s="2" t="n"/>
+      <c r="J488" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K488" s="2" t="n"/>
       <c r="L488" s="2" t="n"/>
       <c r="M488" s="3" t="n"/>
@@ -25707,7 +26167,11 @@
         </is>
       </c>
       <c r="I489" s="3" t="n"/>
-      <c r="J489" s="2" t="n"/>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K489" s="2" t="n"/>
       <c r="L489" s="2" t="n"/>
       <c r="M489" s="3" t="n"/>
@@ -33407,8 +33871,69 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="15" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" s="15" t="inlineStr">
+        <is>
+          <t>FT-04.5</t>
+        </is>
+      </c>
+      <c r="C635" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D635" s="15" t="inlineStr">
+        <is>
+          <t>消音灯·新故障熄灭</t>
+        </is>
+      </c>
+      <c r="E635" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F635" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.2/5.3.1.5</t>
+        </is>
+      </c>
+      <c r="G635" s="15" t="inlineStr">
+        <is>
+          <t>故障①→消音（灯亮）→制造故障②（拔另一部件支线）</t>
+        </is>
+      </c>
+      <c r="H635" s="15" t="inlineStr">
+        <is>
+          <t>声再启动的同时消音灯熄灭——消音灯指示『当前消音状态』，声音重新启动即状态结束</t>
+        </is>
+      </c>
+      <c r="I635" s="15" t="inlineStr">
+        <is>
+          <t>新故障输入后消音灯仍亮</t>
+        </is>
+      </c>
+      <c r="J635" s="15" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="K635" s="15" t="inlineStr"/>
+      <c r="L635" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M635" s="15" t="inlineStr">
+        <is>
+          <t>现场实测补充用例；声再启动正常（FT-04.1 通过），仅灯状态机错；疑与 UI-11.5 消音灯常亮同源</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M634"/>
+  <autoFilter ref="A1:M635"/>
   <dataValidations count="11">
     <dataValidation sqref="J2:J606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
@@ -33479,9 +34004,8 @@
           <t>用例总数</t>
         </is>
       </c>
-      <c r="B2">
-        <f>COUNTA(测试执行表!$B$2:$B$606)</f>
-        <v/>
+      <c r="B2" t="n">
+        <v>634</v>
       </c>
     </row>
     <row r="3">
@@ -34672,7 +35196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35816,6 +36340,38 @@
       <c r="F40" s="15" t="inlineStr">
         <is>
           <t>★ 全局导航缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>FT-04.5</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>面板/消音</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>消音灯·新故障不熄灭</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>新故障输入后消音灯仍亮（声再启动正常）</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>UI-11.5 消音灯常亮·不自动复位</t>
         </is>
       </c>
     </row>
@@ -35880,23 +36436,23 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(测试执行表!C2:C634,A2)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A2)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A2,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G2">
@@ -35911,23 +36467,23 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(测试执行表!C2:C634,A3)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A3)</f>
         <v/>
       </c>
       <c r="C3">
-        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A3,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G3">
@@ -35942,23 +36498,23 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!C2:C634,A4)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A4)</f>
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F4">
-        <f>COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A4,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G4">
@@ -35973,23 +36529,23 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!C2:C634,A5)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A5)</f>
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F5">
-        <f>COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A5,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G5">
@@ -36004,23 +36560,23 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!C2:C634,A6)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A6)</f>
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A6,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G6">
@@ -36035,23 +36591,23 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(测试执行表!C2:C634,A7)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A7)</f>
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F7">
-        <f>COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A7,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G7">
@@ -36066,23 +36622,23 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(测试执行表!C2:C634,A8)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A8)</f>
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F8">
-        <f>COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A8,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G8">
@@ -36097,23 +36653,23 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(测试执行表!C2:C634,A9)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A9)</f>
         <v/>
       </c>
       <c r="C9">
-        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F9">
-        <f>COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A9,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G9">
@@ -36128,23 +36684,23 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIF(测试执行表!C2:C634,A10)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A10)</f>
         <v/>
       </c>
       <c r="C10">
-        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F10">
-        <f>COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A10,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G10">
@@ -36159,23 +36715,23 @@
         </is>
       </c>
       <c r="B11">
-        <f>COUNTIF(测试执行表!C2:C634,A11)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A11)</f>
         <v/>
       </c>
       <c r="C11">
-        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F11">
-        <f>COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A11,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G11">
@@ -36190,23 +36746,23 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTIF(测试执行表!C2:C634,A12)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A12)</f>
         <v/>
       </c>
       <c r="C12">
-        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A12,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G12">
@@ -36221,23 +36777,23 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTIF(测试执行表!C2:C634,A13)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A13)</f>
         <v/>
       </c>
       <c r="C13">
-        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F13">
-        <f>COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A13,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G13">
@@ -36252,23 +36808,23 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF(测试执行表!C2:C634,A14)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A14)</f>
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F14">
-        <f>COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A14,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G14">
@@ -36283,23 +36839,23 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF(测试执行表!C2:C634,A15)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A15)</f>
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F15">
-        <f>COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A15,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G15">
@@ -36314,23 +36870,23 @@
         </is>
       </c>
       <c r="B16">
-        <f>COUNTIF(测试执行表!C2:C634,A16)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A16)</f>
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F16">
-        <f>COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A16,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G16">
@@ -36345,23 +36901,23 @@
         </is>
       </c>
       <c r="B17">
-        <f>COUNTIF(测试执行表!C2:C634,A17)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A17)</f>
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F17">
-        <f>COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A17,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G17">
@@ -36376,23 +36932,23 @@
         </is>
       </c>
       <c r="B18">
-        <f>COUNTIF(测试执行表!C2:C634,A18)</f>
+        <f>COUNTIF(测试执行表!C2:C635,A18)</f>
         <v/>
       </c>
       <c r="C18">
-        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"通过")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"不通过")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"不适用")</f>
         <v/>
       </c>
       <c r="F18">
-        <f>COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"待测")+COUNTIFS(测试执行表!C2:C634,A18,测试执行表!J2:J634,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"暂不测试")</f>
         <v/>
       </c>
       <c r="G18">
@@ -36411,7 +36967,7 @@
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>SUM(C2:C18)</f>
+        <f>SUM(C2:C635)</f>
         <v/>
       </c>
       <c r="D19" s="10">

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -1907,7 +1907,7 @@
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>待条件：需第2个火警触发部位（再加1只烟感或手报）——消音后的『新火警』须来自新部位</t>
+          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>待条件：需第2个火警触发部位（同上）</t>
+          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -6787,7 +6787,7 @@
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>待条件：需第2个火警触发部位（消音后新火警再响）</t>
+          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
         </is>
       </c>
       <c r="N116" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -841,16 +841,20 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>部位显示正常；时间缺年份（同源 UI-14.6 时钟停00年），修复后复验</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -953,7 +957,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -1011,7 +1015,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1069,7 +1073,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1127,7 +1131,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1301,7 +1305,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1907,7 +1911,7 @@
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
+          <t>待条件：需第2报警信号源（必做项，补第2只烟感/手报后测）</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
@@ -1965,7 +1969,7 @@
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -1976,7 +1980,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
+          <t>待条件：需第2报警信号源（必做项，补第2只烟感/手报后测）</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -2023,7 +2027,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -2139,7 +2143,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2197,7 +2201,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2255,7 +2259,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2313,7 +2317,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2371,7 +2375,7 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -3399,7 +3403,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K50" s="2" t="n"/>
@@ -3507,7 +3511,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K52" s="2" t="n"/>
@@ -3885,12 +3889,16 @@
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
-      <c r="M59" s="3" t="n"/>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>子项①③（无延时/手动放行）通过；②延时分支不适用（产品未实现输出延时）——P0 总案按适用子项判</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="n"/>
     </row>
     <row r="60">
@@ -3990,7 +3998,11 @@
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
-      <c r="M61" s="3" t="n"/>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>延时条件分支：输出延时为可选功能（5.4.2.10 条件适用），产品未实现→分支不适用</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="n"/>
     </row>
     <row r="62">
@@ -4040,7 +4052,11 @@
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
-      <c r="M62" s="3" t="n"/>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>延时条件分支：输出延时为可选功能（5.4.2.10 条件适用），产品未实现→分支不适用</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="n"/>
     </row>
     <row r="63">
@@ -4451,7 +4467,7 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K70" s="2" t="n"/>
@@ -6787,7 +6803,7 @@
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K116" s="2" t="n"/>
@@ -6798,7 +6814,7 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>单回路单烟感无法产生第二报警信号（2026-08-19 用户决定标不适用）——注意：本条为必做项非条款豁免，补第2只烟感/手报后须回测</t>
+          <t>待条件：需第2报警信号源（必做项，补第2只烟感/手报后测）</t>
         </is>
       </c>
       <c r="N116" s="2" t="n"/>
@@ -8511,7 +8527,7 @@
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8569,7 +8585,7 @@
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8623,7 +8639,7 @@
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K152" s="2" t="n"/>
@@ -8681,7 +8697,7 @@
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K153" s="2" t="n"/>
@@ -8739,7 +8755,7 @@
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K154" s="2" t="n"/>
@@ -8797,7 +8813,7 @@
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K155" s="2" t="n"/>
@@ -8855,7 +8871,7 @@
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K156" s="2" t="n"/>
@@ -11911,7 +11927,7 @@
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K220" s="2" t="n"/>
@@ -11973,7 +11989,7 @@
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K221" s="2" t="n"/>
@@ -12035,7 +12051,7 @@
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K222" s="2" t="n"/>
@@ -12097,7 +12113,7 @@
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K223" s="2" t="n"/>
@@ -12159,7 +12175,7 @@
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K224" s="2" t="n"/>
@@ -13235,7 +13251,7 @@
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K244" s="2" t="n"/>
@@ -13293,7 +13309,7 @@
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K245" s="2" t="n"/>
@@ -13351,7 +13367,7 @@
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K246" s="2" t="n"/>
@@ -13405,7 +13421,7 @@
       </c>
       <c r="J247" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K247" s="2" t="n"/>
@@ -13463,7 +13479,7 @@
       </c>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K248" s="2" t="n"/>
@@ -13521,7 +13537,7 @@
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K249" s="2" t="n"/>
@@ -13575,7 +13591,7 @@
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K250" s="2" t="n"/>
@@ -13633,7 +13649,7 @@
       </c>
       <c r="J251" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K251" s="2" t="n"/>
@@ -13691,7 +13707,7 @@
       </c>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K252" s="2" t="n"/>
@@ -13837,7 +13853,7 @@
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K255" s="2" t="n"/>
@@ -13895,7 +13911,7 @@
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K256" s="2" t="n"/>
@@ -14225,7 +14241,7 @@
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K263" s="2" t="n"/>
@@ -14731,7 +14747,7 @@
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K274" s="2" t="n"/>
@@ -14789,7 +14805,7 @@
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K275" s="2" t="n"/>
@@ -14847,7 +14863,7 @@
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K276" s="2" t="n"/>
@@ -14905,7 +14921,7 @@
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K277" s="2" t="n"/>
@@ -14963,7 +14979,7 @@
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K278" s="2" t="n"/>
@@ -15017,7 +15033,7 @@
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K279" s="2" t="n"/>
@@ -15075,7 +15091,7 @@
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K280" s="2" t="n"/>
@@ -15133,7 +15149,7 @@
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K281" s="2" t="n"/>
@@ -15191,7 +15207,7 @@
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K282" s="2" t="n"/>
@@ -15245,7 +15261,7 @@
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K283" s="2" t="n"/>
@@ -15303,7 +15319,7 @@
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K284" s="2" t="n"/>
@@ -15361,7 +15377,7 @@
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K285" s="2" t="n"/>
@@ -15419,7 +15435,7 @@
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K286" s="2" t="n"/>
@@ -15477,7 +15493,7 @@
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K287" s="2" t="n"/>
@@ -15535,7 +15551,7 @@
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K288" s="2" t="n"/>
@@ -15589,7 +15605,7 @@
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K289" s="2" t="n"/>
@@ -15647,7 +15663,7 @@
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K290" s="2" t="n"/>
@@ -15705,7 +15721,7 @@
       </c>
       <c r="J291" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K291" s="2" t="n"/>
@@ -15763,7 +15779,7 @@
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K292" s="2" t="n"/>
@@ -15817,7 +15833,7 @@
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K293" s="2" t="n"/>
@@ -15875,7 +15891,7 @@
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K294" s="2" t="n"/>
@@ -15933,7 +15949,7 @@
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K295" s="2" t="n"/>
@@ -16037,7 +16053,7 @@
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K297" s="2" t="n"/>
@@ -21567,7 +21583,7 @@
       </c>
       <c r="J400" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K400" s="2" t="n"/>
@@ -21629,7 +21645,7 @@
       </c>
       <c r="J401" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K401" s="2" t="n"/>
@@ -21691,7 +21707,7 @@
       </c>
       <c r="J402" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K402" s="2" t="n"/>
@@ -23027,7 +23043,7 @@
       </c>
       <c r="J426" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K426" s="2" t="n"/>
@@ -25719,7 +25735,7 @@
       </c>
       <c r="J480" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K480" s="2" t="n"/>
@@ -27035,7 +27051,7 @@
       </c>
       <c r="J508" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K508" s="2" t="n"/>
@@ -28307,7 +28323,7 @@
       </c>
       <c r="J536" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K536" s="2" t="n"/>
@@ -28365,7 +28381,7 @@
       </c>
       <c r="J537" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K537" s="2" t="n"/>
@@ -28423,7 +28439,7 @@
       </c>
       <c r="J538" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K538" s="2" t="n"/>
@@ -28481,7 +28497,7 @@
       </c>
       <c r="J539" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K539" s="2" t="n"/>
@@ -28539,7 +28555,7 @@
       </c>
       <c r="J540" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K540" s="2" t="n"/>
@@ -29309,7 +29325,7 @@
       </c>
       <c r="J557" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K557" s="2" t="n"/>
@@ -29367,7 +29383,7 @@
       </c>
       <c r="J558" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K558" s="2" t="n"/>
@@ -29425,7 +29441,7 @@
       </c>
       <c r="J559" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K559" s="2" t="n"/>
@@ -29483,7 +29499,7 @@
       </c>
       <c r="J560" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K560" s="2" t="n"/>
@@ -29537,7 +29553,7 @@
       </c>
       <c r="J561" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K561" s="2" t="n"/>
@@ -29595,7 +29611,7 @@
       </c>
       <c r="J562" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K562" s="2" t="n"/>
@@ -29653,7 +29669,7 @@
       </c>
       <c r="J563" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K563" s="2" t="n"/>
@@ -29711,7 +29727,7 @@
       </c>
       <c r="J564" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K564" s="2" t="n"/>
@@ -29765,7 +29781,7 @@
       </c>
       <c r="J565" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K565" s="2" t="n"/>
@@ -29823,7 +29839,7 @@
       </c>
       <c r="J566" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K566" s="2" t="n"/>
@@ -29881,7 +29897,7 @@
       </c>
       <c r="J567" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K567" s="2" t="n"/>
@@ -29935,7 +29951,7 @@
       </c>
       <c r="J568" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K568" s="2" t="n"/>
@@ -29993,7 +30009,7 @@
       </c>
       <c r="J569" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K569" s="2" t="n"/>
@@ -30051,7 +30067,7 @@
       </c>
       <c r="J570" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K570" s="2" t="n"/>
@@ -30105,7 +30121,7 @@
       </c>
       <c r="J571" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K571" s="2" t="n"/>
@@ -30163,7 +30179,7 @@
       </c>
       <c r="J572" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K572" s="2" t="n"/>
@@ -30221,7 +30237,7 @@
       </c>
       <c r="J573" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K573" s="2" t="n"/>
@@ -30275,7 +30291,7 @@
       </c>
       <c r="J574" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K574" s="2" t="n"/>
@@ -30333,7 +30349,7 @@
       </c>
       <c r="J575" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K575" s="2" t="n"/>
@@ -30391,7 +30407,7 @@
       </c>
       <c r="J576" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K576" s="2" t="n"/>
@@ -30445,7 +30461,7 @@
       </c>
       <c r="J577" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K577" s="2" t="n"/>
@@ -30503,7 +30519,7 @@
       </c>
       <c r="J578" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K578" s="2" t="n"/>
@@ -30561,7 +30577,7 @@
       </c>
       <c r="J579" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K579" s="2" t="n"/>
@@ -30615,7 +30631,7 @@
       </c>
       <c r="J580" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K580" s="2" t="n"/>
@@ -30673,7 +30689,7 @@
       </c>
       <c r="J581" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K581" s="2" t="n"/>
@@ -30731,7 +30747,7 @@
       </c>
       <c r="J582" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K582" s="2" t="n"/>
@@ -30785,7 +30801,7 @@
       </c>
       <c r="J583" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K583" s="2" t="n"/>
@@ -30843,7 +30859,7 @@
       </c>
       <c r="J584" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K584" s="2" t="n"/>
@@ -30901,7 +30917,7 @@
       </c>
       <c r="J585" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K585" s="2" t="n"/>
@@ -30955,7 +30971,7 @@
       </c>
       <c r="J586" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K586" s="2" t="n"/>
@@ -31013,7 +31029,7 @@
       </c>
       <c r="J587" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K587" s="2" t="n"/>
@@ -31071,7 +31087,7 @@
       </c>
       <c r="J588" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K588" s="2" t="n"/>
@@ -31125,7 +31141,7 @@
       </c>
       <c r="J589" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K589" s="2" t="n"/>
@@ -31183,7 +31199,7 @@
       </c>
       <c r="J590" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K590" s="2" t="n"/>
@@ -31241,7 +31257,7 @@
       </c>
       <c r="J591" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K591" s="2" t="n"/>
@@ -31299,7 +31315,7 @@
       </c>
       <c r="J592" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K592" s="2" t="n"/>
@@ -31353,7 +31369,7 @@
       </c>
       <c r="J593" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K593" s="2" t="n"/>
@@ -31411,7 +31427,7 @@
       </c>
       <c r="J594" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K594" s="2" t="n"/>
@@ -31469,7 +31485,7 @@
       </c>
       <c r="J595" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K595" s="2" t="n"/>
@@ -31523,7 +31539,7 @@
       </c>
       <c r="J596" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K596" s="2" t="n"/>
@@ -31581,7 +31597,7 @@
       </c>
       <c r="J597" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K597" s="2" t="n"/>
@@ -31639,7 +31655,7 @@
       </c>
       <c r="J598" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K598" s="2" t="n"/>
@@ -31693,7 +31709,7 @@
       </c>
       <c r="J599" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K599" s="2" t="n"/>
@@ -31747,7 +31763,7 @@
       </c>
       <c r="J600" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K600" s="2" t="n"/>
@@ -31805,7 +31821,7 @@
       </c>
       <c r="J601" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K601" s="2" t="n"/>
@@ -31863,7 +31879,7 @@
       </c>
       <c r="J602" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K602" s="2" t="n"/>
@@ -31921,7 +31937,7 @@
       </c>
       <c r="J603" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K603" s="2" t="n"/>
@@ -31979,7 +31995,7 @@
       </c>
       <c r="J604" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K604" s="2" t="n"/>
@@ -32037,7 +32053,7 @@
       </c>
       <c r="J605" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K605" s="2" t="n"/>
@@ -32095,7 +32111,7 @@
       </c>
       <c r="J606" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K606" s="2" t="n"/>
@@ -32153,7 +32169,7 @@
       </c>
       <c r="J607" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K607" s="2" t="n"/>
@@ -32211,7 +32227,7 @@
       </c>
       <c r="J608" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K608" s="2" t="n"/>
@@ -32269,7 +32285,7 @@
       </c>
       <c r="J609" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K609" s="2" t="n"/>
@@ -32327,7 +32343,7 @@
       </c>
       <c r="J610" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K610" s="2" t="n"/>
@@ -32381,7 +32397,7 @@
       </c>
       <c r="J611" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K611" s="2" t="n"/>
@@ -32439,7 +32455,7 @@
       </c>
       <c r="J612" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K612" s="2" t="n"/>
@@ -32497,7 +32513,7 @@
       </c>
       <c r="J613" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K613" s="2" t="n"/>
@@ -32555,7 +32571,7 @@
       </c>
       <c r="J614" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K614" s="2" t="n"/>
@@ -32613,7 +32629,7 @@
       </c>
       <c r="J615" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K615" s="2" t="n"/>
@@ -32671,7 +32687,7 @@
       </c>
       <c r="J616" s="6" t="inlineStr">
         <is>
-          <t>暂不测试</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K616" s="2" t="n"/>
@@ -33934,39 +33950,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M635"/>
-  <dataValidations count="11">
-    <dataValidation sqref="J2:J606" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J608" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J611" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J614" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J617" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J623" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J628" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J630" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J631" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J631" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J634" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"通过,不通过,不适用,待测,暂不测试"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J635" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"通过,不通过,不适用,待测"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -14,7 +14,7 @@
     <sheet name="分组统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$635</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$643</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N635"/>
+  <dimension ref="A1:N643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7369,12 +7369,16 @@
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>待测</t>
         </is>
       </c>
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
-      <c r="M127" s="3" t="n"/>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 按条款项拆分为 .1～.5——原整案"通过"继承给 .1 断路；短路/接地/探头若当时已做，请把对应子行勾回通过</t>
+        </is>
+      </c>
       <c r="N127" s="2" t="n"/>
     </row>
     <row r="128">
@@ -33948,8 +33952,428 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="15" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" s="15" t="inlineStr">
+        <is>
+          <t>FT-01.1</t>
+        </is>
+      </c>
+      <c r="C636" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D636" s="15" t="inlineStr">
+        <is>
+          <t>回路断路</t>
+        </is>
+      </c>
+      <c r="E636" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F636" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 a)</t>
+        </is>
+      </c>
+      <c r="G636" s="15" t="inlineStr">
+        <is>
+          <t>拔部件支线</t>
+        </is>
+      </c>
+      <c r="H636" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障并指示部位</t>
+        </is>
+      </c>
+      <c r="I636" s="15" t="inlineStr"/>
+      <c r="J636" s="15" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K636" s="15" t="inlineStr"/>
+      <c r="L636" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M636" s="15" t="inlineStr">
+        <is>
+          <t>继承原 FT-01 整案通过（断路已实测：输入1断路故障）</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="15" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" s="15" t="inlineStr">
+        <is>
+          <t>FT-01.2</t>
+        </is>
+      </c>
+      <c r="C637" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D637" s="15" t="inlineStr">
+        <is>
+          <t>回路短路</t>
+        </is>
+      </c>
+      <c r="E637" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F637" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 a)</t>
+        </is>
+      </c>
+      <c r="G637" s="15" t="inlineStr">
+        <is>
+          <t>总线两线短接</t>
+        </is>
+      </c>
+      <c r="H637" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障（总线制短路应报故障）</t>
+        </is>
+      </c>
+      <c r="I637" s="15" t="inlineStr"/>
+      <c r="J637" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K637" s="15" t="inlineStr"/>
+      <c r="L637" s="15" t="inlineStr"/>
+      <c r="M637" s="15" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="15" t="n">
+        <v>637</v>
+      </c>
+      <c r="B638" s="15" t="inlineStr">
+        <is>
+          <t>FT-01.3</t>
+        </is>
+      </c>
+      <c r="C638" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D638" s="15" t="inlineStr">
+        <is>
+          <t>影响功能的接地</t>
+        </is>
+      </c>
+      <c r="E638" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F638" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 a)</t>
+        </is>
+      </c>
+      <c r="G638" s="15" t="inlineStr">
+        <is>
+          <t>回路线直接碰机壳</t>
+        </is>
+      </c>
+      <c r="H638" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障；火警下仍须显示（尾注例外）</t>
+        </is>
+      </c>
+      <c r="I638" s="15" t="inlineStr"/>
+      <c r="J638" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K638" s="15" t="inlineStr"/>
+      <c r="L638" s="15" t="inlineStr"/>
+      <c r="M638" s="15" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="15" t="n">
+        <v>638</v>
+      </c>
+      <c r="B639" s="15" t="inlineStr">
+        <is>
+          <t>FT-01.4</t>
+        </is>
+      </c>
+      <c r="C639" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D639" s="15" t="inlineStr">
+        <is>
+          <t>探头与底座断路</t>
+        </is>
+      </c>
+      <c r="E639" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F639" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 a) 尾句</t>
+        </is>
+      </c>
+      <c r="G639" s="15" t="inlineStr">
+        <is>
+          <t>拧下探头保留底座</t>
+        </is>
+      </c>
+      <c r="H639" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报该部位故障（防拆）</t>
+        </is>
+      </c>
+      <c r="I639" s="15" t="inlineStr"/>
+      <c r="J639" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K639" s="15" t="inlineStr"/>
+      <c r="L639" s="15" t="inlineStr"/>
+      <c r="M639" s="15" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="15" t="n">
+        <v>639</v>
+      </c>
+      <c r="B640" s="15" t="inlineStr">
+        <is>
+          <t>FT-01.5</t>
+        </is>
+      </c>
+      <c r="C640" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D640" s="15" t="inlineStr">
+        <is>
+          <t>手报及传输部件连线故障</t>
+        </is>
+      </c>
+      <c r="E640" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F640" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 a)</t>
+        </is>
+      </c>
+      <c r="G640" s="15" t="inlineStr">
+        <is>
+          <t>断/短/接地分别制造</t>
+        </is>
+      </c>
+      <c r="H640" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障指示部位</t>
+        </is>
+      </c>
+      <c r="I640" s="15" t="inlineStr"/>
+      <c r="J640" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K640" s="15" t="inlineStr"/>
+      <c r="L640" s="15" t="inlineStr"/>
+      <c r="M640" s="15" t="inlineStr">
+        <is>
+          <t>待条件：需手报</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="15" t="n">
+        <v>640</v>
+      </c>
+      <c r="B641" s="15" t="inlineStr">
+        <is>
+          <t>FT-02.3</t>
+        </is>
+      </c>
+      <c r="C641" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D641" s="15" t="inlineStr">
+        <is>
+          <t>火灾显示盘连线故障</t>
+        </is>
+      </c>
+      <c r="E641" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F641" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 b)</t>
+        </is>
+      </c>
+      <c r="G641" s="15" t="inlineStr">
+        <is>
+          <t>断/短/接地分别制造</t>
+        </is>
+      </c>
+      <c r="H641" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障指示部位</t>
+        </is>
+      </c>
+      <c r="I641" s="15" t="inlineStr"/>
+      <c r="J641" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K641" s="15" t="inlineStr"/>
+      <c r="L641" s="15" t="inlineStr"/>
+      <c r="M641" s="15" t="inlineStr">
+        <is>
+          <t>待条件：需火灾显示盘；可先用注册无硬件法验监督路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="15" t="n">
+        <v>641</v>
+      </c>
+      <c r="B642" s="15" t="inlineStr">
+        <is>
+          <t>FT-02.4</t>
+        </is>
+      </c>
+      <c r="C642" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D642" s="15" t="inlineStr">
+        <is>
+          <t>传输设备连线故障</t>
+        </is>
+      </c>
+      <c r="E642" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F642" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 c)</t>
+        </is>
+      </c>
+      <c r="G642" s="15" t="inlineStr">
+        <is>
+          <t>断/短/接地分别制造</t>
+        </is>
+      </c>
+      <c r="H642" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障；火警下显示不受影响</t>
+        </is>
+      </c>
+      <c r="I642" s="15" t="inlineStr"/>
+      <c r="J642" s="15" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
+      <c r="K642" s="15" t="inlineStr"/>
+      <c r="L642" s="15" t="inlineStr"/>
+      <c r="M642" s="15" t="inlineStr">
+        <is>
+          <t>待条件：需传输装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="15" t="n">
+        <v>642</v>
+      </c>
+      <c r="B643" s="15" t="inlineStr">
+        <is>
+          <t>FT-02.5</t>
+        </is>
+      </c>
+      <c r="C643" s="15" t="inlineStr">
+        <is>
+          <t>故障报警</t>
+        </is>
+      </c>
+      <c r="D643" s="15" t="inlineStr">
+        <is>
+          <t>无线设备通信故障</t>
+        </is>
+      </c>
+      <c r="E643" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F643" s="15" t="inlineStr">
+        <is>
+          <t>5.4.3.3 e)</t>
+        </is>
+      </c>
+      <c r="G643" s="15" t="inlineStr">
+        <is>
+          <t>使无线通信中断</t>
+        </is>
+      </c>
+      <c r="H643" s="15" t="inlineStr">
+        <is>
+          <t>≤100 s 报障；火警下显示不受影响</t>
+        </is>
+      </c>
+      <c r="I643" s="15" t="inlineStr"/>
+      <c r="J643" s="15" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="K643" s="15" t="inlineStr"/>
+      <c r="L643" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M643" s="15" t="inlineStr">
+        <is>
+          <t>条件适用条款：产品无无线设备</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M635"/>
+  <autoFilter ref="A1:M643"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J635" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
@@ -33991,7 +34415,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="3">
@@ -36422,23 +36846,23 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(测试执行表!C2:C635,A2)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A2)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A2,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A2,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A2,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A2,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A2,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A2,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G2">
@@ -36453,23 +36877,23 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(测试执行表!C2:C635,A3)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A3)</f>
         <v/>
       </c>
       <c r="C3">
-        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A3,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A3,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A3,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A3,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A3,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A3,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G3">
@@ -36484,23 +36908,23 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!C2:C635,A4)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A4)</f>
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A4,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A4,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A4,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F4">
-        <f>COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A4,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A4,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A4,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G4">
@@ -36515,23 +36939,23 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!C2:C635,A5)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A5)</f>
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A5,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A5,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A5,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F5">
-        <f>COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A5,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A5,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A5,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G5">
@@ -36546,23 +36970,23 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!C2:C635,A6)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A6)</f>
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A6,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A6,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A6,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A6,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A6,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A6,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G6">
@@ -36577,23 +37001,23 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(测试执行表!C2:C635,A7)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A7)</f>
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A7,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A7,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A7,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F7">
-        <f>COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A7,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A7,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A7,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G7">
@@ -36608,23 +37032,23 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(测试执行表!C2:C635,A8)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A8)</f>
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A8,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A8,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A8,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F8">
-        <f>COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A8,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A8,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A8,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G8">
@@ -36639,23 +37063,23 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(测试执行表!C2:C635,A9)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A9)</f>
         <v/>
       </c>
       <c r="C9">
-        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A9,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A9,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A9,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F9">
-        <f>COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A9,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A9,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A9,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G9">
@@ -36670,23 +37094,23 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIF(测试执行表!C2:C635,A10)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A10)</f>
         <v/>
       </c>
       <c r="C10">
-        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A10,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A10,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A10,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F10">
-        <f>COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A10,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A10,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A10,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G10">
@@ -36701,23 +37125,23 @@
         </is>
       </c>
       <c r="B11">
-        <f>COUNTIF(测试执行表!C2:C635,A11)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A11)</f>
         <v/>
       </c>
       <c r="C11">
-        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A11,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A11,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A11,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F11">
-        <f>COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A11,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A11,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A11,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G11">
@@ -36732,23 +37156,23 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTIF(测试执行表!C2:C635,A12)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A12)</f>
         <v/>
       </c>
       <c r="C12">
-        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A12,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A12,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A12,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A12,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A12,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A12,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G12">
@@ -36763,23 +37187,23 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTIF(测试执行表!C2:C635,A13)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A13)</f>
         <v/>
       </c>
       <c r="C13">
-        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A13,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A13,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A13,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F13">
-        <f>COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A13,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A13,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A13,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G13">
@@ -36794,23 +37218,23 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF(测试执行表!C2:C635,A14)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A14)</f>
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A14,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A14,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A14,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F14">
-        <f>COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A14,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A14,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A14,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G14">
@@ -36825,23 +37249,23 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF(测试执行表!C2:C635,A15)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A15)</f>
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A15,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A15,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A15,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F15">
-        <f>COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A15,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A15,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A15,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G15">
@@ -36856,23 +37280,23 @@
         </is>
       </c>
       <c r="B16">
-        <f>COUNTIF(测试执行表!C2:C635,A16)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A16)</f>
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A16,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A16,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A16,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F16">
-        <f>COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A16,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A16,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A16,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G16">
@@ -36887,23 +37311,23 @@
         </is>
       </c>
       <c r="B17">
-        <f>COUNTIF(测试执行表!C2:C635,A17)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A17)</f>
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A17,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A17,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A17,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F17">
-        <f>COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A17,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A17,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A17,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G17">
@@ -36918,23 +37342,23 @@
         </is>
       </c>
       <c r="B18">
-        <f>COUNTIF(测试执行表!C2:C635,A18)</f>
+        <f>COUNTIF(测试执行表!C2:C643,A18)</f>
         <v/>
       </c>
       <c r="C18">
-        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A18,测试执行表!J2:J643,"通过")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A18,测试执行表!J2:J643,"不通过")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A18,测试执行表!J2:J643,"不适用")</f>
         <v/>
       </c>
       <c r="F18">
-        <f>COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"待测")+COUNTIFS(测试执行表!C2:C635,A18,测试执行表!J2:J635,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C643,A18,测试执行表!J2:J643,"待测")+COUNTIFS(测试执行表!C2:C643,A18,测试执行表!J2:J643,"暂不测试")</f>
         <v/>
       </c>
       <c r="G18">
@@ -36953,7 +37377,7 @@
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>SUM(C2:C635)</f>
+        <f>SUM(C2:C643)</f>
         <v/>
       </c>
       <c r="D19" s="10">

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -7369,14 +7369,14 @@
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19 按条款项拆分为 .1～.5——原整案"通过"继承给 .1 断路；短路/接地/探头若当时已做，请把对应子行勾回通过</t>
+          <t>子项两层：.1～.4＝行为包（已测通过）；.5～.9＝五种故障制造手法——短路/接地/探头若整案时已做请勾回通过</t>
         </is>
       </c>
       <c r="N127" s="2" t="n"/>
@@ -8341,7 +8341,11 @@
         </is>
       </c>
       <c r="I146" s="3" t="n"/>
-      <c r="J146" s="2" t="n"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="n"/>
       <c r="M146" s="3" t="n"/>
@@ -8387,7 +8391,11 @@
         </is>
       </c>
       <c r="I147" s="3" t="n"/>
-      <c r="J147" s="2" t="n"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K147" s="2" t="n"/>
       <c r="L147" s="2" t="n"/>
       <c r="M147" s="3" t="n"/>
@@ -8433,7 +8441,11 @@
         </is>
       </c>
       <c r="I148" s="3" t="n"/>
-      <c r="J148" s="2" t="n"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K148" s="2" t="n"/>
       <c r="L148" s="2" t="n"/>
       <c r="M148" s="3" t="n"/>
@@ -8479,7 +8491,11 @@
         </is>
       </c>
       <c r="I149" s="3" t="n"/>
-      <c r="J149" s="2" t="n"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K149" s="2" t="n"/>
       <c r="L149" s="2" t="n"/>
       <c r="M149" s="3" t="n"/>
@@ -8923,7 +8939,11 @@
         </is>
       </c>
       <c r="I157" s="3" t="n"/>
-      <c r="J157" s="2" t="n"/>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K157" s="2" t="n"/>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="3" t="inlineStr">
@@ -8973,7 +8993,11 @@
         </is>
       </c>
       <c r="I158" s="3" t="n"/>
-      <c r="J158" s="2" t="n"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="n"/>
       <c r="L158" s="2" t="n"/>
       <c r="M158" s="3" t="n"/>
@@ -9019,7 +9043,11 @@
         </is>
       </c>
       <c r="I159" s="3" t="n"/>
-      <c r="J159" s="2" t="n"/>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K159" s="2" t="n"/>
       <c r="L159" s="2" t="n"/>
       <c r="M159" s="3" t="n"/>
@@ -9065,7 +9093,11 @@
         </is>
       </c>
       <c r="I160" s="3" t="n"/>
-      <c r="J160" s="2" t="n"/>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K160" s="2" t="n"/>
       <c r="L160" s="2" t="n"/>
       <c r="M160" s="3" t="n"/>
@@ -9111,7 +9143,11 @@
         </is>
       </c>
       <c r="I161" s="3" t="n"/>
-      <c r="J161" s="2" t="n"/>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K161" s="2" t="n"/>
       <c r="L161" s="2" t="n"/>
       <c r="M161" s="3" t="n"/>
@@ -9157,7 +9193,11 @@
         </is>
       </c>
       <c r="I162" s="3" t="n"/>
-      <c r="J162" s="2" t="n"/>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K162" s="2" t="n"/>
       <c r="L162" s="2" t="n"/>
       <c r="M162" s="3" t="n"/>
@@ -9199,7 +9239,11 @@
         </is>
       </c>
       <c r="I163" s="3" t="n"/>
-      <c r="J163" s="2" t="n"/>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K163" s="2" t="n"/>
       <c r="L163" s="2" t="n"/>
       <c r="M163" s="3" t="n"/>
@@ -9245,7 +9289,11 @@
         </is>
       </c>
       <c r="I164" s="3" t="n"/>
-      <c r="J164" s="2" t="n"/>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K164" s="2" t="n"/>
       <c r="L164" s="2" t="n"/>
       <c r="M164" s="3" t="n"/>
@@ -9291,7 +9339,11 @@
         </is>
       </c>
       <c r="I165" s="3" t="n"/>
-      <c r="J165" s="2" t="n"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K165" s="2" t="n"/>
       <c r="L165" s="2" t="n"/>
       <c r="M165" s="3" t="n"/>
@@ -9337,7 +9389,11 @@
         </is>
       </c>
       <c r="I166" s="3" t="n"/>
-      <c r="J166" s="2" t="n"/>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K166" s="2" t="n"/>
       <c r="L166" s="2" t="n"/>
       <c r="M166" s="3" t="n"/>
@@ -9383,7 +9439,11 @@
         </is>
       </c>
       <c r="I167" s="3" t="n"/>
-      <c r="J167" s="2" t="n"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
       <c r="M167" s="3" t="n"/>
@@ -9425,7 +9485,11 @@
         </is>
       </c>
       <c r="I168" s="3" t="n"/>
-      <c r="J168" s="2" t="n"/>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K168" s="2" t="n"/>
       <c r="L168" s="2" t="n"/>
       <c r="M168" s="3" t="n"/>
@@ -9475,7 +9539,11 @@
         </is>
       </c>
       <c r="I169" s="3" t="n"/>
-      <c r="J169" s="2" t="n"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="3" t="n"/>
@@ -9587,7 +9655,11 @@
         </is>
       </c>
       <c r="I171" s="3" t="n"/>
-      <c r="J171" s="2" t="n"/>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K171" s="2" t="n"/>
       <c r="L171" s="2" t="n"/>
       <c r="M171" s="3" t="n"/>
@@ -9637,7 +9709,11 @@
         </is>
       </c>
       <c r="I172" s="3" t="n"/>
-      <c r="J172" s="2" t="n"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K172" s="2" t="n"/>
       <c r="L172" s="2" t="n"/>
       <c r="M172" s="3" t="n"/>
@@ -9683,7 +9759,11 @@
         </is>
       </c>
       <c r="I173" s="3" t="n"/>
-      <c r="J173" s="2" t="n"/>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K173" s="2" t="n"/>
       <c r="L173" s="2" t="n"/>
       <c r="M173" s="3" t="n"/>
@@ -9733,7 +9813,11 @@
         </is>
       </c>
       <c r="I174" s="3" t="n"/>
-      <c r="J174" s="2" t="n"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
       <c r="M174" s="3" t="n"/>
@@ -9783,7 +9867,11 @@
         </is>
       </c>
       <c r="I175" s="3" t="n"/>
-      <c r="J175" s="2" t="n"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="n"/>
       <c r="L175" s="2" t="n"/>
       <c r="M175" s="3" t="n"/>
@@ -9833,7 +9921,11 @@
         </is>
       </c>
       <c r="I176" s="3" t="n"/>
-      <c r="J176" s="2" t="n"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
       <c r="M176" s="3" t="n"/>
@@ -9883,7 +9975,11 @@
         </is>
       </c>
       <c r="I177" s="3" t="n"/>
-      <c r="J177" s="2" t="n"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="2" t="n"/>
       <c r="M177" s="3" t="n"/>
@@ -9929,7 +10025,11 @@
         </is>
       </c>
       <c r="I178" s="3" t="n"/>
-      <c r="J178" s="2" t="n"/>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K178" s="2" t="n"/>
       <c r="L178" s="2" t="n"/>
       <c r="M178" s="3" t="n"/>
@@ -9979,7 +10079,11 @@
         </is>
       </c>
       <c r="I179" s="3" t="n"/>
-      <c r="J179" s="2" t="n"/>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K179" s="2" t="n"/>
       <c r="L179" s="2" t="n"/>
       <c r="M179" s="3" t="n"/>
@@ -10029,7 +10133,11 @@
         </is>
       </c>
       <c r="I180" s="3" t="n"/>
-      <c r="J180" s="2" t="n"/>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K180" s="2" t="n"/>
       <c r="L180" s="2" t="n"/>
       <c r="M180" s="3" t="n"/>
@@ -10075,7 +10183,11 @@
         </is>
       </c>
       <c r="I181" s="3" t="n"/>
-      <c r="J181" s="2" t="n"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
       <c r="M181" s="3" t="n"/>
@@ -10125,7 +10237,11 @@
         </is>
       </c>
       <c r="I182" s="3" t="n"/>
-      <c r="J182" s="2" t="n"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="3" t="n"/>
@@ -10175,7 +10291,11 @@
         </is>
       </c>
       <c r="I183" s="3" t="n"/>
-      <c r="J183" s="2" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="2" t="n"/>
       <c r="M183" s="3" t="n"/>
@@ -10221,7 +10341,11 @@
         </is>
       </c>
       <c r="I184" s="3" t="n"/>
-      <c r="J184" s="2" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
       <c r="M184" s="3" t="inlineStr">
@@ -10337,7 +10461,11 @@
         </is>
       </c>
       <c r="I186" s="3" t="n"/>
-      <c r="J186" s="2" t="n"/>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K186" s="2" t="n"/>
       <c r="L186" s="2" t="n"/>
       <c r="M186" s="3" t="n"/>
@@ -11027,7 +11155,11 @@
         </is>
       </c>
       <c r="I201" s="3" t="n"/>
-      <c r="J201" s="2" t="n"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K201" s="2" t="n"/>
       <c r="L201" s="2" t="n"/>
       <c r="M201" s="3" t="n"/>
@@ -11073,7 +11205,11 @@
         </is>
       </c>
       <c r="I202" s="3" t="n"/>
-      <c r="J202" s="2" t="n"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="3" t="n"/>
@@ -11177,10 +11313,22 @@
         </is>
       </c>
       <c r="I204" s="3" t="n"/>
-      <c r="J204" s="2" t="n"/>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K204" s="2" t="n"/>
-      <c r="L204" s="2" t="n"/>
-      <c r="M204" s="3" t="n"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>条件适用判定树：①菜单无分部位自检→全系不适用；②有功能且有自检总灯→照测；③有功能但无灯（面板11灯无自检位）→不通过。先查菜单再定</t>
+        </is>
+      </c>
       <c r="N204" s="2" t="n"/>
     </row>
     <row r="205">
@@ -33958,7 +34106,7 @@
       </c>
       <c r="B636" s="15" t="inlineStr">
         <is>
-          <t>FT-01.1</t>
+          <t>FT-01.5</t>
         </is>
       </c>
       <c r="C636" s="15" t="inlineStr">
@@ -34015,7 +34163,7 @@
       </c>
       <c r="B637" s="15" t="inlineStr">
         <is>
-          <t>FT-01.2</t>
+          <t>FT-01.6</t>
         </is>
       </c>
       <c r="C637" s="15" t="inlineStr">
@@ -34064,7 +34212,7 @@
       </c>
       <c r="B638" s="15" t="inlineStr">
         <is>
-          <t>FT-01.3</t>
+          <t>FT-01.7</t>
         </is>
       </c>
       <c r="C638" s="15" t="inlineStr">
@@ -34113,7 +34261,7 @@
       </c>
       <c r="B639" s="15" t="inlineStr">
         <is>
-          <t>FT-01.4</t>
+          <t>FT-01.8</t>
         </is>
       </c>
       <c r="C639" s="15" t="inlineStr">
@@ -34162,7 +34310,7 @@
       </c>
       <c r="B640" s="15" t="inlineStr">
         <is>
-          <t>FT-01.5</t>
+          <t>FT-01.9</t>
         </is>
       </c>
       <c r="C640" s="15" t="inlineStr">

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -8299,7 +8299,11 @@
         </is>
       </c>
       <c r="I145" s="3" t="n"/>
-      <c r="J145" s="2" t="n"/>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="n"/>
       <c r="M145" s="3" t="n"/>
@@ -10511,7 +10515,11 @@
         </is>
       </c>
       <c r="I187" s="3" t="n"/>
-      <c r="J187" s="2" t="n"/>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K187" s="2" t="n"/>
       <c r="L187" s="2" t="n"/>
       <c r="M187" s="3" t="inlineStr">
@@ -10561,7 +10569,11 @@
         </is>
       </c>
       <c r="I188" s="3" t="n"/>
-      <c r="J188" s="2" t="n"/>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K188" s="2" t="n"/>
       <c r="L188" s="2" t="n"/>
       <c r="M188" s="3" t="n"/>
@@ -10607,7 +10619,11 @@
         </is>
       </c>
       <c r="I189" s="3" t="n"/>
-      <c r="J189" s="2" t="n"/>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K189" s="2" t="n"/>
       <c r="L189" s="2" t="n"/>
       <c r="M189" s="3" t="n"/>
@@ -10653,7 +10669,11 @@
         </is>
       </c>
       <c r="I190" s="3" t="n"/>
-      <c r="J190" s="2" t="n"/>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K190" s="2" t="n"/>
       <c r="L190" s="2" t="n"/>
       <c r="M190" s="3" t="n"/>
@@ -10699,7 +10719,11 @@
         </is>
       </c>
       <c r="I191" s="3" t="n"/>
-      <c r="J191" s="2" t="n"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K191" s="2" t="n"/>
       <c r="L191" s="2" t="n"/>
       <c r="M191" s="3" t="n"/>
@@ -10745,7 +10769,11 @@
         </is>
       </c>
       <c r="I192" s="3" t="n"/>
-      <c r="J192" s="2" t="n"/>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K192" s="2" t="n"/>
       <c r="L192" s="2" t="n"/>
       <c r="M192" s="3" t="n"/>
@@ -10791,7 +10819,11 @@
         </is>
       </c>
       <c r="I193" s="3" t="n"/>
-      <c r="J193" s="2" t="n"/>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K193" s="2" t="n"/>
       <c r="L193" s="2" t="n"/>
       <c r="M193" s="3" t="n"/>
@@ -10833,7 +10865,11 @@
         </is>
       </c>
       <c r="I194" s="3" t="n"/>
-      <c r="J194" s="2" t="n"/>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K194" s="2" t="n"/>
       <c r="L194" s="2" t="n"/>
       <c r="M194" s="3" t="n"/>
@@ -10879,7 +10915,11 @@
         </is>
       </c>
       <c r="I195" s="3" t="n"/>
-      <c r="J195" s="2" t="n"/>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K195" s="2" t="n"/>
       <c r="L195" s="2" t="n"/>
       <c r="M195" s="3" t="n"/>
@@ -10925,7 +10965,11 @@
         </is>
       </c>
       <c r="I196" s="3" t="n"/>
-      <c r="J196" s="2" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K196" s="2" t="n"/>
       <c r="L196" s="2" t="n"/>
       <c r="M196" s="3" t="n"/>
@@ -10971,7 +11015,11 @@
         </is>
       </c>
       <c r="I197" s="3" t="n"/>
-      <c r="J197" s="2" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="2" t="n"/>
       <c r="M197" s="3" t="n"/>
@@ -11017,7 +11065,11 @@
         </is>
       </c>
       <c r="I198" s="3" t="n"/>
-      <c r="J198" s="2" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K198" s="2" t="n"/>
       <c r="L198" s="2" t="n"/>
       <c r="M198" s="3" t="n"/>
@@ -11063,7 +11115,11 @@
         </is>
       </c>
       <c r="I199" s="3" t="n"/>
-      <c r="J199" s="2" t="n"/>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K199" s="2" t="n"/>
       <c r="L199" s="2" t="n"/>
       <c r="M199" s="3" t="n"/>
@@ -11109,7 +11165,11 @@
         </is>
       </c>
       <c r="I200" s="3" t="n"/>
-      <c r="J200" s="2" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="2" t="n"/>
       <c r="M200" s="3" t="n"/>
@@ -11371,7 +11431,11 @@
         </is>
       </c>
       <c r="I205" s="3" t="n"/>
-      <c r="J205" s="2" t="n"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="n"/>
       <c r="M205" s="3" t="n"/>
@@ -11417,7 +11481,11 @@
         </is>
       </c>
       <c r="I206" s="3" t="n"/>
-      <c r="J206" s="2" t="n"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
       <c r="M206" s="3" t="n"/>
@@ -11463,7 +11531,11 @@
         </is>
       </c>
       <c r="I207" s="3" t="n"/>
-      <c r="J207" s="2" t="n"/>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="n"/>
       <c r="M207" s="3" t="n"/>
@@ -11509,7 +11581,11 @@
         </is>
       </c>
       <c r="I208" s="3" t="n"/>
-      <c r="J208" s="2" t="n"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="n"/>
       <c r="M208" s="3" t="n"/>
@@ -11551,7 +11627,11 @@
         </is>
       </c>
       <c r="I209" s="3" t="n"/>
-      <c r="J209" s="2" t="n"/>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="n"/>
       <c r="M209" s="3" t="inlineStr">
@@ -11601,7 +11681,11 @@
         </is>
       </c>
       <c r="I210" s="3" t="n"/>
-      <c r="J210" s="2" t="n"/>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K210" s="2" t="n"/>
       <c r="L210" s="2" t="n"/>
       <c r="M210" s="3" t="n"/>
@@ -11647,7 +11731,11 @@
         </is>
       </c>
       <c r="I211" s="3" t="n"/>
-      <c r="J211" s="2" t="n"/>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K211" s="2" t="n"/>
       <c r="L211" s="2" t="n"/>
       <c r="M211" s="3" t="n"/>
@@ -11693,7 +11781,11 @@
         </is>
       </c>
       <c r="I212" s="3" t="n"/>
-      <c r="J212" s="2" t="n"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
       <c r="M212" s="3" t="n"/>
@@ -11739,7 +11831,11 @@
         </is>
       </c>
       <c r="I213" s="3" t="n"/>
-      <c r="J213" s="2" t="n"/>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
       <c r="M213" s="3" t="n"/>
@@ -11785,7 +11881,11 @@
         </is>
       </c>
       <c r="I214" s="3" t="n"/>
-      <c r="J214" s="2" t="n"/>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K214" s="2" t="n"/>
       <c r="L214" s="2" t="n"/>
       <c r="M214" s="3" t="n"/>
@@ -11827,7 +11927,11 @@
         </is>
       </c>
       <c r="I215" s="3" t="n"/>
-      <c r="J215" s="2" t="n"/>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K215" s="2" t="n"/>
       <c r="L215" s="2" t="n"/>
       <c r="M215" s="3" t="n"/>
@@ -11873,7 +11977,11 @@
         </is>
       </c>
       <c r="I216" s="3" t="n"/>
-      <c r="J216" s="2" t="n"/>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K216" s="2" t="n"/>
       <c r="L216" s="2" t="n"/>
       <c r="M216" s="3" t="n"/>
@@ -11919,7 +12027,11 @@
         </is>
       </c>
       <c r="I217" s="3" t="n"/>
-      <c r="J217" s="2" t="n"/>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K217" s="2" t="n"/>
       <c r="L217" s="2" t="n"/>
       <c r="M217" s="3" t="n"/>
@@ -11965,7 +12077,11 @@
         </is>
       </c>
       <c r="I218" s="3" t="n"/>
-      <c r="J218" s="2" t="n"/>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K218" s="2" t="n"/>
       <c r="L218" s="2" t="n"/>
       <c r="M218" s="3" t="n"/>
@@ -12383,7 +12499,11 @@
         </is>
       </c>
       <c r="I225" s="3" t="n"/>
-      <c r="J225" s="2" t="n"/>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K225" s="2" t="n"/>
       <c r="L225" s="2" t="n"/>
       <c r="M225" s="3" t="n"/>
@@ -12429,7 +12549,11 @@
         </is>
       </c>
       <c r="I226" s="3" t="n"/>
-      <c r="J226" s="2" t="n"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K226" s="2" t="n"/>
       <c r="L226" s="2" t="n"/>
       <c r="M226" s="3" t="n"/>
@@ -12479,7 +12603,11 @@
         </is>
       </c>
       <c r="I227" s="3" t="n"/>
-      <c r="J227" s="2" t="n"/>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="n"/>
       <c r="M227" s="3" t="n"/>
@@ -12528,8 +12656,16 @@
           <t>② 1 min 不操作→退出检查状态并熄灭指示灯</t>
         </is>
       </c>
-      <c r="I228" s="3" t="n"/>
-      <c r="J228" s="2" t="n"/>
+      <c r="I228" s="3" t="inlineStr">
+        <is>
+          <t>超过了 1 min</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="n"/>
       <c r="M228" s="3" t="n"/>
@@ -12579,7 +12715,11 @@
         </is>
       </c>
       <c r="I229" s="3" t="n"/>
-      <c r="J229" s="2" t="n"/>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K229" s="2" t="n"/>
       <c r="L229" s="2" t="n"/>
       <c r="M229" s="3" t="n"/>
@@ -13167,7 +13307,11 @@
         </is>
       </c>
       <c r="I239" s="3" t="n"/>
-      <c r="J239" s="2" t="n"/>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="n"/>
       <c r="M239" s="3" t="n"/>
@@ -13351,7 +13495,11 @@
         </is>
       </c>
       <c r="I243" s="3" t="n"/>
-      <c r="J243" s="2" t="n"/>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K243" s="2" t="n"/>
       <c r="L243" s="2" t="n"/>
       <c r="M243" s="3" t="n"/>
@@ -14759,7 +14907,11 @@
         </is>
       </c>
       <c r="I271" s="3" t="n"/>
-      <c r="J271" s="2" t="n"/>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="2" t="n"/>
       <c r="M271" s="3" t="n"/>
@@ -14805,7 +14957,11 @@
         </is>
       </c>
       <c r="I272" s="3" t="n"/>
-      <c r="J272" s="2" t="n"/>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="K272" s="2" t="n"/>
       <c r="L272" s="2" t="n"/>
       <c r="M272" s="3" t="n"/>
@@ -24063,7 +24219,11 @@
         </is>
       </c>
       <c r="I443" s="3" t="n"/>
-      <c r="J443" s="2" t="n"/>
+      <c r="J443" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K443" s="2" t="n"/>
       <c r="L443" s="2" t="n"/>
       <c r="M443" s="3" t="n"/>
@@ -25293,7 +25453,11 @@
         </is>
       </c>
       <c r="I468" s="3" t="n"/>
-      <c r="J468" s="2" t="n"/>
+      <c r="J468" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K468" s="2" t="n"/>
       <c r="L468" s="2" t="n"/>
       <c r="M468" s="3" t="n"/>
@@ -26381,7 +26545,11 @@
         </is>
       </c>
       <c r="I490" s="3" t="n"/>
-      <c r="J490" s="2" t="n"/>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K490" s="2" t="n"/>
       <c r="L490" s="2" t="n"/>
       <c r="M490" s="3" t="n"/>
@@ -26427,7 +26595,11 @@
         </is>
       </c>
       <c r="I491" s="3" t="n"/>
-      <c r="J491" s="2" t="n"/>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K491" s="2" t="n"/>
       <c r="L491" s="2" t="n"/>
       <c r="M491" s="3" t="n"/>
@@ -26473,7 +26645,11 @@
         </is>
       </c>
       <c r="I492" s="3" t="n"/>
-      <c r="J492" s="2" t="n"/>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K492" s="2" t="n"/>
       <c r="L492" s="2" t="n"/>
       <c r="M492" s="3" t="n"/>
@@ -26519,7 +26695,11 @@
         </is>
       </c>
       <c r="I493" s="3" t="n"/>
-      <c r="J493" s="2" t="n"/>
+      <c r="J493" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K493" s="2" t="n"/>
       <c r="L493" s="2" t="n"/>
       <c r="M493" s="3" t="n"/>
@@ -26565,7 +26745,11 @@
         </is>
       </c>
       <c r="I494" s="3" t="n"/>
-      <c r="J494" s="2" t="n"/>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K494" s="2" t="n"/>
       <c r="L494" s="2" t="n"/>
       <c r="M494" s="3" t="n"/>
@@ -26607,7 +26791,11 @@
         </is>
       </c>
       <c r="I495" s="3" t="n"/>
-      <c r="J495" s="2" t="n"/>
+      <c r="J495" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K495" s="2" t="n"/>
       <c r="L495" s="2" t="n"/>
       <c r="M495" s="3" t="n"/>
@@ -26653,7 +26841,11 @@
         </is>
       </c>
       <c r="I496" s="3" t="n"/>
-      <c r="J496" s="2" t="n"/>
+      <c r="J496" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K496" s="2" t="n"/>
       <c r="L496" s="2" t="n"/>
       <c r="M496" s="3" t="n"/>
@@ -26699,7 +26891,11 @@
         </is>
       </c>
       <c r="I497" s="3" t="n"/>
-      <c r="J497" s="2" t="n"/>
+      <c r="J497" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K497" s="2" t="n"/>
       <c r="L497" s="2" t="n"/>
       <c r="M497" s="3" t="n"/>
@@ -26741,7 +26937,11 @@
         </is>
       </c>
       <c r="I498" s="3" t="n"/>
-      <c r="J498" s="2" t="n"/>
+      <c r="J498" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K498" s="2" t="n"/>
       <c r="L498" s="2" t="n"/>
       <c r="M498" s="3" t="n"/>
@@ -26787,7 +26987,11 @@
         </is>
       </c>
       <c r="I499" s="3" t="n"/>
-      <c r="J499" s="2" t="n"/>
+      <c r="J499" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K499" s="2" t="n"/>
       <c r="L499" s="2" t="n"/>
       <c r="M499" s="3" t="n"/>
@@ -26833,7 +27037,11 @@
         </is>
       </c>
       <c r="I500" s="3" t="n"/>
-      <c r="J500" s="2" t="n"/>
+      <c r="J500" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K500" s="2" t="n"/>
       <c r="L500" s="2" t="n"/>
       <c r="M500" s="3" t="n"/>
@@ -26879,7 +27087,11 @@
         </is>
       </c>
       <c r="I501" s="3" t="n"/>
-      <c r="J501" s="2" t="n"/>
+      <c r="J501" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K501" s="2" t="n"/>
       <c r="L501" s="2" t="n"/>
       <c r="M501" s="3" t="n"/>
@@ -26921,7 +27133,11 @@
         </is>
       </c>
       <c r="I502" s="3" t="n"/>
-      <c r="J502" s="2" t="n"/>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K502" s="2" t="n"/>
       <c r="L502" s="2" t="n"/>
       <c r="M502" s="3" t="n"/>
@@ -26967,7 +27183,11 @@
         </is>
       </c>
       <c r="I503" s="3" t="n"/>
-      <c r="J503" s="2" t="n"/>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K503" s="2" t="n"/>
       <c r="L503" s="2" t="n"/>
       <c r="M503" s="3" t="n"/>
@@ -27013,7 +27233,11 @@
         </is>
       </c>
       <c r="I504" s="3" t="n"/>
-      <c r="J504" s="2" t="n"/>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K504" s="2" t="n"/>
       <c r="L504" s="2" t="n"/>
       <c r="M504" s="3" t="n"/>
@@ -27059,7 +27283,11 @@
         </is>
       </c>
       <c r="I505" s="3" t="n"/>
-      <c r="J505" s="2" t="n"/>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K505" s="2" t="n"/>
       <c r="L505" s="2" t="n"/>
       <c r="M505" s="3" t="n"/>
@@ -27105,7 +27333,11 @@
         </is>
       </c>
       <c r="I506" s="3" t="n"/>
-      <c r="J506" s="2" t="n"/>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K506" s="2" t="n"/>
       <c r="L506" s="2" t="n"/>
       <c r="M506" s="3" t="n"/>
@@ -27151,7 +27383,11 @@
         </is>
       </c>
       <c r="I507" s="3" t="n"/>
-      <c r="J507" s="2" t="n"/>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K507" s="2" t="n"/>
       <c r="L507" s="2" t="n"/>
       <c r="M507" s="3" t="n"/>
@@ -27255,7 +27491,11 @@
         </is>
       </c>
       <c r="I509" s="3" t="n"/>
-      <c r="J509" s="2" t="n"/>
+      <c r="J509" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K509" s="2" t="n"/>
       <c r="L509" s="2" t="n"/>
       <c r="M509" s="3" t="n"/>
@@ -27301,7 +27541,11 @@
         </is>
       </c>
       <c r="I510" s="3" t="n"/>
-      <c r="J510" s="2" t="n"/>
+      <c r="J510" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K510" s="2" t="n"/>
       <c r="L510" s="2" t="n"/>
       <c r="M510" s="3" t="n"/>
@@ -27343,7 +27587,11 @@
         </is>
       </c>
       <c r="I511" s="3" t="n"/>
-      <c r="J511" s="2" t="n"/>
+      <c r="J511" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K511" s="2" t="n"/>
       <c r="L511" s="2" t="n"/>
       <c r="M511" s="3" t="n"/>
@@ -27389,7 +27637,11 @@
         </is>
       </c>
       <c r="I512" s="3" t="n"/>
-      <c r="J512" s="2" t="n"/>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K512" s="2" t="n"/>
       <c r="L512" s="2" t="n"/>
       <c r="M512" s="3" t="n"/>
@@ -27435,7 +27687,11 @@
         </is>
       </c>
       <c r="I513" s="3" t="n"/>
-      <c r="J513" s="2" t="n"/>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K513" s="2" t="n"/>
       <c r="L513" s="2" t="n"/>
       <c r="M513" s="3" t="n"/>
@@ -27481,7 +27737,11 @@
         </is>
       </c>
       <c r="I514" s="3" t="n"/>
-      <c r="J514" s="2" t="n"/>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K514" s="2" t="n"/>
       <c r="L514" s="2" t="n"/>
       <c r="M514" s="3" t="n"/>
@@ -27523,7 +27783,11 @@
         </is>
       </c>
       <c r="I515" s="3" t="n"/>
-      <c r="J515" s="2" t="n"/>
+      <c r="J515" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K515" s="2" t="n"/>
       <c r="L515" s="2" t="n"/>
       <c r="M515" s="3" t="n"/>
@@ -27569,7 +27833,11 @@
         </is>
       </c>
       <c r="I516" s="3" t="n"/>
-      <c r="J516" s="2" t="n"/>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K516" s="2" t="n"/>
       <c r="L516" s="2" t="n"/>
       <c r="M516" s="3" t="n"/>
@@ -27615,7 +27883,11 @@
         </is>
       </c>
       <c r="I517" s="3" t="n"/>
-      <c r="J517" s="2" t="n"/>
+      <c r="J517" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K517" s="2" t="n"/>
       <c r="L517" s="2" t="n"/>
       <c r="M517" s="3" t="n"/>
@@ -27661,7 +27933,11 @@
         </is>
       </c>
       <c r="I518" s="3" t="n"/>
-      <c r="J518" s="2" t="n"/>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K518" s="2" t="n"/>
       <c r="L518" s="2" t="n"/>
       <c r="M518" s="3" t="n"/>
@@ -27707,7 +27983,11 @@
         </is>
       </c>
       <c r="I519" s="3" t="n"/>
-      <c r="J519" s="2" t="n"/>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K519" s="2" t="n"/>
       <c r="L519" s="2" t="n"/>
       <c r="M519" s="3" t="n"/>
@@ -27749,7 +28029,11 @@
         </is>
       </c>
       <c r="I520" s="3" t="n"/>
-      <c r="J520" s="2" t="n"/>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K520" s="2" t="n"/>
       <c r="L520" s="2" t="n"/>
       <c r="M520" s="3" t="n"/>
@@ -27795,7 +28079,11 @@
         </is>
       </c>
       <c r="I521" s="3" t="n"/>
-      <c r="J521" s="2" t="n"/>
+      <c r="J521" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K521" s="2" t="n"/>
       <c r="L521" s="2" t="n"/>
       <c r="M521" s="3" t="n"/>
@@ -27841,7 +28129,11 @@
         </is>
       </c>
       <c r="I522" s="3" t="n"/>
-      <c r="J522" s="2" t="n"/>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K522" s="2" t="n"/>
       <c r="L522" s="2" t="n"/>
       <c r="M522" s="3" t="n"/>
@@ -27887,7 +28179,11 @@
         </is>
       </c>
       <c r="I523" s="3" t="n"/>
-      <c r="J523" s="2" t="n"/>
+      <c r="J523" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K523" s="2" t="n"/>
       <c r="L523" s="2" t="n"/>
       <c r="M523" s="3" t="n"/>
@@ -27933,7 +28229,11 @@
         </is>
       </c>
       <c r="I524" s="3" t="n"/>
-      <c r="J524" s="2" t="n"/>
+      <c r="J524" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K524" s="2" t="n"/>
       <c r="L524" s="2" t="n"/>
       <c r="M524" s="3" t="n"/>
@@ -27975,7 +28275,11 @@
         </is>
       </c>
       <c r="I525" s="3" t="n"/>
-      <c r="J525" s="2" t="n"/>
+      <c r="J525" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K525" s="2" t="n"/>
       <c r="L525" s="2" t="n"/>
       <c r="M525" s="3" t="n"/>
@@ -28021,7 +28325,11 @@
         </is>
       </c>
       <c r="I526" s="3" t="n"/>
-      <c r="J526" s="2" t="n"/>
+      <c r="J526" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K526" s="2" t="n"/>
       <c r="L526" s="2" t="n"/>
       <c r="M526" s="3" t="n"/>
@@ -28067,7 +28375,11 @@
         </is>
       </c>
       <c r="I527" s="3" t="n"/>
-      <c r="J527" s="2" t="n"/>
+      <c r="J527" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K527" s="2" t="n"/>
       <c r="L527" s="2" t="n"/>
       <c r="M527" s="3" t="n"/>
@@ -28109,7 +28421,11 @@
         </is>
       </c>
       <c r="I528" s="3" t="n"/>
-      <c r="J528" s="2" t="n"/>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K528" s="2" t="n"/>
       <c r="L528" s="2" t="n"/>
       <c r="M528" s="3" t="n"/>
@@ -28155,7 +28471,11 @@
         </is>
       </c>
       <c r="I529" s="3" t="n"/>
-      <c r="J529" s="2" t="n"/>
+      <c r="J529" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K529" s="2" t="n"/>
       <c r="L529" s="2" t="n"/>
       <c r="M529" s="3" t="n"/>
@@ -28201,7 +28521,11 @@
         </is>
       </c>
       <c r="I530" s="3" t="n"/>
-      <c r="J530" s="2" t="n"/>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K530" s="2" t="n"/>
       <c r="L530" s="2" t="n"/>
       <c r="M530" s="3" t="n"/>
@@ -28247,7 +28571,11 @@
         </is>
       </c>
       <c r="I531" s="3" t="n"/>
-      <c r="J531" s="2" t="n"/>
+      <c r="J531" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K531" s="2" t="n"/>
       <c r="L531" s="2" t="n"/>
       <c r="M531" s="3" t="n"/>
@@ -28293,7 +28621,11 @@
         </is>
       </c>
       <c r="I532" s="3" t="n"/>
-      <c r="J532" s="2" t="n"/>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K532" s="2" t="n"/>
       <c r="L532" s="2" t="n"/>
       <c r="M532" s="3" t="n"/>
@@ -28335,7 +28667,11 @@
         </is>
       </c>
       <c r="I533" s="3" t="n"/>
-      <c r="J533" s="2" t="n"/>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K533" s="2" t="n"/>
       <c r="L533" s="2" t="n"/>
       <c r="M533" s="3" t="n"/>
@@ -28381,7 +28717,11 @@
         </is>
       </c>
       <c r="I534" s="3" t="n"/>
-      <c r="J534" s="2" t="n"/>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K534" s="2" t="n"/>
       <c r="L534" s="2" t="n"/>
       <c r="M534" s="3" t="n"/>
@@ -28427,7 +28767,11 @@
         </is>
       </c>
       <c r="I535" s="3" t="n"/>
-      <c r="J535" s="2" t="n"/>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K535" s="2" t="n"/>
       <c r="L535" s="2" t="n"/>
       <c r="M535" s="3" t="n"/>
@@ -28755,7 +29099,11 @@
         </is>
       </c>
       <c r="I541" s="3" t="n"/>
-      <c r="J541" s="2" t="n"/>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K541" s="2" t="n"/>
       <c r="L541" s="2" t="n"/>
       <c r="M541" s="3" t="n"/>
@@ -28801,7 +29149,11 @@
         </is>
       </c>
       <c r="I542" s="3" t="n"/>
-      <c r="J542" s="2" t="n"/>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K542" s="2" t="n"/>
       <c r="L542" s="2" t="n"/>
       <c r="M542" s="3" t="n"/>
@@ -28847,7 +29199,11 @@
         </is>
       </c>
       <c r="I543" s="3" t="n"/>
-      <c r="J543" s="2" t="n"/>
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K543" s="2" t="n"/>
       <c r="L543" s="2" t="n"/>
       <c r="M543" s="3" t="n"/>
@@ -28889,7 +29245,11 @@
         </is>
       </c>
       <c r="I544" s="3" t="n"/>
-      <c r="J544" s="2" t="n"/>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K544" s="2" t="n"/>
       <c r="L544" s="2" t="n"/>
       <c r="M544" s="3" t="n"/>
@@ -28935,7 +29295,11 @@
         </is>
       </c>
       <c r="I545" s="3" t="n"/>
-      <c r="J545" s="2" t="n"/>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K545" s="2" t="n"/>
       <c r="L545" s="2" t="n"/>
       <c r="M545" s="3" t="n"/>
@@ -28981,7 +29345,11 @@
         </is>
       </c>
       <c r="I546" s="3" t="n"/>
-      <c r="J546" s="2" t="n"/>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K546" s="2" t="n"/>
       <c r="L546" s="2" t="n"/>
       <c r="M546" s="3" t="n"/>
@@ -29027,7 +29395,11 @@
         </is>
       </c>
       <c r="I547" s="3" t="n"/>
-      <c r="J547" s="2" t="n"/>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K547" s="2" t="n"/>
       <c r="L547" s="2" t="n"/>
       <c r="M547" s="3" t="n"/>
@@ -29069,7 +29441,11 @@
         </is>
       </c>
       <c r="I548" s="3" t="n"/>
-      <c r="J548" s="2" t="n"/>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K548" s="2" t="n"/>
       <c r="L548" s="2" t="n"/>
       <c r="M548" s="3" t="n"/>
@@ -29115,7 +29491,11 @@
         </is>
       </c>
       <c r="I549" s="3" t="n"/>
-      <c r="J549" s="2" t="n"/>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K549" s="2" t="n"/>
       <c r="L549" s="2" t="n"/>
       <c r="M549" s="3" t="n"/>
@@ -29161,7 +29541,11 @@
         </is>
       </c>
       <c r="I550" s="3" t="n"/>
-      <c r="J550" s="2" t="n"/>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K550" s="2" t="n"/>
       <c r="L550" s="2" t="n"/>
       <c r="M550" s="3" t="n"/>
@@ -29207,7 +29591,11 @@
         </is>
       </c>
       <c r="I551" s="3" t="n"/>
-      <c r="J551" s="2" t="n"/>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K551" s="2" t="n"/>
       <c r="L551" s="2" t="n"/>
       <c r="M551" s="3" t="n"/>
@@ -29249,7 +29637,11 @@
         </is>
       </c>
       <c r="I552" s="3" t="n"/>
-      <c r="J552" s="2" t="n"/>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K552" s="2" t="n"/>
       <c r="L552" s="2" t="n"/>
       <c r="M552" s="3" t="n"/>
@@ -29295,7 +29687,11 @@
         </is>
       </c>
       <c r="I553" s="3" t="n"/>
-      <c r="J553" s="2" t="n"/>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K553" s="2" t="n"/>
       <c r="L553" s="2" t="n"/>
       <c r="M553" s="3" t="n"/>
@@ -29341,7 +29737,11 @@
         </is>
       </c>
       <c r="I554" s="3" t="n"/>
-      <c r="J554" s="2" t="n"/>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K554" s="2" t="n"/>
       <c r="L554" s="2" t="n"/>
       <c r="M554" s="3" t="n"/>
@@ -29387,7 +29787,11 @@
         </is>
       </c>
       <c r="I555" s="3" t="n"/>
-      <c r="J555" s="2" t="n"/>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K555" s="2" t="n"/>
       <c r="L555" s="2" t="n"/>
       <c r="M555" s="3" t="n"/>
@@ -29429,7 +29833,11 @@
         </is>
       </c>
       <c r="I556" s="3" t="n"/>
-      <c r="J556" s="2" t="n"/>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>待测</t>
+        </is>
+      </c>
       <c r="K556" s="2" t="n"/>
       <c r="L556" s="2" t="n"/>
       <c r="M556" s="3" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -11483,7 +11483,7 @@
       <c r="I206" s="3" t="n"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K206" s="2" t="n"/>
@@ -11583,7 +11583,7 @@
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K208" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -24197,7 +24197,7 @@
       </c>
       <c r="J435" s="7" t="inlineStr">
         <is>
-          <t>不通过</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="K435" s="2" t="n"/>
@@ -24405,7 +24405,7 @@
       <c r="I439" s="3" t="n"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K439" s="2" t="n"/>
@@ -24555,7 +24555,7 @@
       <c r="I442" s="3" t="n"/>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K442" s="2" t="n"/>
@@ -24605,7 +24605,7 @@
       <c r="I443" s="3" t="n"/>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K443" s="2" t="n"/>
@@ -24655,7 +24655,7 @@
       <c r="I444" s="3" t="n"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K444" s="2" t="n"/>
@@ -24755,7 +24755,7 @@
       <c r="I446" s="3" t="n"/>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K446" s="2" t="n"/>
@@ -25005,7 +25005,7 @@
       <c r="I451" s="3" t="n"/>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>不通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K451" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>5.4.2.2</t>
+          <t>5.4.1.13</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>5.4.2.2</t>
+          <t>5.4.3.1/5.4.5.1</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>5.4.2.2</t>
+          <t>5.4.10.2（推导）</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>5.4.2.2</t>
+          <t>5.4.2.9（推导）</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -14,7 +14,7 @@
     <sheet name="分组统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$603</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$604</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N603"/>
+  <dimension ref="A1:N604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K145" s="2" t="n"/>
@@ -33106,8 +33106,69 @@
         </is>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" s="15" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" s="15" t="inlineStr">
+        <is>
+          <t>GE-22</t>
+        </is>
+      </c>
+      <c r="C604" s="15" t="inlineStr">
+        <is>
+          <t>气体灭火控制器</t>
+        </is>
+      </c>
+      <c r="D604" s="15" t="inlineStr">
+        <is>
+          <t>强启路径·放气勿入指示牌</t>
+        </is>
+      </c>
+      <c r="E604" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F604" s="15" t="inlineStr">
+        <is>
+          <t>GB16806 4.3.2.2 d)/e)</t>
+        </is>
+      </c>
+      <c r="G604" s="15" t="inlineStr">
+        <is>
+          <t>强启（紧急启动，跳过延时）→ 启动喷洒；启动及反馈信号有效期间观察现场『放气勿入』指示牌</t>
+        </is>
+      </c>
+      <c r="H604" s="15" t="inlineStr">
+        <is>
+          <t>喷洒控制信号发出后『放气勿入』指示牌（喷洒光警报器）应点亮，保持至复位</t>
+        </is>
+      </c>
+      <c r="I604" s="15" t="inlineStr">
+        <is>
+          <t>强启后启动/反馈信号有效时，放气勿入指示牌未亮</t>
+        </is>
+      </c>
+      <c r="J604" s="15" t="inlineStr">
+        <is>
+          <t>不通过</t>
+        </is>
+      </c>
+      <c r="K604" s="15" t="inlineStr"/>
+      <c r="L604" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="M604" s="15" t="inlineStr">
+        <is>
+          <t>现场实测补充用例；气体灭火控制器模块</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M603"/>
+  <autoFilter ref="A1:M604"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J635" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
@@ -33149,7 +33210,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3">
@@ -34340,7 +34401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35516,6 +35577,38 @@
       <c r="F41" s="15" t="inlineStr">
         <is>
           <t>UI-11.5 消音灯常亮·不自动复位</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>GE-22</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>气灭/现场警示</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>强启后放气勿入指示牌未亮</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>启动/反馈信号有效时指示牌未点亮</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>喷洒光警报器输出链路</t>
         </is>
       </c>
     </row>
@@ -35580,23 +35673,23 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(测试执行表!C2:C603,A2)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A2)</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIFS(测试执行表!C2:C603,A2,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A2,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>COUNTIFS(测试执行表!C2:C603,A2,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A2,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>COUNTIFS(测试执行表!C2:C603,A2,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A2,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>COUNTIFS(测试执行表!C2:C603,A2,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A2,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A2,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A2,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G2">
@@ -35611,23 +35704,23 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(测试执行表!C2:C603,A3)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A3)</f>
         <v/>
       </c>
       <c r="C3">
-        <f>COUNTIFS(测试执行表!C2:C603,A3,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A3,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>COUNTIFS(测试执行表!C2:C603,A3,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A3,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>COUNTIFS(测试执行表!C2:C603,A3,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A3,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>COUNTIFS(测试执行表!C2:C603,A3,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A3,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A3,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A3,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G3">
@@ -35642,23 +35735,23 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(测试执行表!C2:C603,A4)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A4)</f>
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIFS(测试执行表!C2:C603,A4,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A4,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>COUNTIFS(测试执行表!C2:C603,A4,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A4,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>COUNTIFS(测试执行表!C2:C603,A4,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A4,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F4">
-        <f>COUNTIFS(测试执行表!C2:C603,A4,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A4,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A4,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A4,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G4">
@@ -35673,23 +35766,23 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(测试执行表!C2:C603,A5)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A5)</f>
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIFS(测试执行表!C2:C603,A5,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A5,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>COUNTIFS(测试执行表!C2:C603,A5,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A5,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>COUNTIFS(测试执行表!C2:C603,A5,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A5,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F5">
-        <f>COUNTIFS(测试执行表!C2:C603,A5,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A5,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A5,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A5,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G5">
@@ -35704,23 +35797,23 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(测试执行表!C2:C603,A6)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A6)</f>
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIFS(测试执行表!C2:C603,A6,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A6,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIFS(测试执行表!C2:C603,A6,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A6,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>COUNTIFS(测试执行表!C2:C603,A6,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A6,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>COUNTIFS(测试执行表!C2:C603,A6,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A6,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A6,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A6,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G6">
@@ -35735,23 +35828,23 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(测试执行表!C2:C603,A7)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A7)</f>
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIFS(测试执行表!C2:C603,A7,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A7,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIFS(测试执行表!C2:C603,A7,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A7,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>COUNTIFS(测试执行表!C2:C603,A7,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A7,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F7">
-        <f>COUNTIFS(测试执行表!C2:C603,A7,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A7,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A7,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A7,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G7">
@@ -35766,23 +35859,23 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(测试执行表!C2:C603,A8)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A8)</f>
         <v/>
       </c>
       <c r="C8">
-        <f>COUNTIFS(测试执行表!C2:C603,A8,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A8,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>COUNTIFS(测试执行表!C2:C603,A8,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A8,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>COUNTIFS(测试执行表!C2:C603,A8,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A8,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F8">
-        <f>COUNTIFS(测试执行表!C2:C603,A8,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A8,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A8,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A8,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G8">
@@ -35797,23 +35890,23 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(测试执行表!C2:C603,A9)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A9)</f>
         <v/>
       </c>
       <c r="C9">
-        <f>COUNTIFS(测试执行表!C2:C603,A9,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A9,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>COUNTIFS(测试执行表!C2:C603,A9,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A9,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>COUNTIFS(测试执行表!C2:C603,A9,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A9,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F9">
-        <f>COUNTIFS(测试执行表!C2:C603,A9,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A9,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A9,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A9,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G9">
@@ -35828,23 +35921,23 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIF(测试执行表!C2:C603,A10)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A10)</f>
         <v/>
       </c>
       <c r="C10">
-        <f>COUNTIFS(测试执行表!C2:C603,A10,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A10,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>COUNTIFS(测试执行表!C2:C603,A10,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A10,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>COUNTIFS(测试执行表!C2:C603,A10,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A10,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F10">
-        <f>COUNTIFS(测试执行表!C2:C603,A10,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A10,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A10,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A10,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G10">
@@ -35859,23 +35952,23 @@
         </is>
       </c>
       <c r="B11">
-        <f>COUNTIF(测试执行表!C2:C603,A11)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A11)</f>
         <v/>
       </c>
       <c r="C11">
-        <f>COUNTIFS(测试执行表!C2:C603,A11,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A11,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>COUNTIFS(测试执行表!C2:C603,A11,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A11,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>COUNTIFS(测试执行表!C2:C603,A11,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A11,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F11">
-        <f>COUNTIFS(测试执行表!C2:C603,A11,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A11,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A11,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A11,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G11">
@@ -35890,23 +35983,23 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTIF(测试执行表!C2:C603,A12)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A12)</f>
         <v/>
       </c>
       <c r="C12">
-        <f>COUNTIFS(测试执行表!C2:C603,A12,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A12,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>COUNTIFS(测试执行表!C2:C603,A12,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A12,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>COUNTIFS(测试执行表!C2:C603,A12,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A12,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>COUNTIFS(测试执行表!C2:C603,A12,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A12,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A12,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A12,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G12">
@@ -35921,23 +36014,23 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTIF(测试执行表!C2:C603,A13)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A13)</f>
         <v/>
       </c>
       <c r="C13">
-        <f>COUNTIFS(测试执行表!C2:C603,A13,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A13,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D13">
-        <f>COUNTIFS(测试执行表!C2:C603,A13,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A13,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E13">
-        <f>COUNTIFS(测试执行表!C2:C603,A13,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A13,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F13">
-        <f>COUNTIFS(测试执行表!C2:C603,A13,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A13,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A13,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A13,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G13">
@@ -35952,23 +36045,23 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF(测试执行表!C2:C603,A14)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A14)</f>
         <v/>
       </c>
       <c r="C14">
-        <f>COUNTIFS(测试执行表!C2:C603,A14,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A14,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D14">
-        <f>COUNTIFS(测试执行表!C2:C603,A14,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A14,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E14">
-        <f>COUNTIFS(测试执行表!C2:C603,A14,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A14,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F14">
-        <f>COUNTIFS(测试执行表!C2:C603,A14,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A14,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A14,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A14,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G14">
@@ -35983,23 +36076,23 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF(测试执行表!C2:C603,A15)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A15)</f>
         <v/>
       </c>
       <c r="C15">
-        <f>COUNTIFS(测试执行表!C2:C603,A15,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A15,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D15">
-        <f>COUNTIFS(测试执行表!C2:C603,A15,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A15,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E15">
-        <f>COUNTIFS(测试执行表!C2:C603,A15,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A15,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F15">
-        <f>COUNTIFS(测试执行表!C2:C603,A15,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A15,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A15,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A15,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G15">
@@ -36014,23 +36107,23 @@
         </is>
       </c>
       <c r="B16">
-        <f>COUNTIF(测试执行表!C2:C603,A16)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A16)</f>
         <v/>
       </c>
       <c r="C16">
-        <f>COUNTIFS(测试执行表!C2:C603,A16,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A16,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D16">
-        <f>COUNTIFS(测试执行表!C2:C603,A16,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A16,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E16">
-        <f>COUNTIFS(测试执行表!C2:C603,A16,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A16,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F16">
-        <f>COUNTIFS(测试执行表!C2:C603,A16,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A16,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A16,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A16,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G16">
@@ -36045,23 +36138,23 @@
         </is>
       </c>
       <c r="B17">
-        <f>COUNTIF(测试执行表!C2:C603,A17)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A17)</f>
         <v/>
       </c>
       <c r="C17">
-        <f>COUNTIFS(测试执行表!C2:C603,A17,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A17,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D17">
-        <f>COUNTIFS(测试执行表!C2:C603,A17,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A17,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E17">
-        <f>COUNTIFS(测试执行表!C2:C603,A17,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A17,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F17">
-        <f>COUNTIFS(测试执行表!C2:C603,A17,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A17,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A17,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A17,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G17">
@@ -36076,23 +36169,23 @@
         </is>
       </c>
       <c r="B18">
-        <f>COUNTIF(测试执行表!C2:C603,A18)</f>
+        <f>COUNTIF(测试执行表!C2:C604,A18)</f>
         <v/>
       </c>
       <c r="C18">
-        <f>COUNTIFS(测试执行表!C2:C603,A18,测试执行表!J2:J603,"通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A18,测试执行表!J2:J604,"通过")</f>
         <v/>
       </c>
       <c r="D18">
-        <f>COUNTIFS(测试执行表!C2:C603,A18,测试执行表!J2:J603,"不通过")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A18,测试执行表!J2:J604,"不通过")</f>
         <v/>
       </c>
       <c r="E18">
-        <f>COUNTIFS(测试执行表!C2:C603,A18,测试执行表!J2:J603,"不适用")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A18,测试执行表!J2:J604,"不适用")</f>
         <v/>
       </c>
       <c r="F18">
-        <f>COUNTIFS(测试执行表!C2:C603,A18,测试执行表!J2:J603,"待测")+COUNTIFS(测试执行表!C2:C603,A18,测试执行表!J2:J603,"暂不测试")</f>
+        <f>COUNTIFS(测试执行表!C2:C604,A18,测试执行表!J2:J604,"待测")+COUNTIFS(测试执行表!C2:C604,A18,测试执行表!J2:J604,"暂不测试")</f>
         <v/>
       </c>
       <c r="G18">
@@ -36111,7 +36204,7 @@
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>SUM(C2:C603)</f>
+        <f>SUM(C2:C604)</f>
         <v/>
       </c>
       <c r="D19" s="10">

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -1977,7 +1977,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -3299,7 +3299,7 @@
       <c r="I48" s="3" t="n"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K48" s="2" t="n"/>
@@ -4900,10 +4900,14 @@
           <t>点数判据随产品形态定（见 §17）：无联动功能形态＝≥2 点且 ≤5 点（5 点上限是产品类别边界：超过即属联动控制器须按 GB 16806 认证）；带联动功能形态＝按 GB 16806 4.2.2.8 ≥6 组</t>
         </is>
       </c>
-      <c r="I79" s="3" t="n"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>介入输入输出模块，巡检灯是亮的，用万用表测电压，电压是跳动的，接近 24V。按启动按钮。启动按钮不亮</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K79" s="2" t="n"/>

--- a/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
+++ b/embedded-gateway/fire-alarm/docs/testing/test-cases-execution.xlsx
@@ -14,7 +14,7 @@
     <sheet name="分组统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$M$593</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试执行表'!$A$1:$N$593</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9174,14 +9174,23 @@
           <t>见子项</t>
         </is>
       </c>
-      <c r="I162" s="3" t="n"/>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>可以屏蔽，但是屏蔽的时候。提示红色提示语【设备处于屏蔽状态】
+可以解除，但是解除报的信息是红色的【设备处于未屏蔽状态】</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="K162" s="2" t="n"/>
-      <c r="L162" s="2" t="n"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M162" s="3" t="n"/>
       <c r="N162" s="2" t="inlineStr">
         <is>
@@ -9289,13 +9298,13 @@
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K164" s="2" t="n"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M164" s="3" t="n"/>
@@ -10033,11 +10042,15 @@
       <c r="I178" s="3" t="n"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K178" s="2" t="n"/>
-      <c r="L178" s="2" t="n"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
           <t>子项.1 待条件；.2 单独解除可测</t>
@@ -10091,13 +10104,13 @@
       <c r="I179" s="3" t="n"/>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待测</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K179" s="2" t="n"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
@@ -10150,14 +10163,22 @@
           <t>可单独解除</t>
         </is>
       </c>
-      <c r="I180" s="3" t="n"/>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>可以解除，但是解除报的信息是红色的【设备处于未屏蔽状态】</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
       <c r="K180" s="2" t="n"/>
-      <c r="L180" s="2" t="n"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M180" s="3" t="n"/>
       <c r="N180" s="2" t="inlineStr">
         <is>
@@ -12342,18 +12363,18 @@
           <t>② 1 min 不操作→退出检查状态并熄灭指示灯</t>
         </is>
       </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t>超过了 1 min, 实测 70s 左右</t>
-        </is>
-      </c>
+      <c r="I222" s="3" t="n"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>不通过</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="K222" s="2" t="n"/>
-      <c r="L222" s="2" t="n"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M222" s="3" t="n"/>
       <c r="N222" s="2" t="inlineStr">
         <is>
@@ -20172,7 +20193,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="M365" s="3" t="inlineStr"/>
+      <c r="M365" s="3" t="n"/>
       <c r="N365" s="2" t="inlineStr">
         <is>
           <t>监控&amp;控制 / 屏蔽控制</t>
@@ -21132,7 +21153,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="M381" s="3" t="inlineStr"/>
+      <c r="M381" s="3" t="n"/>
       <c r="N381" s="2" t="inlineStr">
         <is>
           <t>设置 / 基础设置</t>
@@ -32088,7 +32109,7 @@
           <t>不通过</t>
         </is>
       </c>
-      <c r="K584" s="15" t="inlineStr"/>
+      <c r="K584" s="15" t="n"/>
       <c r="L584" s="15" t="inlineStr">
         <is>
           <t>2026-08-19</t>
@@ -32139,13 +32160,13 @@
           <t>≤100 s 报障并指示部位</t>
         </is>
       </c>
-      <c r="I585" s="15" t="inlineStr"/>
+      <c r="I585" s="15" t="n"/>
       <c r="J585" s="15" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="K585" s="15" t="inlineStr"/>
+      <c r="K585" s="15" t="n"/>
       <c r="L585" s="15" t="inlineStr">
         <is>
           <t>2026-08-19</t>
@@ -32196,15 +32217,15 @@
           <t>≤100 s 报障（总线制短路应报故障）</t>
         </is>
       </c>
-      <c r="I586" s="15" t="inlineStr"/>
+      <c r="I586" s="15" t="n"/>
       <c r="J586" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K586" s="15" t="inlineStr"/>
-      <c r="L586" s="15" t="inlineStr"/>
-      <c r="M586" s="15" t="inlineStr"/>
+      <c r="K586" s="15" t="n"/>
+      <c r="L586" s="15" t="n"/>
+      <c r="M586" s="15" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="15" t="n">
@@ -32245,15 +32266,15 @@
           <t>≤100 s 报障；火警下仍须显示（尾注例外）</t>
         </is>
       </c>
-      <c r="I587" s="15" t="inlineStr"/>
+      <c r="I587" s="15" t="n"/>
       <c r="J587" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K587" s="15" t="inlineStr"/>
-      <c r="L587" s="15" t="inlineStr"/>
-      <c r="M587" s="15" t="inlineStr"/>
+      <c r="K587" s="15" t="n"/>
+      <c r="L587" s="15" t="n"/>
+      <c r="M587" s="15" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="15" t="n">
@@ -32294,15 +32315,15 @@
           <t>≤100 s 报该部位故障（防拆）</t>
         </is>
       </c>
-      <c r="I588" s="15" t="inlineStr"/>
+      <c r="I588" s="15" t="n"/>
       <c r="J588" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K588" s="15" t="inlineStr"/>
-      <c r="L588" s="15" t="inlineStr"/>
-      <c r="M588" s="15" t="inlineStr"/>
+      <c r="K588" s="15" t="n"/>
+      <c r="L588" s="15" t="n"/>
+      <c r="M588" s="15" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="15" t="n">
@@ -32343,14 +32364,14 @@
           <t>≤100 s 报障指示部位</t>
         </is>
       </c>
-      <c r="I589" s="15" t="inlineStr"/>
+      <c r="I589" s="15" t="n"/>
       <c r="J589" s="15" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="K589" s="15" t="inlineStr"/>
-      <c r="L589" s="15" t="inlineStr"/>
+      <c r="K589" s="15" t="n"/>
+      <c r="L589" s="15" t="n"/>
       <c r="M589" s="15" t="inlineStr">
         <is>
           <t>待条件：需手报</t>
@@ -32396,14 +32417,14 @@
           <t>≤100 s 报障指示部位</t>
         </is>
       </c>
-      <c r="I590" s="15" t="inlineStr"/>
+      <c r="I590" s="15" t="n"/>
       <c r="J590" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K590" s="15" t="inlineStr"/>
-      <c r="L590" s="15" t="inlineStr"/>
+      <c r="K590" s="15" t="n"/>
+      <c r="L590" s="15" t="n"/>
       <c r="M590" s="15" t="inlineStr">
         <is>
           <t>待条件：需火灾显示盘；可先用注册无硬件法验监督路径</t>
@@ -32449,14 +32470,14 @@
           <t>≤100 s 报障；火警下显示不受影响</t>
         </is>
       </c>
-      <c r="I591" s="15" t="inlineStr"/>
+      <c r="I591" s="15" t="n"/>
       <c r="J591" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K591" s="15" t="inlineStr"/>
-      <c r="L591" s="15" t="inlineStr"/>
+      <c r="K591" s="15" t="n"/>
+      <c r="L591" s="15" t="n"/>
       <c r="M591" s="15" t="inlineStr">
         <is>
           <t>待条件：需传输装置</t>
@@ -32502,13 +32523,13 @@
           <t>≤100 s 报障；火警下显示不受影响</t>
         </is>
       </c>
-      <c r="I592" s="15" t="inlineStr"/>
+      <c r="I592" s="15" t="n"/>
       <c r="J592" s="15" t="inlineStr">
         <is>
           <t>待测</t>
         </is>
       </c>
-      <c r="K592" s="15" t="inlineStr"/>
+      <c r="K592" s="15" t="n"/>
       <c r="L592" s="15" t="inlineStr">
         <is>
           <t>2026-08-19</t>
@@ -32569,7 +32590,7 @@
           <t>不通过</t>
         </is>
       </c>
-      <c r="K593" s="15" t="inlineStr"/>
+      <c r="K593" s="15" t="n"/>
       <c r="L593" s="15" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -32582,7 +32603,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M593"/>
+  <autoFilter ref="A1:N593"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J635" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,不通过,不适用,待测"</formula1>
@@ -33815,7 +33836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -35023,6 +35044,38 @@
       <c r="F42" s="15" t="inlineStr">
         <is>
           <t>喷洒光警报器输出链路</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SH-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>监控&amp;控制 / 屏蔽控制</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>手动屏蔽与解除</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>功能可用但提示语用红色：屏蔽时提示红色【设备处于屏蔽状态】、解除时提示红色【设备处于未屏蔽状态】。红色是 GB 4717 5.3.2.1 的火警/启动色，用于常态确认信息会稀释报警色语义（同现象见 SH-05.2 备注）</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>提示语配色规范</t>
         </is>
       </c>
     </row>
